--- a/output/北塩原村_図表番号一覧.xlsx
+++ b/output/北塩原村_図表番号一覧.xlsx
@@ -535,7 +535,7 @@
       </c>
       <c r="B6" s="3" t="inlineStr">
         <is>
-          <t>図24点・表84点に章ごとの通し番号を振った（図１-１・表１-１の形）。注記ボックス（【村へ確認】等の1×1の枠）45点には振っていない。確定時に削るため、番号を振ると欠番が出るからである。</t>
+          <t>図25点・表86点に章ごとの通し番号を振った（図１-１・表１-１の形）。注記ボックス（【村へ確認】等の1×1の枠）45点には振っていない。確定時に削るため、番号を振ると欠番が出るからである。</t>
         </is>
       </c>
     </row>
@@ -607,7 +607,7 @@
       </c>
       <c r="B12" s="3" t="inlineStr">
         <is>
-          <t>出所は、村の実績・アンケート・外部資料から数値を引いた図表40点にのみ付けた。手順・区分・確認事項を整理しただけの表は本計画の記述そのものであり、出所を書くと出どころが二重になるためである（規約への補足1件）。</t>
+          <t>出所は、村の実績・アンケート・外部資料から数値を引いた図表41点にのみ付けた。手順・区分・確認事項を整理しただけの表は本計画の記述そのものであり、出所を書くと出どころが二重になるためである（規約への補足1件）。</t>
         </is>
       </c>
     </row>
@@ -638,7 +638,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F29"/>
+  <dimension ref="A1:F30"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -652,7 +652,7 @@
     <row r="1" ht="30" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>図 24点</t>
+          <t>図 25点</t>
         </is>
       </c>
     </row>
@@ -1279,12 +1279,12 @@
       </c>
       <c r="B24" s="3" t="inlineStr">
         <is>
-          <t>65歳到達時の判定の流れ</t>
+          <t>ライフコースと制度の移行</t>
         </is>
       </c>
       <c r="C24" s="3" t="inlineStr">
         <is>
-          <t>第5章5（2）65歳到達時のサービスの区分</t>
+          <t>第5章5 年齢到達に伴うサービスの移行</t>
         </is>
       </c>
       <c r="D24" s="8" t="inlineStr">
@@ -1299,7 +1299,7 @@
       </c>
       <c r="F24" s="3" t="inlineStr">
         <is>
-          <t>資料：障害者総合支援法第７条及び本計画により作成</t>
+          <t>資料：北塩原村（第５章５及び第７章により作成）</t>
         </is>
       </c>
     </row>
@@ -1311,12 +1311,12 @@
       </c>
       <c r="B25" s="4" t="inlineStr">
         <is>
-          <t>関係機関との連携</t>
+          <t>65歳到達時の判定の流れ</t>
         </is>
       </c>
       <c r="C25" s="4" t="inlineStr">
         <is>
-          <t>第5章6 関係機関との連携</t>
+          <t>第5章5（2）65歳到達時のサービスの区分</t>
         </is>
       </c>
       <c r="D25" s="8" t="inlineStr">
@@ -1331,7 +1331,7 @@
       </c>
       <c r="F25" s="4" t="inlineStr">
         <is>
-          <t>資料：北塩原村（第５章６により作成）</t>
+          <t>資料：障害者総合支援法第７条及び本計画により作成</t>
         </is>
       </c>
     </row>
@@ -1343,12 +1343,12 @@
       </c>
       <c r="B26" s="3" t="inlineStr">
         <is>
-          <t>障がい福祉サービス等に係る給付費の推移</t>
+          <t>関係機関との連携</t>
         </is>
       </c>
       <c r="C26" s="3" t="inlineStr">
         <is>
-          <t>第5章7（1）給付費の推移</t>
+          <t>第5章6 関係機関との連携</t>
         </is>
       </c>
       <c r="D26" s="8" t="inlineStr">
@@ -1363,7 +1363,7 @@
       </c>
       <c r="F26" s="3" t="inlineStr">
         <is>
-          <t>資料：村提供の障がいサービス給付実績</t>
+          <t>資料：北塩原村（第５章６により作成）</t>
         </is>
       </c>
     </row>
@@ -1375,12 +1375,12 @@
       </c>
       <c r="B27" s="4" t="inlineStr">
         <is>
-          <t>サービス別の給付費（令和７年度）</t>
+          <t>障がい福祉サービス等に係る給付費の推移</t>
         </is>
       </c>
       <c r="C27" s="4" t="inlineStr">
         <is>
-          <t>第5章7（3）サービス別の構成</t>
+          <t>第5章7（1）給付費の推移</t>
         </is>
       </c>
       <c r="D27" s="8" t="inlineStr">
@@ -1402,17 +1402,17 @@
     <row r="28">
       <c r="A28" s="3" t="inlineStr">
         <is>
-          <t>図6-1</t>
+          <t>図5-7</t>
         </is>
       </c>
       <c r="B28" s="3" t="inlineStr">
         <is>
-          <t>高齢化率の推移</t>
+          <t>サービス別の給付費（令和７年度）</t>
         </is>
       </c>
       <c r="C28" s="3" t="inlineStr">
         <is>
-          <t>第6章1（1）高齢化率</t>
+          <t>第5章7（3）サービス別の構成</t>
         </is>
       </c>
       <c r="D28" s="8" t="inlineStr">
@@ -1427,37 +1427,69 @@
       </c>
       <c r="F28" s="3" t="inlineStr">
         <is>
-          <t>資料：北塩原村（各年４月１日現在）</t>
+          <t>資料：村提供の障がいサービス給付実績</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="4" t="inlineStr">
         <is>
+          <t>図6-1</t>
+        </is>
+      </c>
+      <c r="B29" s="4" t="inlineStr">
+        <is>
+          <t>高齢化率の推移</t>
+        </is>
+      </c>
+      <c r="C29" s="4" t="inlineStr">
+        <is>
+          <t>第6章1（1）高齢化率</t>
+        </is>
+      </c>
+      <c r="D29" s="8" t="inlineStr">
+        <is>
+          <t>当方</t>
+        </is>
+      </c>
+      <c r="E29" s="4" t="inlineStr">
+        <is>
+          <t>（画像内に表題なし）</t>
+        </is>
+      </c>
+      <c r="F29" s="4" t="inlineStr">
+        <is>
+          <t>資料：北塩原村（各年４月１日現在）</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="3" t="inlineStr">
+        <is>
           <t>図7-1</t>
         </is>
       </c>
-      <c r="B29" s="4" t="inlineStr">
+      <c r="B30" s="3" t="inlineStr">
         <is>
           <t>他の計画との関係</t>
         </is>
       </c>
-      <c r="C29" s="4" t="inlineStr">
+      <c r="C30" s="3" t="inlineStr">
         <is>
           <t>第7章 他計画との連携（章の冒頭）</t>
         </is>
       </c>
-      <c r="D29" s="6" t="inlineStr">
+      <c r="D30" s="6" t="inlineStr">
         <is>
           <t>他メンバー</t>
         </is>
       </c>
-      <c r="E29" s="7" t="inlineStr">
+      <c r="E30" s="7" t="inlineStr">
         <is>
           <t>図表　他の計画との関係</t>
         </is>
       </c>
-      <c r="F29" s="4" t="inlineStr">
+      <c r="F30" s="3" t="inlineStr">
         <is>
           <t>―</t>
         </is>
@@ -1478,7 +1510,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E89"/>
+  <dimension ref="A1:E91"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -1491,7 +1523,7 @@
     <row r="1" ht="30" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>表 84点</t>
+          <t>表 86点</t>
         </is>
       </c>
     </row>
@@ -2540,7 +2572,7 @@
       </c>
       <c r="B43" s="4" t="inlineStr">
         <is>
-          <t>訪問系サービスの実績</t>
+          <t>見込量を定めるまでの段階</t>
         </is>
       </c>
       <c r="C43" s="4" t="inlineStr">
@@ -2550,12 +2582,12 @@
       </c>
       <c r="D43" s="4" t="inlineStr">
         <is>
-          <t>サービス種別 / 単位</t>
+          <t>段階 / 何を見るか</t>
         </is>
       </c>
       <c r="E43" s="4" t="inlineStr">
         <is>
-          <t>資料：北塩原村</t>
+          <t>―</t>
         </is>
       </c>
     </row>
@@ -2567,7 +2599,7 @@
       </c>
       <c r="B44" s="3" t="inlineStr">
         <is>
-          <t>訪問系サービスの見込量</t>
+          <t>訪問系サービスの実績</t>
         </is>
       </c>
       <c r="C44" s="3" t="inlineStr">
@@ -2582,7 +2614,7 @@
       </c>
       <c r="E44" s="3" t="inlineStr">
         <is>
-          <t>―</t>
+          <t>資料：北塩原村</t>
         </is>
       </c>
     </row>
@@ -2594,7 +2626,7 @@
       </c>
       <c r="B45" s="4" t="inlineStr">
         <is>
-          <t>日中活動系サービスの実績</t>
+          <t>訪問系サービスの見込量</t>
         </is>
       </c>
       <c r="C45" s="4" t="inlineStr">
@@ -2609,7 +2641,7 @@
       </c>
       <c r="E45" s="4" t="inlineStr">
         <is>
-          <t>資料：北塩原村</t>
+          <t>―</t>
         </is>
       </c>
     </row>
@@ -2621,7 +2653,7 @@
       </c>
       <c r="B46" s="3" t="inlineStr">
         <is>
-          <t>日中活動系サービスの見込量</t>
+          <t>訪問系サービスの利用がない場合に確かめる事項</t>
         </is>
       </c>
       <c r="C46" s="3" t="inlineStr">
@@ -2631,7 +2663,7 @@
       </c>
       <c r="D46" s="3" t="inlineStr">
         <is>
-          <t>サービス種別 / 単位</t>
+          <t>確かめる側 / 確かめる事項</t>
         </is>
       </c>
       <c r="E46" s="3" t="inlineStr">
@@ -2648,7 +2680,7 @@
       </c>
       <c r="B47" s="4" t="inlineStr">
         <is>
-          <t>強度行動障害を有する方等の生活介護の利用の見込み</t>
+          <t>日中活動系サービスの実績</t>
         </is>
       </c>
       <c r="C47" s="4" t="inlineStr">
@@ -2658,12 +2690,12 @@
       </c>
       <c r="D47" s="4" t="inlineStr">
         <is>
-          <t>区分 / 現在の人数</t>
+          <t>サービス種別 / 単位</t>
         </is>
       </c>
       <c r="E47" s="4" t="inlineStr">
         <is>
-          <t>―</t>
+          <t>資料：北塩原村</t>
         </is>
       </c>
     </row>
@@ -2675,7 +2707,7 @@
       </c>
       <c r="B48" s="3" t="inlineStr">
         <is>
-          <t>居住系サービスの実績</t>
+          <t>日中活動系サービスの見込量</t>
         </is>
       </c>
       <c r="C48" s="3" t="inlineStr">
@@ -2690,7 +2722,7 @@
       </c>
       <c r="E48" s="3" t="inlineStr">
         <is>
-          <t>資料：北塩原村</t>
+          <t>―</t>
         </is>
       </c>
     </row>
@@ -2702,7 +2734,7 @@
       </c>
       <c r="B49" s="4" t="inlineStr">
         <is>
-          <t>居住系サービスの見込量</t>
+          <t>強度行動障害を有する方等の生活介護の利用の見込み</t>
         </is>
       </c>
       <c r="C49" s="4" t="inlineStr">
@@ -2712,7 +2744,7 @@
       </c>
       <c r="D49" s="4" t="inlineStr">
         <is>
-          <t>サービス種別 / 単位</t>
+          <t>区分 / 現在の人数</t>
         </is>
       </c>
       <c r="E49" s="4" t="inlineStr">
@@ -2729,7 +2761,7 @@
       </c>
       <c r="B50" s="3" t="inlineStr">
         <is>
-          <t>相談支援の実績</t>
+          <t>居住系サービスの実績</t>
         </is>
       </c>
       <c r="C50" s="3" t="inlineStr">
@@ -2756,7 +2788,7 @@
       </c>
       <c r="B51" s="4" t="inlineStr">
         <is>
-          <t>相談支援の見込量</t>
+          <t>居住系サービスの見込量</t>
         </is>
       </c>
       <c r="C51" s="4" t="inlineStr">
@@ -2783,7 +2815,7 @@
       </c>
       <c r="B52" s="3" t="inlineStr">
         <is>
-          <t>障がい児支援の実績</t>
+          <t>相談支援の実績</t>
         </is>
       </c>
       <c r="C52" s="3" t="inlineStr">
@@ -2810,7 +2842,7 @@
       </c>
       <c r="B53" s="4" t="inlineStr">
         <is>
-          <t>障がい児支援の見込量</t>
+          <t>相談支援の見込量</t>
         </is>
       </c>
       <c r="C53" s="4" t="inlineStr">
@@ -2837,7 +2869,7 @@
       </c>
       <c r="B54" s="3" t="inlineStr">
         <is>
-          <t>一般の子育て施策と障がい福祉の切り分け</t>
+          <t>障がい児支援の実績</t>
         </is>
       </c>
       <c r="C54" s="3" t="inlineStr">
@@ -2847,12 +2879,12 @@
       </c>
       <c r="D54" s="3" t="inlineStr">
         <is>
-          <t>場面 / まず確かめる一般の子育て施策</t>
+          <t>サービス種別 / 単位</t>
         </is>
       </c>
       <c r="E54" s="3" t="inlineStr">
         <is>
-          <t>―</t>
+          <t>資料：北塩原村</t>
         </is>
       </c>
     </row>
@@ -2864,7 +2896,7 @@
       </c>
       <c r="B55" s="4" t="inlineStr">
         <is>
-          <t>事業所の受入余力について照会する事項</t>
+          <t>障がい児支援の見込量</t>
         </is>
       </c>
       <c r="C55" s="4" t="inlineStr">
@@ -2874,7 +2906,7 @@
       </c>
       <c r="D55" s="4" t="inlineStr">
         <is>
-          <t>照会する事項 / 確保できる量との関係</t>
+          <t>サービス種別 / 単位</t>
         </is>
       </c>
       <c r="E55" s="4" t="inlineStr">
@@ -2891,7 +2923,7 @@
       </c>
       <c r="B56" s="3" t="inlineStr">
         <is>
-          <t>緊急時に働く仕組み（４つの場面）</t>
+          <t>一般の子育て施策と障がい福祉の切り分け</t>
         </is>
       </c>
       <c r="C56" s="3" t="inlineStr">
@@ -2901,7 +2933,7 @@
       </c>
       <c r="D56" s="3" t="inlineStr">
         <is>
-          <t>場面 / 想定される事態</t>
+          <t>場面 / まず確かめる一般の子育て施策</t>
         </is>
       </c>
       <c r="E56" s="3" t="inlineStr">
@@ -2918,7 +2950,7 @@
       </c>
       <c r="B57" s="4" t="inlineStr">
         <is>
-          <t>災害時にサービスを止めないための備え</t>
+          <t>事業所の受入余力について照会する事項</t>
         </is>
       </c>
       <c r="C57" s="4" t="inlineStr">
@@ -2928,7 +2960,7 @@
       </c>
       <c r="D57" s="4" t="inlineStr">
         <is>
-          <t>備える事項 / 本村の取組み</t>
+          <t>照会する事項 / 確保できる量との関係</t>
         </is>
       </c>
       <c r="E57" s="4" t="inlineStr">
@@ -2945,7 +2977,7 @@
       </c>
       <c r="B58" s="3" t="inlineStr">
         <is>
-          <t>災害時の情報の伝達について確かめること</t>
+          <t>緊急時に働く仕組み（４つの場面）</t>
         </is>
       </c>
       <c r="C58" s="3" t="inlineStr">
@@ -2955,7 +2987,7 @@
       </c>
       <c r="D58" s="3" t="inlineStr">
         <is>
-          <t>確かめること / 確かめ方</t>
+          <t>場面 / 想定される事態</t>
         </is>
       </c>
       <c r="E58" s="3" t="inlineStr">
@@ -2972,7 +3004,7 @@
       </c>
       <c r="B59" s="4" t="inlineStr">
         <is>
-          <t>虐待の予防から再発の防止までの流れ</t>
+          <t>災害時にサービスを止めないための備え</t>
         </is>
       </c>
       <c r="C59" s="4" t="inlineStr">
@@ -2982,7 +3014,7 @@
       </c>
       <c r="D59" s="4" t="inlineStr">
         <is>
-          <t>段階 / 本村の取組み</t>
+          <t>備える事項 / 本村の取組み</t>
         </is>
       </c>
       <c r="E59" s="4" t="inlineStr">
@@ -2999,7 +3031,7 @@
       </c>
       <c r="B60" s="3" t="inlineStr">
         <is>
-          <t>経営基盤に関して把握する事項</t>
+          <t>災害時の情報の伝達について確かめること</t>
         </is>
       </c>
       <c r="C60" s="3" t="inlineStr">
@@ -3009,7 +3041,7 @@
       </c>
       <c r="D60" s="3" t="inlineStr">
         <is>
-          <t>把握する事項 / 見込量への影響</t>
+          <t>確かめること / 確かめ方</t>
         </is>
       </c>
       <c r="E60" s="3" t="inlineStr">
@@ -3026,7 +3058,7 @@
       </c>
       <c r="B61" s="4" t="inlineStr">
         <is>
-          <t>冬季の支援を検討する三つの段階</t>
+          <t>虐待の予防から再発の防止までの流れ</t>
         </is>
       </c>
       <c r="C61" s="4" t="inlineStr">
@@ -3036,7 +3068,7 @@
       </c>
       <c r="D61" s="4" t="inlineStr">
         <is>
-          <t>段階 / 確かめること</t>
+          <t>段階 / 本村の取組み</t>
         </is>
       </c>
       <c r="E61" s="4" t="inlineStr">
@@ -3053,7 +3085,7 @@
       </c>
       <c r="B62" s="3" t="inlineStr">
         <is>
-          <t>冬季の通行規制による中断について記録する事項</t>
+          <t>経営基盤に関して把握する事項</t>
         </is>
       </c>
       <c r="C62" s="3" t="inlineStr">
@@ -3063,7 +3095,7 @@
       </c>
       <c r="D62" s="3" t="inlineStr">
         <is>
-          <t>記録する事項 / 記録の仕方</t>
+          <t>把握する事項 / 見込量への影響</t>
         </is>
       </c>
       <c r="E62" s="3" t="inlineStr">
@@ -3080,7 +3112,7 @@
       </c>
       <c r="B63" s="4" t="inlineStr">
         <is>
-          <t>医療へのアクセス</t>
+          <t>冬季の支援を検討する三つの段階</t>
         </is>
       </c>
       <c r="C63" s="4" t="inlineStr">
@@ -3090,7 +3122,7 @@
       </c>
       <c r="D63" s="4" t="inlineStr">
         <is>
-          <t>場面 / 主な医療資源</t>
+          <t>段階 / 確かめること</t>
         </is>
       </c>
       <c r="E63" s="4" t="inlineStr">
@@ -3107,7 +3139,7 @@
       </c>
       <c r="B64" s="3" t="inlineStr">
         <is>
-          <t>地域生活支援事業の実績</t>
+          <t>冬季の通行規制による中断について記録する事項</t>
         </is>
       </c>
       <c r="C64" s="3" t="inlineStr">
@@ -3117,12 +3149,12 @@
       </c>
       <c r="D64" s="3" t="inlineStr">
         <is>
-          <t>サービスの種類 / 令和６年度</t>
+          <t>記録する事項 / 記録の仕方</t>
         </is>
       </c>
       <c r="E64" s="3" t="inlineStr">
         <is>
-          <t>資料：北塩原村</t>
+          <t>―</t>
         </is>
       </c>
     </row>
@@ -3134,7 +3166,7 @@
       </c>
       <c r="B65" s="4" t="inlineStr">
         <is>
-          <t>地域生活支援事業の見込量</t>
+          <t>医療へのアクセス</t>
         </is>
       </c>
       <c r="C65" s="4" t="inlineStr">
@@ -3144,7 +3176,7 @@
       </c>
       <c r="D65" s="4" t="inlineStr">
         <is>
-          <t>サービスの種類 / 令和９年度</t>
+          <t>場面 / 主な医療資源</t>
         </is>
       </c>
       <c r="E65" s="4" t="inlineStr">
@@ -3161,7 +3193,7 @@
       </c>
       <c r="B66" s="3" t="inlineStr">
         <is>
-          <t>実績がない事業の扱い</t>
+          <t>地域生活支援事業の実績</t>
         </is>
       </c>
       <c r="C66" s="3" t="inlineStr">
@@ -3171,12 +3203,12 @@
       </c>
       <c r="D66" s="3" t="inlineStr">
         <is>
-          <t>実績がない理由 / 確かめ方</t>
+          <t>サービスの種類 / 令和６年度</t>
         </is>
       </c>
       <c r="E66" s="3" t="inlineStr">
         <is>
-          <t>―</t>
+          <t>資料：北塩原村</t>
         </is>
       </c>
     </row>
@@ -3188,7 +3220,7 @@
       </c>
       <c r="B67" s="4" t="inlineStr">
         <is>
-          <t>地域生活支援事業の実施に必要な事項</t>
+          <t>地域生活支援事業の見込量</t>
         </is>
       </c>
       <c r="C67" s="4" t="inlineStr">
@@ -3198,7 +3230,7 @@
       </c>
       <c r="D67" s="4" t="inlineStr">
         <is>
-          <t>事項 / 本村の取扱い</t>
+          <t>サービスの種類 / 令和９年度</t>
         </is>
       </c>
       <c r="E67" s="4" t="inlineStr">
@@ -3215,7 +3247,7 @@
       </c>
       <c r="B68" s="3" t="inlineStr">
         <is>
-          <t>本人に代わって伝えるための道具の使い分け</t>
+          <t>実績がない事業の扱い</t>
         </is>
       </c>
       <c r="C68" s="3" t="inlineStr">
@@ -3225,7 +3257,7 @@
       </c>
       <c r="D68" s="3" t="inlineStr">
         <is>
-          <t>道具 / 伝える場面</t>
+          <t>実績がない理由 / 確かめ方</t>
         </is>
       </c>
       <c r="E68" s="3" t="inlineStr">
@@ -3242,7 +3274,7 @@
       </c>
       <c r="B69" s="4" t="inlineStr">
         <is>
-          <t>年齢到達に伴うサービスの移行</t>
+          <t>地域生活支援事業の実施に必要な事項</t>
         </is>
       </c>
       <c r="C69" s="4" t="inlineStr">
@@ -3252,7 +3284,7 @@
       </c>
       <c r="D69" s="4" t="inlineStr">
         <is>
-          <t>年齢 / 制度上の内容</t>
+          <t>事項 / 本村の取扱い</t>
         </is>
       </c>
       <c r="E69" s="4" t="inlineStr">
@@ -3269,7 +3301,7 @@
       </c>
       <c r="B70" s="3" t="inlineStr">
         <is>
-          <t>学校卒業に伴う移行について確認する事項</t>
+          <t>本人に代わって伝えるための道具の使い分け</t>
         </is>
       </c>
       <c r="C70" s="3" t="inlineStr">
@@ -3279,7 +3311,7 @@
       </c>
       <c r="D70" s="3" t="inlineStr">
         <is>
-          <t>確認する事項 / 見込量への反映</t>
+          <t>道具 / 伝える場面</t>
         </is>
       </c>
       <c r="E70" s="3" t="inlineStr">
@@ -3296,7 +3328,7 @@
       </c>
       <c r="B71" s="4" t="inlineStr">
         <is>
-          <t>65歳到達時のサービスの区分</t>
+          <t>年齢到達に伴うサービスの移行</t>
         </is>
       </c>
       <c r="C71" s="4" t="inlineStr">
@@ -3306,7 +3338,7 @@
       </c>
       <c r="D71" s="4" t="inlineStr">
         <is>
-          <t>区分 / 該当するサービス</t>
+          <t>年齢 / 制度上の内容</t>
         </is>
       </c>
       <c r="E71" s="4" t="inlineStr">
@@ -3323,7 +3355,7 @@
       </c>
       <c r="B72" s="3" t="inlineStr">
         <is>
-          <t>65歳到達時に確認する事項</t>
+          <t>学校卒業に伴う移行について確認する事項</t>
         </is>
       </c>
       <c r="C72" s="3" t="inlineStr">
@@ -3333,7 +3365,7 @@
       </c>
       <c r="D72" s="3" t="inlineStr">
         <is>
-          <t>確認する事項 / 確認の内容</t>
+          <t>確認する事項 / 見込量への反映</t>
         </is>
       </c>
       <c r="E72" s="3" t="inlineStr">
@@ -3350,7 +3382,7 @@
       </c>
       <c r="B73" s="4" t="inlineStr">
         <is>
-          <t>65歳到達時の引継ぎの時期と担当</t>
+          <t>65歳到達時のサービスの区分</t>
         </is>
       </c>
       <c r="C73" s="4" t="inlineStr">
@@ -3360,7 +3392,7 @@
       </c>
       <c r="D73" s="4" t="inlineStr">
         <is>
-          <t>時期 / 行うこと</t>
+          <t>区分 / 該当するサービス</t>
         </is>
       </c>
       <c r="E73" s="4" t="inlineStr">
@@ -3377,7 +3409,7 @@
       </c>
       <c r="B74" s="3" t="inlineStr">
         <is>
-          <t>関係機関と連携の内容</t>
+          <t>65歳到達時に確認する事項</t>
         </is>
       </c>
       <c r="C74" s="3" t="inlineStr">
@@ -3387,7 +3419,7 @@
       </c>
       <c r="D74" s="3" t="inlineStr">
         <is>
-          <t>分野 / 関係機関</t>
+          <t>確認する事項 / 確認の内容</t>
         </is>
       </c>
       <c r="E74" s="3" t="inlineStr">
@@ -3404,7 +3436,7 @@
       </c>
       <c r="B75" s="4" t="inlineStr">
         <is>
-          <t>障がい福祉サービス等に係る給付費の推移</t>
+          <t>65歳到達時の引継ぎの時期と担当</t>
         </is>
       </c>
       <c r="C75" s="4" t="inlineStr">
@@ -3414,12 +3446,12 @@
       </c>
       <c r="D75" s="4" t="inlineStr">
         <is>
-          <t>年度 / 介護給付費等</t>
+          <t>時期 / 行うこと</t>
         </is>
       </c>
       <c r="E75" s="4" t="inlineStr">
         <is>
-          <t>資料：村提供の障がいサービス給付実績</t>
+          <t>―</t>
         </is>
       </c>
     </row>
@@ -3431,7 +3463,7 @@
       </c>
       <c r="B76" s="3" t="inlineStr">
         <is>
-          <t>財源構成（令和７年度・法定負担割合による試算）</t>
+          <t>関係機関と連携の内容</t>
         </is>
       </c>
       <c r="C76" s="3" t="inlineStr">
@@ -3441,12 +3473,12 @@
       </c>
       <c r="D76" s="3" t="inlineStr">
         <is>
-          <t>区分 / 金額</t>
+          <t>分野 / 関係機関</t>
         </is>
       </c>
       <c r="E76" s="3" t="inlineStr">
         <is>
-          <t>資料：村提供の障がいサービス給付実績</t>
+          <t>―</t>
         </is>
       </c>
     </row>
@@ -3458,7 +3490,7 @@
       </c>
       <c r="B77" s="4" t="inlineStr">
         <is>
-          <t>サービス別の給付費と計画上の位置づけ（令和７年度）</t>
+          <t>障がい福祉サービス等に係る給付費の推移</t>
         </is>
       </c>
       <c r="C77" s="4" t="inlineStr">
@@ -3468,7 +3500,7 @@
       </c>
       <c r="D77" s="4" t="inlineStr">
         <is>
-          <t>サービス / 給付費（構成比）</t>
+          <t>年度 / 介護給付費等</t>
         </is>
       </c>
       <c r="E77" s="4" t="inlineStr">
@@ -3480,66 +3512,66 @@
     <row r="78">
       <c r="A78" s="3" t="inlineStr">
         <is>
-          <t>表6-1</t>
+          <t>表5-37</t>
         </is>
       </c>
       <c r="B78" s="3" t="inlineStr">
         <is>
-          <t>高齢化率の推移</t>
+          <t>財源構成（令和７年度・法定負担割合による試算）</t>
         </is>
       </c>
       <c r="C78" s="3" t="inlineStr">
         <is>
-          <t>第6章</t>
+          <t>第5章</t>
         </is>
       </c>
       <c r="D78" s="3" t="inlineStr">
         <is>
-          <t>年度 / 高齢化率</t>
+          <t>区分 / 金額</t>
         </is>
       </c>
       <c r="E78" s="3" t="inlineStr">
         <is>
-          <t>資料：北塩原村</t>
+          <t>資料：村提供の障がいサービス給付実績</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" s="4" t="inlineStr">
         <is>
-          <t>表6-2</t>
+          <t>表5-38</t>
         </is>
       </c>
       <c r="B79" s="4" t="inlineStr">
         <is>
-          <t>精神障がい者及び知的障がい者の人数の推移</t>
+          <t>サービス別の給付費と計画上の位置づけ（令和７年度）</t>
         </is>
       </c>
       <c r="C79" s="4" t="inlineStr">
         <is>
-          <t>第6章</t>
+          <t>第5章</t>
         </is>
       </c>
       <c r="D79" s="4" t="inlineStr">
         <is>
-          <t>年度 / 精神障がい者数（※１）</t>
+          <t>サービス / 給付費（構成比）</t>
         </is>
       </c>
       <c r="E79" s="4" t="inlineStr">
         <is>
-          <t>資料：北塩原村</t>
+          <t>資料：村提供の障がいサービス給付実績</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" s="3" t="inlineStr">
         <is>
-          <t>表6-3</t>
+          <t>表6-1</t>
         </is>
       </c>
       <c r="B80" s="3" t="inlineStr">
         <is>
-          <t>成年後見制度利用支援事業の利用状況</t>
+          <t>高齢化率の推移</t>
         </is>
       </c>
       <c r="C80" s="3" t="inlineStr">
@@ -3549,7 +3581,7 @@
       </c>
       <c r="D80" s="3" t="inlineStr">
         <is>
-          <t>区分 / 令和５年度</t>
+          <t>年度 / 高齢化率</t>
         </is>
       </c>
       <c r="E80" s="3" t="inlineStr">
@@ -3561,12 +3593,12 @@
     <row r="81">
       <c r="A81" s="4" t="inlineStr">
         <is>
-          <t>表6-4</t>
+          <t>表6-2</t>
         </is>
       </c>
       <c r="B81" s="4" t="inlineStr">
         <is>
-          <t>成年後見制度の利用促進に係る指標</t>
+          <t>精神障がい者及び知的障がい者の人数の推移</t>
         </is>
       </c>
       <c r="C81" s="4" t="inlineStr">
@@ -3576,61 +3608,61 @@
       </c>
       <c r="D81" s="4" t="inlineStr">
         <is>
-          <t>指標 / 何を数えるか</t>
+          <t>年度 / 精神障がい者数（※１）</t>
         </is>
       </c>
       <c r="E81" s="4" t="inlineStr">
         <is>
-          <t>―</t>
+          <t>資料：北塩原村</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" s="3" t="inlineStr">
         <is>
-          <t>表7-1</t>
+          <t>表6-3</t>
         </is>
       </c>
       <c r="B82" s="3" t="inlineStr">
         <is>
-          <t>健康21・グッドヘルスプランとの対応</t>
+          <t>成年後見制度利用支援事業の利用状況</t>
         </is>
       </c>
       <c r="C82" s="3" t="inlineStr">
         <is>
-          <t>第7章</t>
+          <t>第6章</t>
         </is>
       </c>
       <c r="D82" s="3" t="inlineStr">
         <is>
-          <t>項目 / 健康21・グッドヘルスプラン</t>
+          <t>区分 / 令和５年度</t>
         </is>
       </c>
       <c r="E82" s="3" t="inlineStr">
         <is>
-          <t>―</t>
+          <t>資料：北塩原村</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" s="4" t="inlineStr">
         <is>
-          <t>表7-2</t>
+          <t>表6-4</t>
         </is>
       </c>
       <c r="B83" s="4" t="inlineStr">
         <is>
-          <t>第五次総合振興計画における本計画の位置づけ</t>
+          <t>成年後見制度の利用促進に係る指標</t>
         </is>
       </c>
       <c r="C83" s="4" t="inlineStr">
         <is>
-          <t>第7章</t>
+          <t>第6章</t>
         </is>
       </c>
       <c r="D83" s="4" t="inlineStr">
         <is>
-          <t>総合振興計画の位置づけ / 内容</t>
+          <t>指標 / 何を数えるか</t>
         </is>
       </c>
       <c r="E83" s="4" t="inlineStr">
@@ -3642,12 +3674,12 @@
     <row r="84">
       <c r="A84" s="3" t="inlineStr">
         <is>
-          <t>表7-3</t>
+          <t>表7-1</t>
         </is>
       </c>
       <c r="B84" s="3" t="inlineStr">
         <is>
-          <t>高齢者福祉計画・介護保険事業計画と重ねて数えないための確認事項</t>
+          <t>健康21・グッドヘルスプランとの対応</t>
         </is>
       </c>
       <c r="C84" s="3" t="inlineStr">
@@ -3657,7 +3689,7 @@
       </c>
       <c r="D84" s="3" t="inlineStr">
         <is>
-          <t>事項 / 両計画での扱い</t>
+          <t>項目 / 健康21・グッドヘルスプラン</t>
         </is>
       </c>
       <c r="E84" s="3" t="inlineStr">
@@ -3669,12 +3701,12 @@
     <row r="85">
       <c r="A85" s="4" t="inlineStr">
         <is>
-          <t>表7-4</t>
+          <t>表7-2</t>
         </is>
       </c>
       <c r="B85" s="4" t="inlineStr">
         <is>
-          <t>こども・子育て計画との整合を確かめる事項</t>
+          <t>第五次総合振興計画における本計画の位置づけ</t>
         </is>
       </c>
       <c r="C85" s="4" t="inlineStr">
@@ -3684,7 +3716,7 @@
       </c>
       <c r="D85" s="4" t="inlineStr">
         <is>
-          <t>確かめる事項 / 確かめ方</t>
+          <t>総合振興計画の位置づけ / 内容</t>
         </is>
       </c>
       <c r="E85" s="4" t="inlineStr">
@@ -3696,22 +3728,22 @@
     <row r="86">
       <c r="A86" s="3" t="inlineStr">
         <is>
-          <t>表8-1</t>
+          <t>表7-3</t>
         </is>
       </c>
       <c r="B86" s="3" t="inlineStr">
         <is>
-          <t>北塩原村障がい者自立支援協議会委員名簿</t>
+          <t>高齢者福祉計画・介護保険事業計画と重ねて数えないための確認事項</t>
         </is>
       </c>
       <c r="C86" s="3" t="inlineStr">
         <is>
-          <t>第8章</t>
+          <t>第7章</t>
         </is>
       </c>
       <c r="D86" s="3" t="inlineStr">
         <is>
-          <t>区　分 / 氏　名</t>
+          <t>事項 / 両計画での扱い</t>
         </is>
       </c>
       <c r="E86" s="3" t="inlineStr">
@@ -3723,22 +3755,22 @@
     <row r="87">
       <c r="A87" s="4" t="inlineStr">
         <is>
-          <t>表8-2</t>
+          <t>表7-4</t>
         </is>
       </c>
       <c r="B87" s="4" t="inlineStr">
         <is>
-          <t>計画の策定経過</t>
+          <t>こども・子育て計画との整合を確かめる事項</t>
         </is>
       </c>
       <c r="C87" s="4" t="inlineStr">
         <is>
-          <t>第8章</t>
+          <t>第7章</t>
         </is>
       </c>
       <c r="D87" s="4" t="inlineStr">
         <is>
-          <t>年月日 / 内容</t>
+          <t>確かめる事項 / 確かめ方</t>
         </is>
       </c>
       <c r="E87" s="4" t="inlineStr">
@@ -3750,12 +3782,12 @@
     <row r="88">
       <c r="A88" s="3" t="inlineStr">
         <is>
-          <t>表8-3</t>
+          <t>表8-1</t>
         </is>
       </c>
       <c r="B88" s="3" t="inlineStr">
         <is>
-          <t>近年の障がい者施策の動向</t>
+          <t>北塩原村障がい者自立支援協議会委員名簿</t>
         </is>
       </c>
       <c r="C88" s="3" t="inlineStr">
@@ -3765,7 +3797,7 @@
       </c>
       <c r="D88" s="3" t="inlineStr">
         <is>
-          <t>年 / 主な動向</t>
+          <t>区　分 / 氏　名</t>
         </is>
       </c>
       <c r="E88" s="3" t="inlineStr">
@@ -3777,25 +3809,79 @@
     <row r="89">
       <c r="A89" s="4" t="inlineStr">
         <is>
+          <t>表8-2</t>
+        </is>
+      </c>
+      <c r="B89" s="4" t="inlineStr">
+        <is>
+          <t>計画の策定経過</t>
+        </is>
+      </c>
+      <c r="C89" s="4" t="inlineStr">
+        <is>
+          <t>第8章</t>
+        </is>
+      </c>
+      <c r="D89" s="4" t="inlineStr">
+        <is>
+          <t>年月日 / 内容</t>
+        </is>
+      </c>
+      <c r="E89" s="4" t="inlineStr">
+        <is>
+          <t>―</t>
+        </is>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" s="3" t="inlineStr">
+        <is>
+          <t>表8-3</t>
+        </is>
+      </c>
+      <c r="B90" s="3" t="inlineStr">
+        <is>
+          <t>近年の障がい者施策の動向</t>
+        </is>
+      </c>
+      <c r="C90" s="3" t="inlineStr">
+        <is>
+          <t>第8章</t>
+        </is>
+      </c>
+      <c r="D90" s="3" t="inlineStr">
+        <is>
+          <t>年 / 主な動向</t>
+        </is>
+      </c>
+      <c r="E90" s="3" t="inlineStr">
+        <is>
+          <t>―</t>
+        </is>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" s="4" t="inlineStr">
+        <is>
           <t>表8-4</t>
         </is>
       </c>
-      <c r="B89" s="4" t="inlineStr">
+      <c r="B91" s="4" t="inlineStr">
         <is>
           <t>用語解説</t>
         </is>
       </c>
-      <c r="C89" s="4" t="inlineStr">
+      <c r="C91" s="4" t="inlineStr">
         <is>
           <t>第8章</t>
         </is>
       </c>
-      <c r="D89" s="4" t="inlineStr">
+      <c r="D91" s="4" t="inlineStr">
         <is>
           <t>用語 / 説明</t>
         </is>
       </c>
-      <c r="E89" s="4" t="inlineStr">
+      <c r="E91" s="4" t="inlineStr">
         <is>
           <t>―</t>
         </is>
@@ -3875,17 +3961,17 @@
       </c>
       <c r="B6" s="3" t="inlineStr">
         <is>
-          <t>第7章4（新設の節）</t>
+          <t>第5章5 年齢到達に伴うサービスの移行</t>
         </is>
       </c>
       <c r="C6" s="3" t="inlineStr">
         <is>
-          <t>児童期→成人期→高齢期を一つの流れとして、こども施策→障がい福祉→介護保険・高齢者福祉の制度間の移行を描く。18歳到達（第5章5（1））と65歳到達（同（2））が別々の節に分かれているため、全体像を示す図がない</t>
+          <t>児童期→成人期→高齢期を一つの流れとして、こども施策→障がい福祉→介護保険・高齢者福祉の制度間の移行を描く。18歳到達（第5章5（1））と65歳到達（同（2））が別々の項に分かれているため、全体像を示す図がない</t>
         </is>
       </c>
       <c r="D6" s="3" t="inlineStr">
         <is>
-          <t>作る（当方の材料で描ける）</t>
+          <t>作成済み（図５-３）。入れ先は第7章4としていたが、18歳・65歳の到達を扱う第5章5の冒頭に置いた</t>
         </is>
       </c>
       <c r="E6" s="7" t="inlineStr">

--- a/output/北塩原村_図表番号一覧.xlsx
+++ b/output/北塩原村_図表番号一覧.xlsx
@@ -535,7 +535,7 @@
       </c>
       <c r="B6" s="3" t="inlineStr">
         <is>
-          <t>図25点・表86点に章ごとの通し番号を振った（図１-１・表１-１の形）。注記ボックス（【村へ確認】等の1×1の枠）45点には振っていない。確定時に削るため、番号を振ると欠番が出るからである。</t>
+          <t>図25点・表87点に章ごとの通し番号を振った（図１-１・表１-１の形）。注記ボックス（【村へ確認】等の1×1の枠）45点には振っていない。確定時に削るため、番号を振ると欠番が出るからである。</t>
         </is>
       </c>
     </row>
@@ -1510,7 +1510,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E91"/>
+  <dimension ref="A1:E92"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -1523,7 +1523,7 @@
     <row r="1" ht="30" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>表 86点</t>
+          <t>表 87点</t>
         </is>
       </c>
     </row>
@@ -2599,7 +2599,7 @@
       </c>
       <c r="B44" s="3" t="inlineStr">
         <is>
-          <t>訪問系サービスの実績</t>
+          <t>必要な利用者数の組み立て</t>
         </is>
       </c>
       <c r="C44" s="3" t="inlineStr">
@@ -2609,12 +2609,12 @@
       </c>
       <c r="D44" s="3" t="inlineStr">
         <is>
-          <t>サービス種別 / 単位</t>
+          <t>加減 / 項目</t>
         </is>
       </c>
       <c r="E44" s="3" t="inlineStr">
         <is>
-          <t>資料：北塩原村</t>
+          <t>―</t>
         </is>
       </c>
     </row>
@@ -2626,7 +2626,7 @@
       </c>
       <c r="B45" s="4" t="inlineStr">
         <is>
-          <t>訪問系サービスの見込量</t>
+          <t>訪問系サービスの実績</t>
         </is>
       </c>
       <c r="C45" s="4" t="inlineStr">
@@ -2641,7 +2641,7 @@
       </c>
       <c r="E45" s="4" t="inlineStr">
         <is>
-          <t>―</t>
+          <t>資料：北塩原村</t>
         </is>
       </c>
     </row>
@@ -2653,7 +2653,7 @@
       </c>
       <c r="B46" s="3" t="inlineStr">
         <is>
-          <t>訪問系サービスの利用がない場合に確かめる事項</t>
+          <t>訪問系サービスの見込量</t>
         </is>
       </c>
       <c r="C46" s="3" t="inlineStr">
@@ -2663,7 +2663,7 @@
       </c>
       <c r="D46" s="3" t="inlineStr">
         <is>
-          <t>確かめる側 / 確かめる事項</t>
+          <t>サービス種別 / 単位</t>
         </is>
       </c>
       <c r="E46" s="3" t="inlineStr">
@@ -2680,7 +2680,7 @@
       </c>
       <c r="B47" s="4" t="inlineStr">
         <is>
-          <t>日中活動系サービスの実績</t>
+          <t>訪問系サービスの利用がない場合に確かめる事項</t>
         </is>
       </c>
       <c r="C47" s="4" t="inlineStr">
@@ -2690,12 +2690,12 @@
       </c>
       <c r="D47" s="4" t="inlineStr">
         <is>
-          <t>サービス種別 / 単位</t>
+          <t>確かめる側 / 確かめる事項</t>
         </is>
       </c>
       <c r="E47" s="4" t="inlineStr">
         <is>
-          <t>資料：北塩原村</t>
+          <t>―</t>
         </is>
       </c>
     </row>
@@ -2707,7 +2707,7 @@
       </c>
       <c r="B48" s="3" t="inlineStr">
         <is>
-          <t>日中活動系サービスの見込量</t>
+          <t>日中活動系サービスの実績</t>
         </is>
       </c>
       <c r="C48" s="3" t="inlineStr">
@@ -2722,7 +2722,7 @@
       </c>
       <c r="E48" s="3" t="inlineStr">
         <is>
-          <t>―</t>
+          <t>資料：北塩原村</t>
         </is>
       </c>
     </row>
@@ -2734,7 +2734,7 @@
       </c>
       <c r="B49" s="4" t="inlineStr">
         <is>
-          <t>強度行動障害を有する方等の生活介護の利用の見込み</t>
+          <t>日中活動系サービスの見込量</t>
         </is>
       </c>
       <c r="C49" s="4" t="inlineStr">
@@ -2744,7 +2744,7 @@
       </c>
       <c r="D49" s="4" t="inlineStr">
         <is>
-          <t>区分 / 現在の人数</t>
+          <t>サービス種別 / 単位</t>
         </is>
       </c>
       <c r="E49" s="4" t="inlineStr">
@@ -2761,7 +2761,7 @@
       </c>
       <c r="B50" s="3" t="inlineStr">
         <is>
-          <t>居住系サービスの実績</t>
+          <t>強度行動障害を有する方等の生活介護の利用の見込み</t>
         </is>
       </c>
       <c r="C50" s="3" t="inlineStr">
@@ -2771,12 +2771,12 @@
       </c>
       <c r="D50" s="3" t="inlineStr">
         <is>
-          <t>サービス種別 / 単位</t>
+          <t>区分 / 現在の人数</t>
         </is>
       </c>
       <c r="E50" s="3" t="inlineStr">
         <is>
-          <t>資料：北塩原村</t>
+          <t>―</t>
         </is>
       </c>
     </row>
@@ -2788,7 +2788,7 @@
       </c>
       <c r="B51" s="4" t="inlineStr">
         <is>
-          <t>居住系サービスの見込量</t>
+          <t>居住系サービスの実績</t>
         </is>
       </c>
       <c r="C51" s="4" t="inlineStr">
@@ -2803,7 +2803,7 @@
       </c>
       <c r="E51" s="4" t="inlineStr">
         <is>
-          <t>―</t>
+          <t>資料：北塩原村</t>
         </is>
       </c>
     </row>
@@ -2815,7 +2815,7 @@
       </c>
       <c r="B52" s="3" t="inlineStr">
         <is>
-          <t>相談支援の実績</t>
+          <t>居住系サービスの見込量</t>
         </is>
       </c>
       <c r="C52" s="3" t="inlineStr">
@@ -2830,7 +2830,7 @@
       </c>
       <c r="E52" s="3" t="inlineStr">
         <is>
-          <t>資料：北塩原村</t>
+          <t>―</t>
         </is>
       </c>
     </row>
@@ -2842,7 +2842,7 @@
       </c>
       <c r="B53" s="4" t="inlineStr">
         <is>
-          <t>相談支援の見込量</t>
+          <t>相談支援の実績</t>
         </is>
       </c>
       <c r="C53" s="4" t="inlineStr">
@@ -2857,7 +2857,7 @@
       </c>
       <c r="E53" s="4" t="inlineStr">
         <is>
-          <t>―</t>
+          <t>資料：北塩原村</t>
         </is>
       </c>
     </row>
@@ -2869,7 +2869,7 @@
       </c>
       <c r="B54" s="3" t="inlineStr">
         <is>
-          <t>障がい児支援の実績</t>
+          <t>相談支援の見込量</t>
         </is>
       </c>
       <c r="C54" s="3" t="inlineStr">
@@ -2884,7 +2884,7 @@
       </c>
       <c r="E54" s="3" t="inlineStr">
         <is>
-          <t>資料：北塩原村</t>
+          <t>―</t>
         </is>
       </c>
     </row>
@@ -2896,7 +2896,7 @@
       </c>
       <c r="B55" s="4" t="inlineStr">
         <is>
-          <t>障がい児支援の見込量</t>
+          <t>障がい児支援の実績</t>
         </is>
       </c>
       <c r="C55" s="4" t="inlineStr">
@@ -2911,7 +2911,7 @@
       </c>
       <c r="E55" s="4" t="inlineStr">
         <is>
-          <t>―</t>
+          <t>資料：北塩原村</t>
         </is>
       </c>
     </row>
@@ -2923,7 +2923,7 @@
       </c>
       <c r="B56" s="3" t="inlineStr">
         <is>
-          <t>一般の子育て施策と障がい福祉の切り分け</t>
+          <t>障がい児支援の見込量</t>
         </is>
       </c>
       <c r="C56" s="3" t="inlineStr">
@@ -2933,7 +2933,7 @@
       </c>
       <c r="D56" s="3" t="inlineStr">
         <is>
-          <t>場面 / まず確かめる一般の子育て施策</t>
+          <t>サービス種別 / 単位</t>
         </is>
       </c>
       <c r="E56" s="3" t="inlineStr">
@@ -2950,7 +2950,7 @@
       </c>
       <c r="B57" s="4" t="inlineStr">
         <is>
-          <t>事業所の受入余力について照会する事項</t>
+          <t>一般の子育て施策と障がい福祉の切り分け</t>
         </is>
       </c>
       <c r="C57" s="4" t="inlineStr">
@@ -2960,7 +2960,7 @@
       </c>
       <c r="D57" s="4" t="inlineStr">
         <is>
-          <t>照会する事項 / 確保できる量との関係</t>
+          <t>場面 / まず確かめる一般の子育て施策</t>
         </is>
       </c>
       <c r="E57" s="4" t="inlineStr">
@@ -2977,7 +2977,7 @@
       </c>
       <c r="B58" s="3" t="inlineStr">
         <is>
-          <t>緊急時に働く仕組み（４つの場面）</t>
+          <t>事業所の受入余力について照会する事項</t>
         </is>
       </c>
       <c r="C58" s="3" t="inlineStr">
@@ -2987,7 +2987,7 @@
       </c>
       <c r="D58" s="3" t="inlineStr">
         <is>
-          <t>場面 / 想定される事態</t>
+          <t>照会する事項 / 確保できる量との関係</t>
         </is>
       </c>
       <c r="E58" s="3" t="inlineStr">
@@ -3004,7 +3004,7 @@
       </c>
       <c r="B59" s="4" t="inlineStr">
         <is>
-          <t>災害時にサービスを止めないための備え</t>
+          <t>緊急時に働く仕組み（４つの場面）</t>
         </is>
       </c>
       <c r="C59" s="4" t="inlineStr">
@@ -3014,7 +3014,7 @@
       </c>
       <c r="D59" s="4" t="inlineStr">
         <is>
-          <t>備える事項 / 本村の取組み</t>
+          <t>場面 / 想定される事態</t>
         </is>
       </c>
       <c r="E59" s="4" t="inlineStr">
@@ -3031,7 +3031,7 @@
       </c>
       <c r="B60" s="3" t="inlineStr">
         <is>
-          <t>災害時の情報の伝達について確かめること</t>
+          <t>災害時にサービスを止めないための備え</t>
         </is>
       </c>
       <c r="C60" s="3" t="inlineStr">
@@ -3041,7 +3041,7 @@
       </c>
       <c r="D60" s="3" t="inlineStr">
         <is>
-          <t>確かめること / 確かめ方</t>
+          <t>備える事項 / 本村の取組み</t>
         </is>
       </c>
       <c r="E60" s="3" t="inlineStr">
@@ -3058,7 +3058,7 @@
       </c>
       <c r="B61" s="4" t="inlineStr">
         <is>
-          <t>虐待の予防から再発の防止までの流れ</t>
+          <t>災害時の情報の伝達について確かめること</t>
         </is>
       </c>
       <c r="C61" s="4" t="inlineStr">
@@ -3068,7 +3068,7 @@
       </c>
       <c r="D61" s="4" t="inlineStr">
         <is>
-          <t>段階 / 本村の取組み</t>
+          <t>確かめること / 確かめ方</t>
         </is>
       </c>
       <c r="E61" s="4" t="inlineStr">
@@ -3085,7 +3085,7 @@
       </c>
       <c r="B62" s="3" t="inlineStr">
         <is>
-          <t>経営基盤に関して把握する事項</t>
+          <t>虐待の予防から再発の防止までの流れ</t>
         </is>
       </c>
       <c r="C62" s="3" t="inlineStr">
@@ -3095,7 +3095,7 @@
       </c>
       <c r="D62" s="3" t="inlineStr">
         <is>
-          <t>把握する事項 / 見込量への影響</t>
+          <t>段階 / 本村の取組み</t>
         </is>
       </c>
       <c r="E62" s="3" t="inlineStr">
@@ -3112,7 +3112,7 @@
       </c>
       <c r="B63" s="4" t="inlineStr">
         <is>
-          <t>冬季の支援を検討する三つの段階</t>
+          <t>経営基盤に関して把握する事項</t>
         </is>
       </c>
       <c r="C63" s="4" t="inlineStr">
@@ -3122,7 +3122,7 @@
       </c>
       <c r="D63" s="4" t="inlineStr">
         <is>
-          <t>段階 / 確かめること</t>
+          <t>把握する事項 / 見込量への影響</t>
         </is>
       </c>
       <c r="E63" s="4" t="inlineStr">
@@ -3139,7 +3139,7 @@
       </c>
       <c r="B64" s="3" t="inlineStr">
         <is>
-          <t>冬季の通行規制による中断について記録する事項</t>
+          <t>冬季の支援を検討する三つの段階</t>
         </is>
       </c>
       <c r="C64" s="3" t="inlineStr">
@@ -3149,7 +3149,7 @@
       </c>
       <c r="D64" s="3" t="inlineStr">
         <is>
-          <t>記録する事項 / 記録の仕方</t>
+          <t>段階 / 確かめること</t>
         </is>
       </c>
       <c r="E64" s="3" t="inlineStr">
@@ -3166,7 +3166,7 @@
       </c>
       <c r="B65" s="4" t="inlineStr">
         <is>
-          <t>医療へのアクセス</t>
+          <t>冬季の通行規制による中断について記録する事項</t>
         </is>
       </c>
       <c r="C65" s="4" t="inlineStr">
@@ -3176,7 +3176,7 @@
       </c>
       <c r="D65" s="4" t="inlineStr">
         <is>
-          <t>場面 / 主な医療資源</t>
+          <t>記録する事項 / 記録の仕方</t>
         </is>
       </c>
       <c r="E65" s="4" t="inlineStr">
@@ -3193,7 +3193,7 @@
       </c>
       <c r="B66" s="3" t="inlineStr">
         <is>
-          <t>地域生活支援事業の実績</t>
+          <t>医療へのアクセス</t>
         </is>
       </c>
       <c r="C66" s="3" t="inlineStr">
@@ -3203,12 +3203,12 @@
       </c>
       <c r="D66" s="3" t="inlineStr">
         <is>
-          <t>サービスの種類 / 令和６年度</t>
+          <t>場面 / 主な医療資源</t>
         </is>
       </c>
       <c r="E66" s="3" t="inlineStr">
         <is>
-          <t>資料：北塩原村</t>
+          <t>―</t>
         </is>
       </c>
     </row>
@@ -3220,7 +3220,7 @@
       </c>
       <c r="B67" s="4" t="inlineStr">
         <is>
-          <t>地域生活支援事業の見込量</t>
+          <t>地域生活支援事業の実績</t>
         </is>
       </c>
       <c r="C67" s="4" t="inlineStr">
@@ -3230,12 +3230,12 @@
       </c>
       <c r="D67" s="4" t="inlineStr">
         <is>
-          <t>サービスの種類 / 令和９年度</t>
+          <t>サービスの種類 / 令和６年度</t>
         </is>
       </c>
       <c r="E67" s="4" t="inlineStr">
         <is>
-          <t>―</t>
+          <t>資料：北塩原村</t>
         </is>
       </c>
     </row>
@@ -3247,7 +3247,7 @@
       </c>
       <c r="B68" s="3" t="inlineStr">
         <is>
-          <t>実績がない事業の扱い</t>
+          <t>地域生活支援事業の見込量</t>
         </is>
       </c>
       <c r="C68" s="3" t="inlineStr">
@@ -3257,7 +3257,7 @@
       </c>
       <c r="D68" s="3" t="inlineStr">
         <is>
-          <t>実績がない理由 / 確かめ方</t>
+          <t>サービスの種類 / 令和９年度</t>
         </is>
       </c>
       <c r="E68" s="3" t="inlineStr">
@@ -3274,7 +3274,7 @@
       </c>
       <c r="B69" s="4" t="inlineStr">
         <is>
-          <t>地域生活支援事業の実施に必要な事項</t>
+          <t>実績がない事業の扱い</t>
         </is>
       </c>
       <c r="C69" s="4" t="inlineStr">
@@ -3284,7 +3284,7 @@
       </c>
       <c r="D69" s="4" t="inlineStr">
         <is>
-          <t>事項 / 本村の取扱い</t>
+          <t>実績がない理由 / 確かめ方</t>
         </is>
       </c>
       <c r="E69" s="4" t="inlineStr">
@@ -3301,7 +3301,7 @@
       </c>
       <c r="B70" s="3" t="inlineStr">
         <is>
-          <t>本人に代わって伝えるための道具の使い分け</t>
+          <t>地域生活支援事業の実施に必要な事項</t>
         </is>
       </c>
       <c r="C70" s="3" t="inlineStr">
@@ -3311,7 +3311,7 @@
       </c>
       <c r="D70" s="3" t="inlineStr">
         <is>
-          <t>道具 / 伝える場面</t>
+          <t>事項 / 本村の取扱い</t>
         </is>
       </c>
       <c r="E70" s="3" t="inlineStr">
@@ -3328,7 +3328,7 @@
       </c>
       <c r="B71" s="4" t="inlineStr">
         <is>
-          <t>年齢到達に伴うサービスの移行</t>
+          <t>本人に代わって伝えるための道具の使い分け</t>
         </is>
       </c>
       <c r="C71" s="4" t="inlineStr">
@@ -3338,7 +3338,7 @@
       </c>
       <c r="D71" s="4" t="inlineStr">
         <is>
-          <t>年齢 / 制度上の内容</t>
+          <t>道具 / 伝える場面</t>
         </is>
       </c>
       <c r="E71" s="4" t="inlineStr">
@@ -3355,7 +3355,7 @@
       </c>
       <c r="B72" s="3" t="inlineStr">
         <is>
-          <t>学校卒業に伴う移行について確認する事項</t>
+          <t>年齢到達に伴うサービスの移行</t>
         </is>
       </c>
       <c r="C72" s="3" t="inlineStr">
@@ -3365,7 +3365,7 @@
       </c>
       <c r="D72" s="3" t="inlineStr">
         <is>
-          <t>確認する事項 / 見込量への反映</t>
+          <t>年齢 / 制度上の内容</t>
         </is>
       </c>
       <c r="E72" s="3" t="inlineStr">
@@ -3382,7 +3382,7 @@
       </c>
       <c r="B73" s="4" t="inlineStr">
         <is>
-          <t>65歳到達時のサービスの区分</t>
+          <t>学校卒業に伴う移行について確認する事項</t>
         </is>
       </c>
       <c r="C73" s="4" t="inlineStr">
@@ -3392,7 +3392,7 @@
       </c>
       <c r="D73" s="4" t="inlineStr">
         <is>
-          <t>区分 / 該当するサービス</t>
+          <t>確認する事項 / 見込量への反映</t>
         </is>
       </c>
       <c r="E73" s="4" t="inlineStr">
@@ -3409,7 +3409,7 @@
       </c>
       <c r="B74" s="3" t="inlineStr">
         <is>
-          <t>65歳到達時に確認する事項</t>
+          <t>65歳到達時のサービスの区分</t>
         </is>
       </c>
       <c r="C74" s="3" t="inlineStr">
@@ -3419,7 +3419,7 @@
       </c>
       <c r="D74" s="3" t="inlineStr">
         <is>
-          <t>確認する事項 / 確認の内容</t>
+          <t>区分 / 該当するサービス</t>
         </is>
       </c>
       <c r="E74" s="3" t="inlineStr">
@@ -3436,7 +3436,7 @@
       </c>
       <c r="B75" s="4" t="inlineStr">
         <is>
-          <t>65歳到達時の引継ぎの時期と担当</t>
+          <t>65歳到達時に確認する事項</t>
         </is>
       </c>
       <c r="C75" s="4" t="inlineStr">
@@ -3446,7 +3446,7 @@
       </c>
       <c r="D75" s="4" t="inlineStr">
         <is>
-          <t>時期 / 行うこと</t>
+          <t>確認する事項 / 確認の内容</t>
         </is>
       </c>
       <c r="E75" s="4" t="inlineStr">
@@ -3463,7 +3463,7 @@
       </c>
       <c r="B76" s="3" t="inlineStr">
         <is>
-          <t>関係機関と連携の内容</t>
+          <t>65歳到達時の引継ぎの時期と担当</t>
         </is>
       </c>
       <c r="C76" s="3" t="inlineStr">
@@ -3473,7 +3473,7 @@
       </c>
       <c r="D76" s="3" t="inlineStr">
         <is>
-          <t>分野 / 関係機関</t>
+          <t>時期 / 行うこと</t>
         </is>
       </c>
       <c r="E76" s="3" t="inlineStr">
@@ -3490,7 +3490,7 @@
       </c>
       <c r="B77" s="4" t="inlineStr">
         <is>
-          <t>障がい福祉サービス等に係る給付費の推移</t>
+          <t>関係機関と連携の内容</t>
         </is>
       </c>
       <c r="C77" s="4" t="inlineStr">
@@ -3500,12 +3500,12 @@
       </c>
       <c r="D77" s="4" t="inlineStr">
         <is>
-          <t>年度 / 介護給付費等</t>
+          <t>分野 / 関係機関</t>
         </is>
       </c>
       <c r="E77" s="4" t="inlineStr">
         <is>
-          <t>資料：村提供の障がいサービス給付実績</t>
+          <t>―</t>
         </is>
       </c>
     </row>
@@ -3517,7 +3517,7 @@
       </c>
       <c r="B78" s="3" t="inlineStr">
         <is>
-          <t>財源構成（令和７年度・法定負担割合による試算）</t>
+          <t>障がい福祉サービス等に係る給付費の推移</t>
         </is>
       </c>
       <c r="C78" s="3" t="inlineStr">
@@ -3527,7 +3527,7 @@
       </c>
       <c r="D78" s="3" t="inlineStr">
         <is>
-          <t>区分 / 金額</t>
+          <t>年度 / 介護給付費等</t>
         </is>
       </c>
       <c r="E78" s="3" t="inlineStr">
@@ -3544,7 +3544,7 @@
       </c>
       <c r="B79" s="4" t="inlineStr">
         <is>
-          <t>サービス別の給付費と計画上の位置づけ（令和７年度）</t>
+          <t>財源構成（令和７年度・法定負担割合による試算）</t>
         </is>
       </c>
       <c r="C79" s="4" t="inlineStr">
@@ -3554,7 +3554,7 @@
       </c>
       <c r="D79" s="4" t="inlineStr">
         <is>
-          <t>サービス / 給付費（構成比）</t>
+          <t>区分 / 金額</t>
         </is>
       </c>
       <c r="E79" s="4" t="inlineStr">
@@ -3566,39 +3566,39 @@
     <row r="80">
       <c r="A80" s="3" t="inlineStr">
         <is>
-          <t>表6-1</t>
+          <t>表5-39</t>
         </is>
       </c>
       <c r="B80" s="3" t="inlineStr">
         <is>
-          <t>高齢化率の推移</t>
+          <t>サービス別の給付費と計画上の位置づけ（令和７年度）</t>
         </is>
       </c>
       <c r="C80" s="3" t="inlineStr">
         <is>
-          <t>第6章</t>
+          <t>第5章</t>
         </is>
       </c>
       <c r="D80" s="3" t="inlineStr">
         <is>
-          <t>年度 / 高齢化率</t>
+          <t>サービス / 給付費（構成比）</t>
         </is>
       </c>
       <c r="E80" s="3" t="inlineStr">
         <is>
-          <t>資料：北塩原村</t>
+          <t>資料：村提供の障がいサービス給付実績</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" s="4" t="inlineStr">
         <is>
-          <t>表6-2</t>
+          <t>表6-1</t>
         </is>
       </c>
       <c r="B81" s="4" t="inlineStr">
         <is>
-          <t>精神障がい者及び知的障がい者の人数の推移</t>
+          <t>高齢化率の推移</t>
         </is>
       </c>
       <c r="C81" s="4" t="inlineStr">
@@ -3608,7 +3608,7 @@
       </c>
       <c r="D81" s="4" t="inlineStr">
         <is>
-          <t>年度 / 精神障がい者数（※１）</t>
+          <t>年度 / 高齢化率</t>
         </is>
       </c>
       <c r="E81" s="4" t="inlineStr">
@@ -3620,12 +3620,12 @@
     <row r="82">
       <c r="A82" s="3" t="inlineStr">
         <is>
-          <t>表6-3</t>
+          <t>表6-2</t>
         </is>
       </c>
       <c r="B82" s="3" t="inlineStr">
         <is>
-          <t>成年後見制度利用支援事業の利用状況</t>
+          <t>精神障がい者及び知的障がい者の人数の推移</t>
         </is>
       </c>
       <c r="C82" s="3" t="inlineStr">
@@ -3635,7 +3635,7 @@
       </c>
       <c r="D82" s="3" t="inlineStr">
         <is>
-          <t>区分 / 令和５年度</t>
+          <t>年度 / 精神障がい者数（※１）</t>
         </is>
       </c>
       <c r="E82" s="3" t="inlineStr">
@@ -3647,12 +3647,12 @@
     <row r="83">
       <c r="A83" s="4" t="inlineStr">
         <is>
-          <t>表6-4</t>
+          <t>表6-3</t>
         </is>
       </c>
       <c r="B83" s="4" t="inlineStr">
         <is>
-          <t>成年後見制度の利用促進に係る指標</t>
+          <t>成年後見制度利用支援事業の利用状況</t>
         </is>
       </c>
       <c r="C83" s="4" t="inlineStr">
@@ -3662,34 +3662,34 @@
       </c>
       <c r="D83" s="4" t="inlineStr">
         <is>
-          <t>指標 / 何を数えるか</t>
+          <t>区分 / 令和５年度</t>
         </is>
       </c>
       <c r="E83" s="4" t="inlineStr">
         <is>
-          <t>―</t>
+          <t>資料：北塩原村</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" s="3" t="inlineStr">
         <is>
-          <t>表7-1</t>
+          <t>表6-4</t>
         </is>
       </c>
       <c r="B84" s="3" t="inlineStr">
         <is>
-          <t>健康21・グッドヘルスプランとの対応</t>
+          <t>成年後見制度の利用促進に係る指標</t>
         </is>
       </c>
       <c r="C84" s="3" t="inlineStr">
         <is>
-          <t>第7章</t>
+          <t>第6章</t>
         </is>
       </c>
       <c r="D84" s="3" t="inlineStr">
         <is>
-          <t>項目 / 健康21・グッドヘルスプラン</t>
+          <t>指標 / 何を数えるか</t>
         </is>
       </c>
       <c r="E84" s="3" t="inlineStr">
@@ -3701,12 +3701,12 @@
     <row r="85">
       <c r="A85" s="4" t="inlineStr">
         <is>
-          <t>表7-2</t>
+          <t>表7-1</t>
         </is>
       </c>
       <c r="B85" s="4" t="inlineStr">
         <is>
-          <t>第五次総合振興計画における本計画の位置づけ</t>
+          <t>健康21・グッドヘルスプランとの対応</t>
         </is>
       </c>
       <c r="C85" s="4" t="inlineStr">
@@ -3716,7 +3716,7 @@
       </c>
       <c r="D85" s="4" t="inlineStr">
         <is>
-          <t>総合振興計画の位置づけ / 内容</t>
+          <t>項目 / 健康21・グッドヘルスプラン</t>
         </is>
       </c>
       <c r="E85" s="4" t="inlineStr">
@@ -3728,12 +3728,12 @@
     <row r="86">
       <c r="A86" s="3" t="inlineStr">
         <is>
-          <t>表7-3</t>
+          <t>表7-2</t>
         </is>
       </c>
       <c r="B86" s="3" t="inlineStr">
         <is>
-          <t>高齢者福祉計画・介護保険事業計画と重ねて数えないための確認事項</t>
+          <t>第五次総合振興計画における本計画の位置づけ</t>
         </is>
       </c>
       <c r="C86" s="3" t="inlineStr">
@@ -3743,7 +3743,7 @@
       </c>
       <c r="D86" s="3" t="inlineStr">
         <is>
-          <t>事項 / 両計画での扱い</t>
+          <t>総合振興計画の位置づけ / 内容</t>
         </is>
       </c>
       <c r="E86" s="3" t="inlineStr">
@@ -3755,12 +3755,12 @@
     <row r="87">
       <c r="A87" s="4" t="inlineStr">
         <is>
-          <t>表7-4</t>
+          <t>表7-3</t>
         </is>
       </c>
       <c r="B87" s="4" t="inlineStr">
         <is>
-          <t>こども・子育て計画との整合を確かめる事項</t>
+          <t>高齢者福祉計画・介護保険事業計画と重ねて数えないための確認事項</t>
         </is>
       </c>
       <c r="C87" s="4" t="inlineStr">
@@ -3770,7 +3770,7 @@
       </c>
       <c r="D87" s="4" t="inlineStr">
         <is>
-          <t>確かめる事項 / 確かめ方</t>
+          <t>事項 / 両計画での扱い</t>
         </is>
       </c>
       <c r="E87" s="4" t="inlineStr">
@@ -3782,22 +3782,22 @@
     <row r="88">
       <c r="A88" s="3" t="inlineStr">
         <is>
-          <t>表8-1</t>
+          <t>表7-4</t>
         </is>
       </c>
       <c r="B88" s="3" t="inlineStr">
         <is>
-          <t>北塩原村障がい者自立支援協議会委員名簿</t>
+          <t>こども・子育て計画との整合を確かめる事項</t>
         </is>
       </c>
       <c r="C88" s="3" t="inlineStr">
         <is>
-          <t>第8章</t>
+          <t>第7章</t>
         </is>
       </c>
       <c r="D88" s="3" t="inlineStr">
         <is>
-          <t>区　分 / 氏　名</t>
+          <t>確かめる事項 / 確かめ方</t>
         </is>
       </c>
       <c r="E88" s="3" t="inlineStr">
@@ -3809,12 +3809,12 @@
     <row r="89">
       <c r="A89" s="4" t="inlineStr">
         <is>
-          <t>表8-2</t>
+          <t>表8-1</t>
         </is>
       </c>
       <c r="B89" s="4" t="inlineStr">
         <is>
-          <t>計画の策定経過</t>
+          <t>北塩原村障がい者自立支援協議会委員名簿</t>
         </is>
       </c>
       <c r="C89" s="4" t="inlineStr">
@@ -3824,7 +3824,7 @@
       </c>
       <c r="D89" s="4" t="inlineStr">
         <is>
-          <t>年月日 / 内容</t>
+          <t>区　分 / 氏　名</t>
         </is>
       </c>
       <c r="E89" s="4" t="inlineStr">
@@ -3836,12 +3836,12 @@
     <row r="90">
       <c r="A90" s="3" t="inlineStr">
         <is>
-          <t>表8-3</t>
+          <t>表8-2</t>
         </is>
       </c>
       <c r="B90" s="3" t="inlineStr">
         <is>
-          <t>近年の障がい者施策の動向</t>
+          <t>計画の策定経過</t>
         </is>
       </c>
       <c r="C90" s="3" t="inlineStr">
@@ -3851,7 +3851,7 @@
       </c>
       <c r="D90" s="3" t="inlineStr">
         <is>
-          <t>年 / 主な動向</t>
+          <t>年月日 / 内容</t>
         </is>
       </c>
       <c r="E90" s="3" t="inlineStr">
@@ -3863,25 +3863,52 @@
     <row r="91">
       <c r="A91" s="4" t="inlineStr">
         <is>
+          <t>表8-3</t>
+        </is>
+      </c>
+      <c r="B91" s="4" t="inlineStr">
+        <is>
+          <t>近年の障がい者施策の動向</t>
+        </is>
+      </c>
+      <c r="C91" s="4" t="inlineStr">
+        <is>
+          <t>第8章</t>
+        </is>
+      </c>
+      <c r="D91" s="4" t="inlineStr">
+        <is>
+          <t>年 / 主な動向</t>
+        </is>
+      </c>
+      <c r="E91" s="4" t="inlineStr">
+        <is>
+          <t>―</t>
+        </is>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" s="3" t="inlineStr">
+        <is>
           <t>表8-4</t>
         </is>
       </c>
-      <c r="B91" s="4" t="inlineStr">
+      <c r="B92" s="3" t="inlineStr">
         <is>
           <t>用語解説</t>
         </is>
       </c>
-      <c r="C91" s="4" t="inlineStr">
+      <c r="C92" s="3" t="inlineStr">
         <is>
           <t>第8章</t>
         </is>
       </c>
-      <c r="D91" s="4" t="inlineStr">
+      <c r="D92" s="3" t="inlineStr">
         <is>
           <t>用語 / 説明</t>
         </is>
       </c>
-      <c r="E91" s="4" t="inlineStr">
+      <c r="E92" s="3" t="inlineStr">
         <is>
           <t>―</t>
         </is>

--- a/output/北塩原村_図表番号一覧.xlsx
+++ b/output/北塩原村_図表番号一覧.xlsx
@@ -535,7 +535,7 @@
       </c>
       <c r="B6" s="3" t="inlineStr">
         <is>
-          <t>図25点・表87点に章ごとの通し番号を振った（図１-１・表１-１の形）。注記ボックス（【村へ確認】等の1×1の枠）45点には振っていない。確定時に削るため、番号を振ると欠番が出るからである。</t>
+          <t>図25点・表88点に章ごとの通し番号を振った（図１-１・表１-１の形）。注記ボックス（【村へ確認】等の1×1の枠）45点には振っていない。確定時に削るため、番号を振ると欠番が出るからである。</t>
         </is>
       </c>
     </row>
@@ -1510,7 +1510,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E92"/>
+  <dimension ref="A1:E93"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -1523,7 +1523,7 @@
     <row r="1" ht="30" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>表 87点</t>
+          <t>表 88点</t>
         </is>
       </c>
     </row>
@@ -2053,39 +2053,39 @@
     <row r="24">
       <c r="A24" s="3" t="inlineStr">
         <is>
-          <t>表3-1</t>
+          <t>表2-9</t>
         </is>
       </c>
       <c r="B24" s="3" t="inlineStr">
         <is>
-          <t>第４次北塩原村障がい者計画の基本施策ごとの目標値</t>
+          <t>アンケート調査の用い方</t>
         </is>
       </c>
       <c r="C24" s="3" t="inlineStr">
         <is>
-          <t>第3章</t>
+          <t>第2章</t>
         </is>
       </c>
       <c r="D24" s="3" t="inlineStr">
         <is>
-          <t>基本施策 / 指標項目</t>
+          <t>用いること / 本村での例</t>
         </is>
       </c>
       <c r="E24" s="3" t="inlineStr">
         <is>
-          <t>資料：第４次北塩原村障がい者計画及び本計画により作成</t>
+          <t>―</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="4" t="inlineStr">
         <is>
-          <t>表3-2</t>
+          <t>表3-1</t>
         </is>
       </c>
       <c r="B25" s="4" t="inlineStr">
         <is>
-          <t>実績がない場合の評価の六つの区分</t>
+          <t>第４次北塩原村障がい者計画の基本施策ごとの目標値</t>
         </is>
       </c>
       <c r="C25" s="4" t="inlineStr">
@@ -2095,51 +2095,51 @@
       </c>
       <c r="D25" s="4" t="inlineStr">
         <is>
-          <t>区分 / 意味</t>
+          <t>基本施策 / 指標項目</t>
         </is>
       </c>
       <c r="E25" s="4" t="inlineStr">
         <is>
-          <t>―</t>
+          <t>資料：第４次北塩原村障がい者計画及び本計画により作成</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="3" t="inlineStr">
         <is>
-          <t>表4-1</t>
+          <t>表3-2</t>
         </is>
       </c>
       <c r="B26" s="3" t="inlineStr">
         <is>
-          <t>第７期計画の成果目標の達成状況</t>
+          <t>実績がない場合の評価の六つの区分</t>
         </is>
       </c>
       <c r="C26" s="3" t="inlineStr">
         <is>
-          <t>第4章</t>
+          <t>第3章</t>
         </is>
       </c>
       <c r="D26" s="3" t="inlineStr">
         <is>
-          <t>成果目標 / 項目</t>
+          <t>区分 / 意味</t>
         </is>
       </c>
       <c r="E26" s="3" t="inlineStr">
         <is>
-          <t>資料：北塩原村</t>
+          <t>―</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="4" t="inlineStr">
         <is>
-          <t>表4-2</t>
+          <t>表4-1</t>
         </is>
       </c>
       <c r="B27" s="4" t="inlineStr">
         <is>
-          <t>施設入所者の地域生活への移行の目標</t>
+          <t>第７期計画の成果目標の達成状況</t>
         </is>
       </c>
       <c r="C27" s="4" t="inlineStr">
@@ -2149,24 +2149,24 @@
       </c>
       <c r="D27" s="4" t="inlineStr">
         <is>
-          <t>項目 / 数値</t>
+          <t>成果目標 / 項目</t>
         </is>
       </c>
       <c r="E27" s="4" t="inlineStr">
         <is>
-          <t>―</t>
+          <t>資料：北塩原村</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="3" t="inlineStr">
         <is>
-          <t>表4-3</t>
+          <t>表4-2</t>
         </is>
       </c>
       <c r="B28" s="3" t="inlineStr">
         <is>
-          <t>地域移行の可能性を確かめる事項</t>
+          <t>施設入所者の地域生活への移行の目標</t>
         </is>
       </c>
       <c r="C28" s="3" t="inlineStr">
@@ -2176,7 +2176,7 @@
       </c>
       <c r="D28" s="3" t="inlineStr">
         <is>
-          <t>確認する事項 / 確認の方法</t>
+          <t>項目 / 数値</t>
         </is>
       </c>
       <c r="E28" s="3" t="inlineStr">
@@ -2188,12 +2188,12 @@
     <row r="29">
       <c r="A29" s="4" t="inlineStr">
         <is>
-          <t>表4-4</t>
+          <t>表4-3</t>
         </is>
       </c>
       <c r="B29" s="4" t="inlineStr">
         <is>
-          <t>精神障害にも対応した地域包括ケアシステムの構築の目標</t>
+          <t>地域移行の可能性を確かめる事項</t>
         </is>
       </c>
       <c r="C29" s="4" t="inlineStr">
@@ -2203,7 +2203,7 @@
       </c>
       <c r="D29" s="4" t="inlineStr">
         <is>
-          <t>項目 / 数値</t>
+          <t>確認する事項 / 確認の方法</t>
         </is>
       </c>
       <c r="E29" s="4" t="inlineStr">
@@ -2215,12 +2215,12 @@
     <row r="30">
       <c r="A30" s="3" t="inlineStr">
         <is>
-          <t>表4-5</t>
+          <t>表4-4</t>
         </is>
       </c>
       <c r="B30" s="3" t="inlineStr">
         <is>
-          <t>精神障がい者のサービス利用の見込み（活動指標）</t>
+          <t>精神障害にも対応した地域包括ケアシステムの構築の目標</t>
         </is>
       </c>
       <c r="C30" s="3" t="inlineStr">
@@ -2230,7 +2230,7 @@
       </c>
       <c r="D30" s="3" t="inlineStr">
         <is>
-          <t>サービス種別 / 単位</t>
+          <t>項目 / 数値</t>
         </is>
       </c>
       <c r="E30" s="3" t="inlineStr">
@@ -2242,12 +2242,12 @@
     <row r="31">
       <c r="A31" s="4" t="inlineStr">
         <is>
-          <t>表4-6</t>
+          <t>表4-5</t>
         </is>
       </c>
       <c r="B31" s="4" t="inlineStr">
         <is>
-          <t>精神病床からの退院に関する県の算定との関係</t>
+          <t>精神障がい者のサービス利用の見込み（活動指標）</t>
         </is>
       </c>
       <c r="C31" s="4" t="inlineStr">
@@ -2257,7 +2257,7 @@
       </c>
       <c r="D31" s="4" t="inlineStr">
         <is>
-          <t>項目 / 値</t>
+          <t>サービス種別 / 単位</t>
         </is>
       </c>
       <c r="E31" s="4" t="inlineStr">
@@ -2269,12 +2269,12 @@
     <row r="32">
       <c r="A32" s="3" t="inlineStr">
         <is>
-          <t>表4-7</t>
+          <t>表4-6</t>
         </is>
       </c>
       <c r="B32" s="3" t="inlineStr">
         <is>
-          <t>福祉施設から一般就労への移行等の目標</t>
+          <t>精神病床からの退院に関する県の算定との関係</t>
         </is>
       </c>
       <c r="C32" s="3" t="inlineStr">
@@ -2284,7 +2284,7 @@
       </c>
       <c r="D32" s="3" t="inlineStr">
         <is>
-          <t>項目 / 数値</t>
+          <t>項目 / 値</t>
         </is>
       </c>
       <c r="E32" s="3" t="inlineStr">
@@ -2296,12 +2296,12 @@
     <row r="33">
       <c r="A33" s="4" t="inlineStr">
         <is>
-          <t>表4-8</t>
+          <t>表4-7</t>
         </is>
       </c>
       <c r="B33" s="4" t="inlineStr">
         <is>
-          <t>就労移行支援等から一般就労への移行者数の目標</t>
+          <t>福祉施設から一般就労への移行等の目標</t>
         </is>
       </c>
       <c r="C33" s="4" t="inlineStr">
@@ -2311,7 +2311,7 @@
       </c>
       <c r="D33" s="4" t="inlineStr">
         <is>
-          <t>事業種別 / 令和６年度実績</t>
+          <t>項目 / 数値</t>
         </is>
       </c>
       <c r="E33" s="4" t="inlineStr">
@@ -2323,52 +2323,52 @@
     <row r="34">
       <c r="A34" s="3" t="inlineStr">
         <is>
+          <t>表4-8</t>
+        </is>
+      </c>
+      <c r="B34" s="3" t="inlineStr">
+        <is>
+          <t>就労移行支援等から一般就労への移行者数の目標</t>
+        </is>
+      </c>
+      <c r="C34" s="3" t="inlineStr">
+        <is>
+          <t>第4章</t>
+        </is>
+      </c>
+      <c r="D34" s="3" t="inlineStr">
+        <is>
+          <t>事業種別 / 令和６年度実績</t>
+        </is>
+      </c>
+      <c r="E34" s="3" t="inlineStr">
+        <is>
+          <t>―</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="4" t="inlineStr">
+        <is>
           <t>表4-9</t>
         </is>
       </c>
-      <c r="B34" s="3" t="inlineStr">
+      <c r="B35" s="4" t="inlineStr">
         <is>
           <t>障がい児支援の提供体制の整備等の目標</t>
         </is>
       </c>
-      <c r="C34" s="3" t="inlineStr">
+      <c r="C35" s="4" t="inlineStr">
         <is>
           <t>第4章</t>
         </is>
       </c>
-      <c r="D34" s="3" t="inlineStr">
+      <c r="D35" s="4" t="inlineStr">
         <is>
           <t>項目 / 現状
 （令和８年度見込み）</t>
         </is>
       </c>
-      <c r="E34" s="3" t="inlineStr">
-        <is>
-          <t>―</t>
-        </is>
-      </c>
-    </row>
-    <row r="35">
-      <c r="A35" s="4" t="inlineStr">
-        <is>
-          <t>表4-10</t>
-        </is>
-      </c>
-      <c r="B35" s="4" t="inlineStr">
-        <is>
-          <t>早期発見から支援につながる経路の記録</t>
-        </is>
-      </c>
-      <c r="C35" s="4" t="inlineStr">
-        <is>
-          <t>第4章</t>
-        </is>
-      </c>
-      <c r="D35" s="4" t="inlineStr">
-        <is>
-          <t>記録する事項 / ねらい</t>
-        </is>
-      </c>
       <c r="E35" s="4" t="inlineStr">
         <is>
           <t>―</t>
@@ -2378,12 +2378,12 @@
     <row r="36">
       <c r="A36" s="3" t="inlineStr">
         <is>
-          <t>表4-11</t>
+          <t>表4-10</t>
         </is>
       </c>
       <c r="B36" s="3" t="inlineStr">
         <is>
-          <t>地域生活支援の充実の目標</t>
+          <t>早期発見から支援につながる経路の記録</t>
         </is>
       </c>
       <c r="C36" s="3" t="inlineStr">
@@ -2393,7 +2393,7 @@
       </c>
       <c r="D36" s="3" t="inlineStr">
         <is>
-          <t>項目 / 数値</t>
+          <t>記録する事項 / ねらい</t>
         </is>
       </c>
       <c r="E36" s="3" t="inlineStr">
@@ -2405,12 +2405,12 @@
     <row r="37">
       <c r="A37" s="4" t="inlineStr">
         <is>
-          <t>表4-12</t>
+          <t>表4-11</t>
         </is>
       </c>
       <c r="B37" s="4" t="inlineStr">
         <is>
-          <t>地域生活支援拠点等の５つの機能と記録する実績</t>
+          <t>地域生活支援の充実の目標</t>
         </is>
       </c>
       <c r="C37" s="4" t="inlineStr">
@@ -2420,7 +2420,7 @@
       </c>
       <c r="D37" s="4" t="inlineStr">
         <is>
-          <t>機能 / 本村での確保の方法</t>
+          <t>項目 / 数値</t>
         </is>
       </c>
       <c r="E37" s="4" t="inlineStr">
@@ -2432,12 +2432,12 @@
     <row r="38">
       <c r="A38" s="3" t="inlineStr">
         <is>
-          <t>表4-13</t>
+          <t>表4-12</t>
         </is>
       </c>
       <c r="B38" s="3" t="inlineStr">
         <is>
-          <t>相談支援体制の充実・強化等の目標</t>
+          <t>地域生活支援拠点等の５つの機能と記録する実績</t>
         </is>
       </c>
       <c r="C38" s="3" t="inlineStr">
@@ -2447,7 +2447,7 @@
       </c>
       <c r="D38" s="3" t="inlineStr">
         <is>
-          <t>項目 / 数値</t>
+          <t>機能 / 本村での確保の方法</t>
         </is>
       </c>
       <c r="E38" s="3" t="inlineStr">
@@ -2459,12 +2459,12 @@
     <row r="39">
       <c r="A39" s="4" t="inlineStr">
         <is>
-          <t>表4-14</t>
+          <t>表4-13</t>
         </is>
       </c>
       <c r="B39" s="4" t="inlineStr">
         <is>
-          <t>障害福祉人材の確保・定着等の目標</t>
+          <t>相談支援体制の充実・強化等の目標</t>
         </is>
       </c>
       <c r="C39" s="4" t="inlineStr">
@@ -2486,12 +2486,12 @@
     <row r="40">
       <c r="A40" s="3" t="inlineStr">
         <is>
-          <t>表4-15</t>
+          <t>表4-14</t>
         </is>
       </c>
       <c r="B40" s="3" t="inlineStr">
         <is>
-          <t>障害福祉サービス等の質を向上させる体制の構築の目標</t>
+          <t>障害福祉人材の確保・定着等の目標</t>
         </is>
       </c>
       <c r="C40" s="3" t="inlineStr">
@@ -2513,12 +2513,12 @@
     <row r="41">
       <c r="A41" s="4" t="inlineStr">
         <is>
-          <t>表4-16</t>
+          <t>表4-15</t>
         </is>
       </c>
       <c r="B41" s="4" t="inlineStr">
         <is>
-          <t>発達障がい者等に対する支援の活動指標</t>
+          <t>障害福祉サービス等の質を向上させる体制の構築の目標</t>
         </is>
       </c>
       <c r="C41" s="4" t="inlineStr">
@@ -2528,7 +2528,7 @@
       </c>
       <c r="D41" s="4" t="inlineStr">
         <is>
-          <t>活動指標 / 令和９年度</t>
+          <t>項目 / 数値</t>
         </is>
       </c>
       <c r="E41" s="4" t="inlineStr">
@@ -2540,22 +2540,22 @@
     <row r="42">
       <c r="A42" s="3" t="inlineStr">
         <is>
-          <t>表5-1</t>
+          <t>表4-16</t>
         </is>
       </c>
       <c r="B42" s="3" t="inlineStr">
         <is>
-          <t>障がい福祉サービス等の体系（参考）</t>
+          <t>発達障がい者等に対する支援の活動指標</t>
         </is>
       </c>
       <c r="C42" s="3" t="inlineStr">
         <is>
-          <t>第5章</t>
+          <t>第4章</t>
         </is>
       </c>
       <c r="D42" s="3" t="inlineStr">
         <is>
-          <t>区分 / 主なサービス・事業</t>
+          <t>活動指標 / 令和９年度</t>
         </is>
       </c>
       <c r="E42" s="3" t="inlineStr">
@@ -2567,12 +2567,12 @@
     <row r="43">
       <c r="A43" s="4" t="inlineStr">
         <is>
-          <t>表5-2</t>
+          <t>表5-1</t>
         </is>
       </c>
       <c r="B43" s="4" t="inlineStr">
         <is>
-          <t>見込量を定めるまでの段階</t>
+          <t>障がい福祉サービス等の体系（参考）</t>
         </is>
       </c>
       <c r="C43" s="4" t="inlineStr">
@@ -2582,7 +2582,7 @@
       </c>
       <c r="D43" s="4" t="inlineStr">
         <is>
-          <t>段階 / 何を見るか</t>
+          <t>区分 / 主なサービス・事業</t>
         </is>
       </c>
       <c r="E43" s="4" t="inlineStr">
@@ -2594,12 +2594,12 @@
     <row r="44">
       <c r="A44" s="3" t="inlineStr">
         <is>
-          <t>表5-3</t>
+          <t>表5-2</t>
         </is>
       </c>
       <c r="B44" s="3" t="inlineStr">
         <is>
-          <t>必要な利用者数の組み立て</t>
+          <t>見込量を定めるまでの段階</t>
         </is>
       </c>
       <c r="C44" s="3" t="inlineStr">
@@ -2609,7 +2609,7 @@
       </c>
       <c r="D44" s="3" t="inlineStr">
         <is>
-          <t>加減 / 項目</t>
+          <t>段階 / 何を見るか</t>
         </is>
       </c>
       <c r="E44" s="3" t="inlineStr">
@@ -2621,12 +2621,12 @@
     <row r="45">
       <c r="A45" s="4" t="inlineStr">
         <is>
-          <t>表5-4</t>
+          <t>表5-3</t>
         </is>
       </c>
       <c r="B45" s="4" t="inlineStr">
         <is>
-          <t>訪問系サービスの実績</t>
+          <t>必要な利用者数の組み立て</t>
         </is>
       </c>
       <c r="C45" s="4" t="inlineStr">
@@ -2636,24 +2636,24 @@
       </c>
       <c r="D45" s="4" t="inlineStr">
         <is>
-          <t>サービス種別 / 単位</t>
+          <t>加減 / 項目</t>
         </is>
       </c>
       <c r="E45" s="4" t="inlineStr">
         <is>
-          <t>資料：北塩原村</t>
+          <t>―</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="3" t="inlineStr">
         <is>
-          <t>表5-5</t>
+          <t>表5-4</t>
         </is>
       </c>
       <c r="B46" s="3" t="inlineStr">
         <is>
-          <t>訪問系サービスの見込量</t>
+          <t>訪問系サービスの実績</t>
         </is>
       </c>
       <c r="C46" s="3" t="inlineStr">
@@ -2668,19 +2668,19 @@
       </c>
       <c r="E46" s="3" t="inlineStr">
         <is>
-          <t>―</t>
+          <t>資料：北塩原村</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="4" t="inlineStr">
         <is>
-          <t>表5-6</t>
+          <t>表5-5</t>
         </is>
       </c>
       <c r="B47" s="4" t="inlineStr">
         <is>
-          <t>訪問系サービスの利用がない場合に確かめる事項</t>
+          <t>訪問系サービスの見込量</t>
         </is>
       </c>
       <c r="C47" s="4" t="inlineStr">
@@ -2690,7 +2690,7 @@
       </c>
       <c r="D47" s="4" t="inlineStr">
         <is>
-          <t>確かめる側 / 確かめる事項</t>
+          <t>サービス種別 / 単位</t>
         </is>
       </c>
       <c r="E47" s="4" t="inlineStr">
@@ -2702,12 +2702,12 @@
     <row r="48">
       <c r="A48" s="3" t="inlineStr">
         <is>
-          <t>表5-7</t>
+          <t>表5-6</t>
         </is>
       </c>
       <c r="B48" s="3" t="inlineStr">
         <is>
-          <t>日中活動系サービスの実績</t>
+          <t>訪問系サービスの利用がない場合に確かめる事項</t>
         </is>
       </c>
       <c r="C48" s="3" t="inlineStr">
@@ -2717,24 +2717,24 @@
       </c>
       <c r="D48" s="3" t="inlineStr">
         <is>
-          <t>サービス種別 / 単位</t>
+          <t>確かめる側 / 確かめる事項</t>
         </is>
       </c>
       <c r="E48" s="3" t="inlineStr">
         <is>
-          <t>資料：北塩原村</t>
+          <t>―</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="4" t="inlineStr">
         <is>
-          <t>表5-8</t>
+          <t>表5-7</t>
         </is>
       </c>
       <c r="B49" s="4" t="inlineStr">
         <is>
-          <t>日中活動系サービスの見込量</t>
+          <t>日中活動系サービスの実績</t>
         </is>
       </c>
       <c r="C49" s="4" t="inlineStr">
@@ -2749,19 +2749,19 @@
       </c>
       <c r="E49" s="4" t="inlineStr">
         <is>
-          <t>―</t>
+          <t>資料：北塩原村</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="3" t="inlineStr">
         <is>
-          <t>表5-9</t>
+          <t>表5-8</t>
         </is>
       </c>
       <c r="B50" s="3" t="inlineStr">
         <is>
-          <t>強度行動障害を有する方等の生活介護の利用の見込み</t>
+          <t>日中活動系サービスの見込量</t>
         </is>
       </c>
       <c r="C50" s="3" t="inlineStr">
@@ -2771,7 +2771,7 @@
       </c>
       <c r="D50" s="3" t="inlineStr">
         <is>
-          <t>区分 / 現在の人数</t>
+          <t>サービス種別 / 単位</t>
         </is>
       </c>
       <c r="E50" s="3" t="inlineStr">
@@ -2783,12 +2783,12 @@
     <row r="51">
       <c r="A51" s="4" t="inlineStr">
         <is>
-          <t>表5-10</t>
+          <t>表5-9</t>
         </is>
       </c>
       <c r="B51" s="4" t="inlineStr">
         <is>
-          <t>居住系サービスの実績</t>
+          <t>強度行動障害を有する方等の生活介護の利用の見込み</t>
         </is>
       </c>
       <c r="C51" s="4" t="inlineStr">
@@ -2798,24 +2798,24 @@
       </c>
       <c r="D51" s="4" t="inlineStr">
         <is>
-          <t>サービス種別 / 単位</t>
+          <t>区分 / 現在の人数</t>
         </is>
       </c>
       <c r="E51" s="4" t="inlineStr">
         <is>
-          <t>資料：北塩原村</t>
+          <t>―</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="3" t="inlineStr">
         <is>
-          <t>表5-11</t>
+          <t>表5-10</t>
         </is>
       </c>
       <c r="B52" s="3" t="inlineStr">
         <is>
-          <t>居住系サービスの見込量</t>
+          <t>居住系サービスの実績</t>
         </is>
       </c>
       <c r="C52" s="3" t="inlineStr">
@@ -2830,19 +2830,19 @@
       </c>
       <c r="E52" s="3" t="inlineStr">
         <is>
-          <t>―</t>
+          <t>資料：北塩原村</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="4" t="inlineStr">
         <is>
-          <t>表5-12</t>
+          <t>表5-11</t>
         </is>
       </c>
       <c r="B53" s="4" t="inlineStr">
         <is>
-          <t>相談支援の実績</t>
+          <t>居住系サービスの見込量</t>
         </is>
       </c>
       <c r="C53" s="4" t="inlineStr">
@@ -2857,19 +2857,19 @@
       </c>
       <c r="E53" s="4" t="inlineStr">
         <is>
-          <t>資料：北塩原村</t>
+          <t>―</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" s="3" t="inlineStr">
         <is>
-          <t>表5-13</t>
+          <t>表5-12</t>
         </is>
       </c>
       <c r="B54" s="3" t="inlineStr">
         <is>
-          <t>相談支援の見込量</t>
+          <t>相談支援の実績</t>
         </is>
       </c>
       <c r="C54" s="3" t="inlineStr">
@@ -2884,19 +2884,19 @@
       </c>
       <c r="E54" s="3" t="inlineStr">
         <is>
-          <t>―</t>
+          <t>資料：北塩原村</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" s="4" t="inlineStr">
         <is>
-          <t>表5-14</t>
+          <t>表5-13</t>
         </is>
       </c>
       <c r="B55" s="4" t="inlineStr">
         <is>
-          <t>障がい児支援の実績</t>
+          <t>相談支援の見込量</t>
         </is>
       </c>
       <c r="C55" s="4" t="inlineStr">
@@ -2911,19 +2911,19 @@
       </c>
       <c r="E55" s="4" t="inlineStr">
         <is>
-          <t>資料：北塩原村</t>
+          <t>―</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" s="3" t="inlineStr">
         <is>
-          <t>表5-15</t>
+          <t>表5-14</t>
         </is>
       </c>
       <c r="B56" s="3" t="inlineStr">
         <is>
-          <t>障がい児支援の見込量</t>
+          <t>障がい児支援の実績</t>
         </is>
       </c>
       <c r="C56" s="3" t="inlineStr">
@@ -2938,19 +2938,19 @@
       </c>
       <c r="E56" s="3" t="inlineStr">
         <is>
-          <t>―</t>
+          <t>資料：北塩原村</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" s="4" t="inlineStr">
         <is>
-          <t>表5-16</t>
+          <t>表5-15</t>
         </is>
       </c>
       <c r="B57" s="4" t="inlineStr">
         <is>
-          <t>一般の子育て施策と障がい福祉の切り分け</t>
+          <t>障がい児支援の見込量</t>
         </is>
       </c>
       <c r="C57" s="4" t="inlineStr">
@@ -2960,7 +2960,7 @@
       </c>
       <c r="D57" s="4" t="inlineStr">
         <is>
-          <t>場面 / まず確かめる一般の子育て施策</t>
+          <t>サービス種別 / 単位</t>
         </is>
       </c>
       <c r="E57" s="4" t="inlineStr">
@@ -2972,12 +2972,12 @@
     <row r="58">
       <c r="A58" s="3" t="inlineStr">
         <is>
-          <t>表5-17</t>
+          <t>表5-16</t>
         </is>
       </c>
       <c r="B58" s="3" t="inlineStr">
         <is>
-          <t>事業所の受入余力について照会する事項</t>
+          <t>一般の子育て施策と障がい福祉の切り分け</t>
         </is>
       </c>
       <c r="C58" s="3" t="inlineStr">
@@ -2987,7 +2987,7 @@
       </c>
       <c r="D58" s="3" t="inlineStr">
         <is>
-          <t>照会する事項 / 確保できる量との関係</t>
+          <t>場面 / まず確かめる一般の子育て施策</t>
         </is>
       </c>
       <c r="E58" s="3" t="inlineStr">
@@ -2999,12 +2999,12 @@
     <row r="59">
       <c r="A59" s="4" t="inlineStr">
         <is>
-          <t>表5-18</t>
+          <t>表5-17</t>
         </is>
       </c>
       <c r="B59" s="4" t="inlineStr">
         <is>
-          <t>緊急時に働く仕組み（４つの場面）</t>
+          <t>事業所の受入余力について照会する事項</t>
         </is>
       </c>
       <c r="C59" s="4" t="inlineStr">
@@ -3014,7 +3014,7 @@
       </c>
       <c r="D59" s="4" t="inlineStr">
         <is>
-          <t>場面 / 想定される事態</t>
+          <t>照会する事項 / 確保できる量との関係</t>
         </is>
       </c>
       <c r="E59" s="4" t="inlineStr">
@@ -3026,12 +3026,12 @@
     <row r="60">
       <c r="A60" s="3" t="inlineStr">
         <is>
-          <t>表5-19</t>
+          <t>表5-18</t>
         </is>
       </c>
       <c r="B60" s="3" t="inlineStr">
         <is>
-          <t>災害時にサービスを止めないための備え</t>
+          <t>緊急時に働く仕組み（４つの場面）</t>
         </is>
       </c>
       <c r="C60" s="3" t="inlineStr">
@@ -3041,7 +3041,7 @@
       </c>
       <c r="D60" s="3" t="inlineStr">
         <is>
-          <t>備える事項 / 本村の取組み</t>
+          <t>場面 / 想定される事態</t>
         </is>
       </c>
       <c r="E60" s="3" t="inlineStr">
@@ -3053,12 +3053,12 @@
     <row r="61">
       <c r="A61" s="4" t="inlineStr">
         <is>
-          <t>表5-20</t>
+          <t>表5-19</t>
         </is>
       </c>
       <c r="B61" s="4" t="inlineStr">
         <is>
-          <t>災害時の情報の伝達について確かめること</t>
+          <t>災害時にサービスを止めないための備え</t>
         </is>
       </c>
       <c r="C61" s="4" t="inlineStr">
@@ -3068,7 +3068,7 @@
       </c>
       <c r="D61" s="4" t="inlineStr">
         <is>
-          <t>確かめること / 確かめ方</t>
+          <t>備える事項 / 本村の取組み</t>
         </is>
       </c>
       <c r="E61" s="4" t="inlineStr">
@@ -3080,12 +3080,12 @@
     <row r="62">
       <c r="A62" s="3" t="inlineStr">
         <is>
-          <t>表5-21</t>
+          <t>表5-20</t>
         </is>
       </c>
       <c r="B62" s="3" t="inlineStr">
         <is>
-          <t>虐待の予防から再発の防止までの流れ</t>
+          <t>災害時の情報の伝達について確かめること</t>
         </is>
       </c>
       <c r="C62" s="3" t="inlineStr">
@@ -3095,7 +3095,7 @@
       </c>
       <c r="D62" s="3" t="inlineStr">
         <is>
-          <t>段階 / 本村の取組み</t>
+          <t>確かめること / 確かめ方</t>
         </is>
       </c>
       <c r="E62" s="3" t="inlineStr">
@@ -3107,12 +3107,12 @@
     <row r="63">
       <c r="A63" s="4" t="inlineStr">
         <is>
-          <t>表5-22</t>
+          <t>表5-21</t>
         </is>
       </c>
       <c r="B63" s="4" t="inlineStr">
         <is>
-          <t>経営基盤に関して把握する事項</t>
+          <t>虐待の予防から再発の防止までの流れ</t>
         </is>
       </c>
       <c r="C63" s="4" t="inlineStr">
@@ -3122,7 +3122,7 @@
       </c>
       <c r="D63" s="4" t="inlineStr">
         <is>
-          <t>把握する事項 / 見込量への影響</t>
+          <t>段階 / 本村の取組み</t>
         </is>
       </c>
       <c r="E63" s="4" t="inlineStr">
@@ -3134,12 +3134,12 @@
     <row r="64">
       <c r="A64" s="3" t="inlineStr">
         <is>
-          <t>表5-23</t>
+          <t>表5-22</t>
         </is>
       </c>
       <c r="B64" s="3" t="inlineStr">
         <is>
-          <t>冬季の支援を検討する三つの段階</t>
+          <t>経営基盤に関して把握する事項</t>
         </is>
       </c>
       <c r="C64" s="3" t="inlineStr">
@@ -3149,7 +3149,7 @@
       </c>
       <c r="D64" s="3" t="inlineStr">
         <is>
-          <t>段階 / 確かめること</t>
+          <t>把握する事項 / 見込量への影響</t>
         </is>
       </c>
       <c r="E64" s="3" t="inlineStr">
@@ -3161,12 +3161,12 @@
     <row r="65">
       <c r="A65" s="4" t="inlineStr">
         <is>
-          <t>表5-24</t>
+          <t>表5-23</t>
         </is>
       </c>
       <c r="B65" s="4" t="inlineStr">
         <is>
-          <t>冬季の通行規制による中断について記録する事項</t>
+          <t>冬季の支援を検討する三つの段階</t>
         </is>
       </c>
       <c r="C65" s="4" t="inlineStr">
@@ -3176,7 +3176,7 @@
       </c>
       <c r="D65" s="4" t="inlineStr">
         <is>
-          <t>記録する事項 / 記録の仕方</t>
+          <t>段階 / 確かめること</t>
         </is>
       </c>
       <c r="E65" s="4" t="inlineStr">
@@ -3188,12 +3188,12 @@
     <row r="66">
       <c r="A66" s="3" t="inlineStr">
         <is>
-          <t>表5-25</t>
+          <t>表5-24</t>
         </is>
       </c>
       <c r="B66" s="3" t="inlineStr">
         <is>
-          <t>医療へのアクセス</t>
+          <t>冬季の通行規制による中断について記録する事項</t>
         </is>
       </c>
       <c r="C66" s="3" t="inlineStr">
@@ -3203,7 +3203,7 @@
       </c>
       <c r="D66" s="3" t="inlineStr">
         <is>
-          <t>場面 / 主な医療資源</t>
+          <t>記録する事項 / 記録の仕方</t>
         </is>
       </c>
       <c r="E66" s="3" t="inlineStr">
@@ -3215,12 +3215,12 @@
     <row r="67">
       <c r="A67" s="4" t="inlineStr">
         <is>
-          <t>表5-26</t>
+          <t>表5-25</t>
         </is>
       </c>
       <c r="B67" s="4" t="inlineStr">
         <is>
-          <t>地域生活支援事業の実績</t>
+          <t>医療へのアクセス</t>
         </is>
       </c>
       <c r="C67" s="4" t="inlineStr">
@@ -3230,24 +3230,24 @@
       </c>
       <c r="D67" s="4" t="inlineStr">
         <is>
-          <t>サービスの種類 / 令和６年度</t>
+          <t>場面 / 主な医療資源</t>
         </is>
       </c>
       <c r="E67" s="4" t="inlineStr">
         <is>
-          <t>資料：北塩原村</t>
+          <t>―</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" s="3" t="inlineStr">
         <is>
-          <t>表5-27</t>
+          <t>表5-26</t>
         </is>
       </c>
       <c r="B68" s="3" t="inlineStr">
         <is>
-          <t>地域生活支援事業の見込量</t>
+          <t>地域生活支援事業の実績</t>
         </is>
       </c>
       <c r="C68" s="3" t="inlineStr">
@@ -3257,24 +3257,24 @@
       </c>
       <c r="D68" s="3" t="inlineStr">
         <is>
-          <t>サービスの種類 / 令和９年度</t>
+          <t>サービスの種類 / 令和６年度</t>
         </is>
       </c>
       <c r="E68" s="3" t="inlineStr">
         <is>
-          <t>―</t>
+          <t>資料：北塩原村</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" s="4" t="inlineStr">
         <is>
-          <t>表5-28</t>
+          <t>表5-27</t>
         </is>
       </c>
       <c r="B69" s="4" t="inlineStr">
         <is>
-          <t>実績がない事業の扱い</t>
+          <t>地域生活支援事業の見込量</t>
         </is>
       </c>
       <c r="C69" s="4" t="inlineStr">
@@ -3284,7 +3284,7 @@
       </c>
       <c r="D69" s="4" t="inlineStr">
         <is>
-          <t>実績がない理由 / 確かめ方</t>
+          <t>サービスの種類 / 令和９年度</t>
         </is>
       </c>
       <c r="E69" s="4" t="inlineStr">
@@ -3296,12 +3296,12 @@
     <row r="70">
       <c r="A70" s="3" t="inlineStr">
         <is>
-          <t>表5-29</t>
+          <t>表5-28</t>
         </is>
       </c>
       <c r="B70" s="3" t="inlineStr">
         <is>
-          <t>地域生活支援事業の実施に必要な事項</t>
+          <t>実績がない事業の扱い</t>
         </is>
       </c>
       <c r="C70" s="3" t="inlineStr">
@@ -3311,7 +3311,7 @@
       </c>
       <c r="D70" s="3" t="inlineStr">
         <is>
-          <t>事項 / 本村の取扱い</t>
+          <t>実績がない理由 / 確かめ方</t>
         </is>
       </c>
       <c r="E70" s="3" t="inlineStr">
@@ -3323,12 +3323,12 @@
     <row r="71">
       <c r="A71" s="4" t="inlineStr">
         <is>
-          <t>表5-30</t>
+          <t>表5-29</t>
         </is>
       </c>
       <c r="B71" s="4" t="inlineStr">
         <is>
-          <t>本人に代わって伝えるための道具の使い分け</t>
+          <t>地域生活支援事業の実施に必要な事項</t>
         </is>
       </c>
       <c r="C71" s="4" t="inlineStr">
@@ -3338,7 +3338,7 @@
       </c>
       <c r="D71" s="4" t="inlineStr">
         <is>
-          <t>道具 / 伝える場面</t>
+          <t>事項 / 本村の取扱い</t>
         </is>
       </c>
       <c r="E71" s="4" t="inlineStr">
@@ -3350,12 +3350,12 @@
     <row r="72">
       <c r="A72" s="3" t="inlineStr">
         <is>
-          <t>表5-31</t>
+          <t>表5-30</t>
         </is>
       </c>
       <c r="B72" s="3" t="inlineStr">
         <is>
-          <t>年齢到達に伴うサービスの移行</t>
+          <t>本人に代わって伝えるための道具の使い分け</t>
         </is>
       </c>
       <c r="C72" s="3" t="inlineStr">
@@ -3365,7 +3365,7 @@
       </c>
       <c r="D72" s="3" t="inlineStr">
         <is>
-          <t>年齢 / 制度上の内容</t>
+          <t>道具 / 伝える場面</t>
         </is>
       </c>
       <c r="E72" s="3" t="inlineStr">
@@ -3377,12 +3377,12 @@
     <row r="73">
       <c r="A73" s="4" t="inlineStr">
         <is>
-          <t>表5-32</t>
+          <t>表5-31</t>
         </is>
       </c>
       <c r="B73" s="4" t="inlineStr">
         <is>
-          <t>学校卒業に伴う移行について確認する事項</t>
+          <t>年齢到達に伴うサービスの移行</t>
         </is>
       </c>
       <c r="C73" s="4" t="inlineStr">
@@ -3392,7 +3392,7 @@
       </c>
       <c r="D73" s="4" t="inlineStr">
         <is>
-          <t>確認する事項 / 見込量への反映</t>
+          <t>年齢 / 制度上の内容</t>
         </is>
       </c>
       <c r="E73" s="4" t="inlineStr">
@@ -3404,12 +3404,12 @@
     <row r="74">
       <c r="A74" s="3" t="inlineStr">
         <is>
-          <t>表5-33</t>
+          <t>表5-32</t>
         </is>
       </c>
       <c r="B74" s="3" t="inlineStr">
         <is>
-          <t>65歳到達時のサービスの区分</t>
+          <t>学校卒業に伴う移行について確認する事項</t>
         </is>
       </c>
       <c r="C74" s="3" t="inlineStr">
@@ -3419,7 +3419,7 @@
       </c>
       <c r="D74" s="3" t="inlineStr">
         <is>
-          <t>区分 / 該当するサービス</t>
+          <t>確認する事項 / 見込量への反映</t>
         </is>
       </c>
       <c r="E74" s="3" t="inlineStr">
@@ -3431,12 +3431,12 @@
     <row r="75">
       <c r="A75" s="4" t="inlineStr">
         <is>
-          <t>表5-34</t>
+          <t>表5-33</t>
         </is>
       </c>
       <c r="B75" s="4" t="inlineStr">
         <is>
-          <t>65歳到達時に確認する事項</t>
+          <t>65歳到達時のサービスの区分</t>
         </is>
       </c>
       <c r="C75" s="4" t="inlineStr">
@@ -3446,7 +3446,7 @@
       </c>
       <c r="D75" s="4" t="inlineStr">
         <is>
-          <t>確認する事項 / 確認の内容</t>
+          <t>区分 / 該当するサービス</t>
         </is>
       </c>
       <c r="E75" s="4" t="inlineStr">
@@ -3458,12 +3458,12 @@
     <row r="76">
       <c r="A76" s="3" t="inlineStr">
         <is>
-          <t>表5-35</t>
+          <t>表5-34</t>
         </is>
       </c>
       <c r="B76" s="3" t="inlineStr">
         <is>
-          <t>65歳到達時の引継ぎの時期と担当</t>
+          <t>65歳到達時に確認する事項</t>
         </is>
       </c>
       <c r="C76" s="3" t="inlineStr">
@@ -3473,7 +3473,7 @@
       </c>
       <c r="D76" s="3" t="inlineStr">
         <is>
-          <t>時期 / 行うこと</t>
+          <t>確認する事項 / 確認の内容</t>
         </is>
       </c>
       <c r="E76" s="3" t="inlineStr">
@@ -3485,12 +3485,12 @@
     <row r="77">
       <c r="A77" s="4" t="inlineStr">
         <is>
-          <t>表5-36</t>
+          <t>表5-35</t>
         </is>
       </c>
       <c r="B77" s="4" t="inlineStr">
         <is>
-          <t>関係機関と連携の内容</t>
+          <t>65歳到達時の引継ぎの時期と担当</t>
         </is>
       </c>
       <c r="C77" s="4" t="inlineStr">
@@ -3500,7 +3500,7 @@
       </c>
       <c r="D77" s="4" t="inlineStr">
         <is>
-          <t>分野 / 関係機関</t>
+          <t>時期 / 行うこと</t>
         </is>
       </c>
       <c r="E77" s="4" t="inlineStr">
@@ -3512,12 +3512,12 @@
     <row r="78">
       <c r="A78" s="3" t="inlineStr">
         <is>
-          <t>表5-37</t>
+          <t>表5-36</t>
         </is>
       </c>
       <c r="B78" s="3" t="inlineStr">
         <is>
-          <t>障がい福祉サービス等に係る給付費の推移</t>
+          <t>関係機関と連携の内容</t>
         </is>
       </c>
       <c r="C78" s="3" t="inlineStr">
@@ -3527,24 +3527,24 @@
       </c>
       <c r="D78" s="3" t="inlineStr">
         <is>
-          <t>年度 / 介護給付費等</t>
+          <t>分野 / 関係機関</t>
         </is>
       </c>
       <c r="E78" s="3" t="inlineStr">
         <is>
-          <t>資料：村提供の障がいサービス給付実績</t>
+          <t>―</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" s="4" t="inlineStr">
         <is>
-          <t>表5-38</t>
+          <t>表5-37</t>
         </is>
       </c>
       <c r="B79" s="4" t="inlineStr">
         <is>
-          <t>財源構成（令和７年度・法定負担割合による試算）</t>
+          <t>障がい福祉サービス等に係る給付費の推移</t>
         </is>
       </c>
       <c r="C79" s="4" t="inlineStr">
@@ -3554,7 +3554,7 @@
       </c>
       <c r="D79" s="4" t="inlineStr">
         <is>
-          <t>区分 / 金額</t>
+          <t>年度 / 介護給付費等</t>
         </is>
       </c>
       <c r="E79" s="4" t="inlineStr">
@@ -3566,12 +3566,12 @@
     <row r="80">
       <c r="A80" s="3" t="inlineStr">
         <is>
-          <t>表5-39</t>
+          <t>表5-38</t>
         </is>
       </c>
       <c r="B80" s="3" t="inlineStr">
         <is>
-          <t>サービス別の給付費と計画上の位置づけ（令和７年度）</t>
+          <t>財源構成（令和７年度・法定負担割合による試算）</t>
         </is>
       </c>
       <c r="C80" s="3" t="inlineStr">
@@ -3581,7 +3581,7 @@
       </c>
       <c r="D80" s="3" t="inlineStr">
         <is>
-          <t>サービス / 給付費（構成比）</t>
+          <t>区分 / 金額</t>
         </is>
       </c>
       <c r="E80" s="3" t="inlineStr">
@@ -3593,39 +3593,39 @@
     <row r="81">
       <c r="A81" s="4" t="inlineStr">
         <is>
-          <t>表6-1</t>
+          <t>表5-39</t>
         </is>
       </c>
       <c r="B81" s="4" t="inlineStr">
         <is>
-          <t>高齢化率の推移</t>
+          <t>サービス別の給付費と計画上の位置づけ（令和７年度）</t>
         </is>
       </c>
       <c r="C81" s="4" t="inlineStr">
         <is>
-          <t>第6章</t>
+          <t>第5章</t>
         </is>
       </c>
       <c r="D81" s="4" t="inlineStr">
         <is>
-          <t>年度 / 高齢化率</t>
+          <t>サービス / 給付費（構成比）</t>
         </is>
       </c>
       <c r="E81" s="4" t="inlineStr">
         <is>
-          <t>資料：北塩原村</t>
+          <t>資料：村提供の障がいサービス給付実績</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" s="3" t="inlineStr">
         <is>
-          <t>表6-2</t>
+          <t>表6-1</t>
         </is>
       </c>
       <c r="B82" s="3" t="inlineStr">
         <is>
-          <t>精神障がい者及び知的障がい者の人数の推移</t>
+          <t>高齢化率の推移</t>
         </is>
       </c>
       <c r="C82" s="3" t="inlineStr">
@@ -3635,7 +3635,7 @@
       </c>
       <c r="D82" s="3" t="inlineStr">
         <is>
-          <t>年度 / 精神障がい者数（※１）</t>
+          <t>年度 / 高齢化率</t>
         </is>
       </c>
       <c r="E82" s="3" t="inlineStr">
@@ -3647,12 +3647,12 @@
     <row r="83">
       <c r="A83" s="4" t="inlineStr">
         <is>
-          <t>表6-3</t>
+          <t>表6-2</t>
         </is>
       </c>
       <c r="B83" s="4" t="inlineStr">
         <is>
-          <t>成年後見制度利用支援事業の利用状況</t>
+          <t>精神障がい者及び知的障がい者の人数の推移</t>
         </is>
       </c>
       <c r="C83" s="4" t="inlineStr">
@@ -3662,7 +3662,7 @@
       </c>
       <c r="D83" s="4" t="inlineStr">
         <is>
-          <t>区分 / 令和５年度</t>
+          <t>年度 / 精神障がい者数（※１）</t>
         </is>
       </c>
       <c r="E83" s="4" t="inlineStr">
@@ -3674,12 +3674,12 @@
     <row r="84">
       <c r="A84" s="3" t="inlineStr">
         <is>
-          <t>表6-4</t>
+          <t>表6-3</t>
         </is>
       </c>
       <c r="B84" s="3" t="inlineStr">
         <is>
-          <t>成年後見制度の利用促進に係る指標</t>
+          <t>成年後見制度利用支援事業の利用状況</t>
         </is>
       </c>
       <c r="C84" s="3" t="inlineStr">
@@ -3689,34 +3689,34 @@
       </c>
       <c r="D84" s="3" t="inlineStr">
         <is>
-          <t>指標 / 何を数えるか</t>
+          <t>区分 / 令和５年度</t>
         </is>
       </c>
       <c r="E84" s="3" t="inlineStr">
         <is>
-          <t>―</t>
+          <t>資料：北塩原村</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" s="4" t="inlineStr">
         <is>
-          <t>表7-1</t>
+          <t>表6-4</t>
         </is>
       </c>
       <c r="B85" s="4" t="inlineStr">
         <is>
-          <t>健康21・グッドヘルスプランとの対応</t>
+          <t>成年後見制度の利用促進に係る指標</t>
         </is>
       </c>
       <c r="C85" s="4" t="inlineStr">
         <is>
-          <t>第7章</t>
+          <t>第6章</t>
         </is>
       </c>
       <c r="D85" s="4" t="inlineStr">
         <is>
-          <t>項目 / 健康21・グッドヘルスプラン</t>
+          <t>指標 / 何を数えるか</t>
         </is>
       </c>
       <c r="E85" s="4" t="inlineStr">
@@ -3728,12 +3728,12 @@
     <row r="86">
       <c r="A86" s="3" t="inlineStr">
         <is>
-          <t>表7-2</t>
+          <t>表7-1</t>
         </is>
       </c>
       <c r="B86" s="3" t="inlineStr">
         <is>
-          <t>第五次総合振興計画における本計画の位置づけ</t>
+          <t>健康21・グッドヘルスプランとの対応</t>
         </is>
       </c>
       <c r="C86" s="3" t="inlineStr">
@@ -3743,7 +3743,7 @@
       </c>
       <c r="D86" s="3" t="inlineStr">
         <is>
-          <t>総合振興計画の位置づけ / 内容</t>
+          <t>項目 / 健康21・グッドヘルスプラン</t>
         </is>
       </c>
       <c r="E86" s="3" t="inlineStr">
@@ -3755,12 +3755,12 @@
     <row r="87">
       <c r="A87" s="4" t="inlineStr">
         <is>
-          <t>表7-3</t>
+          <t>表7-2</t>
         </is>
       </c>
       <c r="B87" s="4" t="inlineStr">
         <is>
-          <t>高齢者福祉計画・介護保険事業計画と重ねて数えないための確認事項</t>
+          <t>第五次総合振興計画における本計画の位置づけ</t>
         </is>
       </c>
       <c r="C87" s="4" t="inlineStr">
@@ -3770,7 +3770,7 @@
       </c>
       <c r="D87" s="4" t="inlineStr">
         <is>
-          <t>事項 / 両計画での扱い</t>
+          <t>総合振興計画の位置づけ / 内容</t>
         </is>
       </c>
       <c r="E87" s="4" t="inlineStr">
@@ -3782,12 +3782,12 @@
     <row r="88">
       <c r="A88" s="3" t="inlineStr">
         <is>
-          <t>表7-4</t>
+          <t>表7-3</t>
         </is>
       </c>
       <c r="B88" s="3" t="inlineStr">
         <is>
-          <t>こども・子育て計画との整合を確かめる事項</t>
+          <t>高齢者福祉計画・介護保険事業計画と重ねて数えないための確認事項</t>
         </is>
       </c>
       <c r="C88" s="3" t="inlineStr">
@@ -3797,7 +3797,7 @@
       </c>
       <c r="D88" s="3" t="inlineStr">
         <is>
-          <t>確かめる事項 / 確かめ方</t>
+          <t>事項 / 両計画での扱い</t>
         </is>
       </c>
       <c r="E88" s="3" t="inlineStr">
@@ -3809,22 +3809,22 @@
     <row r="89">
       <c r="A89" s="4" t="inlineStr">
         <is>
-          <t>表8-1</t>
+          <t>表7-4</t>
         </is>
       </c>
       <c r="B89" s="4" t="inlineStr">
         <is>
-          <t>北塩原村障がい者自立支援協議会委員名簿</t>
+          <t>こども・子育て計画との整合を確かめる事項</t>
         </is>
       </c>
       <c r="C89" s="4" t="inlineStr">
         <is>
-          <t>第8章</t>
+          <t>第7章</t>
         </is>
       </c>
       <c r="D89" s="4" t="inlineStr">
         <is>
-          <t>区　分 / 氏　名</t>
+          <t>確かめる事項 / 確かめ方</t>
         </is>
       </c>
       <c r="E89" s="4" t="inlineStr">
@@ -3836,12 +3836,12 @@
     <row r="90">
       <c r="A90" s="3" t="inlineStr">
         <is>
-          <t>表8-2</t>
+          <t>表8-1</t>
         </is>
       </c>
       <c r="B90" s="3" t="inlineStr">
         <is>
-          <t>計画の策定経過</t>
+          <t>北塩原村障がい者自立支援協議会委員名簿</t>
         </is>
       </c>
       <c r="C90" s="3" t="inlineStr">
@@ -3851,7 +3851,7 @@
       </c>
       <c r="D90" s="3" t="inlineStr">
         <is>
-          <t>年月日 / 内容</t>
+          <t>区　分 / 氏　名</t>
         </is>
       </c>
       <c r="E90" s="3" t="inlineStr">
@@ -3863,12 +3863,12 @@
     <row r="91">
       <c r="A91" s="4" t="inlineStr">
         <is>
-          <t>表8-3</t>
+          <t>表8-2</t>
         </is>
       </c>
       <c r="B91" s="4" t="inlineStr">
         <is>
-          <t>近年の障がい者施策の動向</t>
+          <t>計画の策定経過</t>
         </is>
       </c>
       <c r="C91" s="4" t="inlineStr">
@@ -3878,7 +3878,7 @@
       </c>
       <c r="D91" s="4" t="inlineStr">
         <is>
-          <t>年 / 主な動向</t>
+          <t>年月日 / 内容</t>
         </is>
       </c>
       <c r="E91" s="4" t="inlineStr">
@@ -3890,25 +3890,52 @@
     <row r="92">
       <c r="A92" s="3" t="inlineStr">
         <is>
+          <t>表8-3</t>
+        </is>
+      </c>
+      <c r="B92" s="3" t="inlineStr">
+        <is>
+          <t>近年の障がい者施策の動向</t>
+        </is>
+      </c>
+      <c r="C92" s="3" t="inlineStr">
+        <is>
+          <t>第8章</t>
+        </is>
+      </c>
+      <c r="D92" s="3" t="inlineStr">
+        <is>
+          <t>年 / 主な動向</t>
+        </is>
+      </c>
+      <c r="E92" s="3" t="inlineStr">
+        <is>
+          <t>―</t>
+        </is>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" s="4" t="inlineStr">
+        <is>
           <t>表8-4</t>
         </is>
       </c>
-      <c r="B92" s="3" t="inlineStr">
+      <c r="B93" s="4" t="inlineStr">
         <is>
           <t>用語解説</t>
         </is>
       </c>
-      <c r="C92" s="3" t="inlineStr">
+      <c r="C93" s="4" t="inlineStr">
         <is>
           <t>第8章</t>
         </is>
       </c>
-      <c r="D92" s="3" t="inlineStr">
+      <c r="D93" s="4" t="inlineStr">
         <is>
           <t>用語 / 説明</t>
         </is>
       </c>
-      <c r="E92" s="3" t="inlineStr">
+      <c r="E93" s="4" t="inlineStr">
         <is>
           <t>―</t>
         </is>

--- a/output/北塩原村_図表番号一覧.xlsx
+++ b/output/北塩原村_図表番号一覧.xlsx
@@ -535,7 +535,7 @@
       </c>
       <c r="B6" s="3" t="inlineStr">
         <is>
-          <t>図25点・表88点に章ごとの通し番号を振った（図１-１・表１-１の形）。注記ボックス（【村へ確認】等の1×1の枠）45点には振っていない。確定時に削るため、番号を振ると欠番が出るからである。</t>
+          <t>図26点・表88点に章ごとの通し番号を振った（図１-１・表１-１の形）。注記ボックス（【村へ確認】等の1×1の枠）45点には振っていない。確定時に削るため、番号を振ると欠番が出るからである。</t>
         </is>
       </c>
     </row>
@@ -607,7 +607,7 @@
       </c>
       <c r="B12" s="3" t="inlineStr">
         <is>
-          <t>出所は、村の実績・アンケート・外部資料から数値を引いた図表41点にのみ付けた。手順・区分・確認事項を整理しただけの表は本計画の記述そのものであり、出所を書くと出どころが二重になるためである（規約への補足1件）。</t>
+          <t>出所は、村の実績・アンケート・外部資料から数値を引いた図表42点にのみ付けた。手順・区分・確認事項を整理しただけの表は本計画の記述そのものであり、出所を書くと出どころが二重になるためである（規約への補足1件）。</t>
         </is>
       </c>
     </row>
@@ -638,7 +638,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F30"/>
+  <dimension ref="A1:F31"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -652,7 +652,7 @@
     <row r="1" ht="30" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>図 25点</t>
+          <t>図 26点</t>
         </is>
       </c>
     </row>
@@ -1492,6 +1492,38 @@
       <c r="F30" s="3" t="inlineStr">
         <is>
           <t>―</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="4" t="inlineStr">
+        <is>
+          <t>図7-2</t>
+        </is>
+      </c>
+      <c r="B31" s="4" t="inlineStr">
+        <is>
+          <t>本計画と介護保険事業計画の関係</t>
+        </is>
+      </c>
+      <c r="C31" s="4" t="inlineStr">
+        <is>
+          <t>第7章3 高齢者福祉計画・介護保険事業計画との連携</t>
+        </is>
+      </c>
+      <c r="D31" s="8" t="inlineStr">
+        <is>
+          <t>当方</t>
+        </is>
+      </c>
+      <c r="E31" s="4" t="inlineStr">
+        <is>
+          <t>（画像内に表題なし）</t>
+        </is>
+      </c>
+      <c r="F31" s="4" t="inlineStr">
+        <is>
+          <t>資料：北塩原村（第７章３及び第10期北塩原村高齢者福祉計画・介護保険事業計画の素案により作成）</t>
         </is>
       </c>
     </row>

--- a/output/北塩原村_図表番号一覧.xlsx
+++ b/output/北塩原村_図表番号一覧.xlsx
@@ -535,7 +535,7 @@
       </c>
       <c r="B6" s="3" t="inlineStr">
         <is>
-          <t>図26点・表88点に章ごとの通し番号を振った（図１-１・表１-１の形）。注記ボックス（【村へ確認】等の1×1の枠）45点には振っていない。確定時に削るため、番号を振ると欠番が出るからである。</t>
+          <t>図26点・表90点に章ごとの通し番号を振った（図１-１・表１-１の形）。注記ボックス（【村へ確認】等の1×1の枠）45点には振っていない。確定時に削るため、番号を振ると欠番が出るからである。</t>
         </is>
       </c>
     </row>
@@ -1542,7 +1542,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E93"/>
+  <dimension ref="A1:E95"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -1555,7 +1555,7 @@
     <row r="1" ht="30" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>表 88点</t>
+          <t>表 90点</t>
         </is>
       </c>
     </row>
@@ -3009,7 +3009,7 @@
       </c>
       <c r="B58" s="3" t="inlineStr">
         <is>
-          <t>一般の子育て施策と障がい福祉の切り分け</t>
+          <t>村内に事業所がないサービスの確保の経路</t>
         </is>
       </c>
       <c r="C58" s="3" t="inlineStr">
@@ -3019,7 +3019,7 @@
       </c>
       <c r="D58" s="3" t="inlineStr">
         <is>
-          <t>場面 / まず確かめる一般の子育て施策</t>
+          <t>サービス / 本村の設置数</t>
         </is>
       </c>
       <c r="E58" s="3" t="inlineStr">
@@ -3036,7 +3036,7 @@
       </c>
       <c r="B59" s="4" t="inlineStr">
         <is>
-          <t>事業所の受入余力について照会する事項</t>
+          <t>地域生活支援拠点の実績について４町村で揃える定義</t>
         </is>
       </c>
       <c r="C59" s="4" t="inlineStr">
@@ -3046,7 +3046,7 @@
       </c>
       <c r="D59" s="4" t="inlineStr">
         <is>
-          <t>照会する事項 / 確保できる量との関係</t>
+          <t>記録する事項 / ４町村で揃える定義</t>
         </is>
       </c>
       <c r="E59" s="4" t="inlineStr">
@@ -3063,7 +3063,7 @@
       </c>
       <c r="B60" s="3" t="inlineStr">
         <is>
-          <t>緊急時に働く仕組み（４つの場面）</t>
+          <t>一般の子育て施策と障がい福祉の切り分け</t>
         </is>
       </c>
       <c r="C60" s="3" t="inlineStr">
@@ -3073,7 +3073,7 @@
       </c>
       <c r="D60" s="3" t="inlineStr">
         <is>
-          <t>場面 / 想定される事態</t>
+          <t>場面 / まず確かめる一般の子育て施策</t>
         </is>
       </c>
       <c r="E60" s="3" t="inlineStr">
@@ -3090,7 +3090,7 @@
       </c>
       <c r="B61" s="4" t="inlineStr">
         <is>
-          <t>災害時にサービスを止めないための備え</t>
+          <t>事業所の受入余力について照会する事項</t>
         </is>
       </c>
       <c r="C61" s="4" t="inlineStr">
@@ -3100,7 +3100,7 @@
       </c>
       <c r="D61" s="4" t="inlineStr">
         <is>
-          <t>備える事項 / 本村の取組み</t>
+          <t>照会する事項 / 確保できる量との関係</t>
         </is>
       </c>
       <c r="E61" s="4" t="inlineStr">
@@ -3117,7 +3117,7 @@
       </c>
       <c r="B62" s="3" t="inlineStr">
         <is>
-          <t>災害時の情報の伝達について確かめること</t>
+          <t>緊急時に働く仕組み（４つの場面）</t>
         </is>
       </c>
       <c r="C62" s="3" t="inlineStr">
@@ -3127,7 +3127,7 @@
       </c>
       <c r="D62" s="3" t="inlineStr">
         <is>
-          <t>確かめること / 確かめ方</t>
+          <t>場面 / 想定される事態</t>
         </is>
       </c>
       <c r="E62" s="3" t="inlineStr">
@@ -3144,7 +3144,7 @@
       </c>
       <c r="B63" s="4" t="inlineStr">
         <is>
-          <t>虐待の予防から再発の防止までの流れ</t>
+          <t>災害時にサービスを止めないための備え</t>
         </is>
       </c>
       <c r="C63" s="4" t="inlineStr">
@@ -3154,7 +3154,7 @@
       </c>
       <c r="D63" s="4" t="inlineStr">
         <is>
-          <t>段階 / 本村の取組み</t>
+          <t>備える事項 / 本村の取組み</t>
         </is>
       </c>
       <c r="E63" s="4" t="inlineStr">
@@ -3171,7 +3171,7 @@
       </c>
       <c r="B64" s="3" t="inlineStr">
         <is>
-          <t>経営基盤に関して把握する事項</t>
+          <t>災害時の情報の伝達について確かめること</t>
         </is>
       </c>
       <c r="C64" s="3" t="inlineStr">
@@ -3181,7 +3181,7 @@
       </c>
       <c r="D64" s="3" t="inlineStr">
         <is>
-          <t>把握する事項 / 見込量への影響</t>
+          <t>確かめること / 確かめ方</t>
         </is>
       </c>
       <c r="E64" s="3" t="inlineStr">
@@ -3198,7 +3198,7 @@
       </c>
       <c r="B65" s="4" t="inlineStr">
         <is>
-          <t>冬季の支援を検討する三つの段階</t>
+          <t>虐待の予防から再発の防止までの流れ</t>
         </is>
       </c>
       <c r="C65" s="4" t="inlineStr">
@@ -3208,7 +3208,7 @@
       </c>
       <c r="D65" s="4" t="inlineStr">
         <is>
-          <t>段階 / 確かめること</t>
+          <t>段階 / 本村の取組み</t>
         </is>
       </c>
       <c r="E65" s="4" t="inlineStr">
@@ -3225,7 +3225,7 @@
       </c>
       <c r="B66" s="3" t="inlineStr">
         <is>
-          <t>冬季の通行規制による中断について記録する事項</t>
+          <t>経営基盤に関して把握する事項</t>
         </is>
       </c>
       <c r="C66" s="3" t="inlineStr">
@@ -3235,7 +3235,7 @@
       </c>
       <c r="D66" s="3" t="inlineStr">
         <is>
-          <t>記録する事項 / 記録の仕方</t>
+          <t>把握する事項 / 見込量への影響</t>
         </is>
       </c>
       <c r="E66" s="3" t="inlineStr">
@@ -3252,7 +3252,7 @@
       </c>
       <c r="B67" s="4" t="inlineStr">
         <is>
-          <t>医療へのアクセス</t>
+          <t>冬季の支援を検討する三つの段階</t>
         </is>
       </c>
       <c r="C67" s="4" t="inlineStr">
@@ -3262,7 +3262,7 @@
       </c>
       <c r="D67" s="4" t="inlineStr">
         <is>
-          <t>場面 / 主な医療資源</t>
+          <t>段階 / 確かめること</t>
         </is>
       </c>
       <c r="E67" s="4" t="inlineStr">
@@ -3279,7 +3279,7 @@
       </c>
       <c r="B68" s="3" t="inlineStr">
         <is>
-          <t>地域生活支援事業の実績</t>
+          <t>冬季の通行規制による中断について記録する事項</t>
         </is>
       </c>
       <c r="C68" s="3" t="inlineStr">
@@ -3289,12 +3289,12 @@
       </c>
       <c r="D68" s="3" t="inlineStr">
         <is>
-          <t>サービスの種類 / 令和６年度</t>
+          <t>記録する事項 / 記録の仕方</t>
         </is>
       </c>
       <c r="E68" s="3" t="inlineStr">
         <is>
-          <t>資料：北塩原村</t>
+          <t>―</t>
         </is>
       </c>
     </row>
@@ -3306,7 +3306,7 @@
       </c>
       <c r="B69" s="4" t="inlineStr">
         <is>
-          <t>地域生活支援事業の見込量</t>
+          <t>医療へのアクセス</t>
         </is>
       </c>
       <c r="C69" s="4" t="inlineStr">
@@ -3316,7 +3316,7 @@
       </c>
       <c r="D69" s="4" t="inlineStr">
         <is>
-          <t>サービスの種類 / 令和９年度</t>
+          <t>場面 / 主な医療資源</t>
         </is>
       </c>
       <c r="E69" s="4" t="inlineStr">
@@ -3333,7 +3333,7 @@
       </c>
       <c r="B70" s="3" t="inlineStr">
         <is>
-          <t>実績がない事業の扱い</t>
+          <t>地域生活支援事業の実績</t>
         </is>
       </c>
       <c r="C70" s="3" t="inlineStr">
@@ -3343,12 +3343,12 @@
       </c>
       <c r="D70" s="3" t="inlineStr">
         <is>
-          <t>実績がない理由 / 確かめ方</t>
+          <t>サービスの種類 / 令和６年度</t>
         </is>
       </c>
       <c r="E70" s="3" t="inlineStr">
         <is>
-          <t>―</t>
+          <t>資料：北塩原村</t>
         </is>
       </c>
     </row>
@@ -3360,7 +3360,7 @@
       </c>
       <c r="B71" s="4" t="inlineStr">
         <is>
-          <t>地域生活支援事業の実施に必要な事項</t>
+          <t>地域生活支援事業の見込量</t>
         </is>
       </c>
       <c r="C71" s="4" t="inlineStr">
@@ -3370,7 +3370,7 @@
       </c>
       <c r="D71" s="4" t="inlineStr">
         <is>
-          <t>事項 / 本村の取扱い</t>
+          <t>サービスの種類 / 令和９年度</t>
         </is>
       </c>
       <c r="E71" s="4" t="inlineStr">
@@ -3387,7 +3387,7 @@
       </c>
       <c r="B72" s="3" t="inlineStr">
         <is>
-          <t>本人に代わって伝えるための道具の使い分け</t>
+          <t>実績がない事業の扱い</t>
         </is>
       </c>
       <c r="C72" s="3" t="inlineStr">
@@ -3397,7 +3397,7 @@
       </c>
       <c r="D72" s="3" t="inlineStr">
         <is>
-          <t>道具 / 伝える場面</t>
+          <t>実績がない理由 / 確かめ方</t>
         </is>
       </c>
       <c r="E72" s="3" t="inlineStr">
@@ -3414,7 +3414,7 @@
       </c>
       <c r="B73" s="4" t="inlineStr">
         <is>
-          <t>年齢到達に伴うサービスの移行</t>
+          <t>地域生活支援事業の実施に必要な事項</t>
         </is>
       </c>
       <c r="C73" s="4" t="inlineStr">
@@ -3424,7 +3424,7 @@
       </c>
       <c r="D73" s="4" t="inlineStr">
         <is>
-          <t>年齢 / 制度上の内容</t>
+          <t>事項 / 本村の取扱い</t>
         </is>
       </c>
       <c r="E73" s="4" t="inlineStr">
@@ -3441,7 +3441,7 @@
       </c>
       <c r="B74" s="3" t="inlineStr">
         <is>
-          <t>学校卒業に伴う移行について確認する事項</t>
+          <t>本人に代わって伝えるための道具の使い分け</t>
         </is>
       </c>
       <c r="C74" s="3" t="inlineStr">
@@ -3451,7 +3451,7 @@
       </c>
       <c r="D74" s="3" t="inlineStr">
         <is>
-          <t>確認する事項 / 見込量への反映</t>
+          <t>道具 / 伝える場面</t>
         </is>
       </c>
       <c r="E74" s="3" t="inlineStr">
@@ -3468,7 +3468,7 @@
       </c>
       <c r="B75" s="4" t="inlineStr">
         <is>
-          <t>65歳到達時のサービスの区分</t>
+          <t>年齢到達に伴うサービスの移行</t>
         </is>
       </c>
       <c r="C75" s="4" t="inlineStr">
@@ -3478,7 +3478,7 @@
       </c>
       <c r="D75" s="4" t="inlineStr">
         <is>
-          <t>区分 / 該当するサービス</t>
+          <t>年齢 / 制度上の内容</t>
         </is>
       </c>
       <c r="E75" s="4" t="inlineStr">
@@ -3495,7 +3495,7 @@
       </c>
       <c r="B76" s="3" t="inlineStr">
         <is>
-          <t>65歳到達時に確認する事項</t>
+          <t>学校卒業に伴う移行について確認する事項</t>
         </is>
       </c>
       <c r="C76" s="3" t="inlineStr">
@@ -3505,7 +3505,7 @@
       </c>
       <c r="D76" s="3" t="inlineStr">
         <is>
-          <t>確認する事項 / 確認の内容</t>
+          <t>確認する事項 / 見込量への反映</t>
         </is>
       </c>
       <c r="E76" s="3" t="inlineStr">
@@ -3522,7 +3522,7 @@
       </c>
       <c r="B77" s="4" t="inlineStr">
         <is>
-          <t>65歳到達時の引継ぎの時期と担当</t>
+          <t>65歳到達時のサービスの区分</t>
         </is>
       </c>
       <c r="C77" s="4" t="inlineStr">
@@ -3532,7 +3532,7 @@
       </c>
       <c r="D77" s="4" t="inlineStr">
         <is>
-          <t>時期 / 行うこと</t>
+          <t>区分 / 該当するサービス</t>
         </is>
       </c>
       <c r="E77" s="4" t="inlineStr">
@@ -3549,7 +3549,7 @@
       </c>
       <c r="B78" s="3" t="inlineStr">
         <is>
-          <t>関係機関と連携の内容</t>
+          <t>65歳到達時に確認する事項</t>
         </is>
       </c>
       <c r="C78" s="3" t="inlineStr">
@@ -3559,7 +3559,7 @@
       </c>
       <c r="D78" s="3" t="inlineStr">
         <is>
-          <t>分野 / 関係機関</t>
+          <t>確認する事項 / 確認の内容</t>
         </is>
       </c>
       <c r="E78" s="3" t="inlineStr">
@@ -3576,7 +3576,7 @@
       </c>
       <c r="B79" s="4" t="inlineStr">
         <is>
-          <t>障がい福祉サービス等に係る給付費の推移</t>
+          <t>65歳到達時の引継ぎの時期と担当</t>
         </is>
       </c>
       <c r="C79" s="4" t="inlineStr">
@@ -3586,12 +3586,12 @@
       </c>
       <c r="D79" s="4" t="inlineStr">
         <is>
-          <t>年度 / 介護給付費等</t>
+          <t>時期 / 行うこと</t>
         </is>
       </c>
       <c r="E79" s="4" t="inlineStr">
         <is>
-          <t>資料：村提供の障がいサービス給付実績</t>
+          <t>―</t>
         </is>
       </c>
     </row>
@@ -3603,7 +3603,7 @@
       </c>
       <c r="B80" s="3" t="inlineStr">
         <is>
-          <t>財源構成（令和７年度・法定負担割合による試算）</t>
+          <t>関係機関と連携の内容</t>
         </is>
       </c>
       <c r="C80" s="3" t="inlineStr">
@@ -3613,12 +3613,12 @@
       </c>
       <c r="D80" s="3" t="inlineStr">
         <is>
-          <t>区分 / 金額</t>
+          <t>分野 / 関係機関</t>
         </is>
       </c>
       <c r="E80" s="3" t="inlineStr">
         <is>
-          <t>資料：村提供の障がいサービス給付実績</t>
+          <t>―</t>
         </is>
       </c>
     </row>
@@ -3630,7 +3630,7 @@
       </c>
       <c r="B81" s="4" t="inlineStr">
         <is>
-          <t>サービス別の給付費と計画上の位置づけ（令和７年度）</t>
+          <t>障がい福祉サービス等に係る給付費の推移</t>
         </is>
       </c>
       <c r="C81" s="4" t="inlineStr">
@@ -3640,7 +3640,7 @@
       </c>
       <c r="D81" s="4" t="inlineStr">
         <is>
-          <t>サービス / 給付費（構成比）</t>
+          <t>年度 / 介護給付費等</t>
         </is>
       </c>
       <c r="E81" s="4" t="inlineStr">
@@ -3652,66 +3652,66 @@
     <row r="82">
       <c r="A82" s="3" t="inlineStr">
         <is>
-          <t>表6-1</t>
+          <t>表5-40</t>
         </is>
       </c>
       <c r="B82" s="3" t="inlineStr">
         <is>
-          <t>高齢化率の推移</t>
+          <t>財源構成（令和７年度・法定負担割合による試算）</t>
         </is>
       </c>
       <c r="C82" s="3" t="inlineStr">
         <is>
-          <t>第6章</t>
+          <t>第5章</t>
         </is>
       </c>
       <c r="D82" s="3" t="inlineStr">
         <is>
-          <t>年度 / 高齢化率</t>
+          <t>区分 / 金額</t>
         </is>
       </c>
       <c r="E82" s="3" t="inlineStr">
         <is>
-          <t>資料：北塩原村</t>
+          <t>資料：村提供の障がいサービス給付実績</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" s="4" t="inlineStr">
         <is>
-          <t>表6-2</t>
+          <t>表5-41</t>
         </is>
       </c>
       <c r="B83" s="4" t="inlineStr">
         <is>
-          <t>精神障がい者及び知的障がい者の人数の推移</t>
+          <t>サービス別の給付費と計画上の位置づけ（令和７年度）</t>
         </is>
       </c>
       <c r="C83" s="4" t="inlineStr">
         <is>
-          <t>第6章</t>
+          <t>第5章</t>
         </is>
       </c>
       <c r="D83" s="4" t="inlineStr">
         <is>
-          <t>年度 / 精神障がい者数（※１）</t>
+          <t>サービス / 給付費（構成比）</t>
         </is>
       </c>
       <c r="E83" s="4" t="inlineStr">
         <is>
-          <t>資料：北塩原村</t>
+          <t>資料：村提供の障がいサービス給付実績</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" s="3" t="inlineStr">
         <is>
-          <t>表6-3</t>
+          <t>表6-1</t>
         </is>
       </c>
       <c r="B84" s="3" t="inlineStr">
         <is>
-          <t>成年後見制度利用支援事業の利用状況</t>
+          <t>高齢化率の推移</t>
         </is>
       </c>
       <c r="C84" s="3" t="inlineStr">
@@ -3721,7 +3721,7 @@
       </c>
       <c r="D84" s="3" t="inlineStr">
         <is>
-          <t>区分 / 令和５年度</t>
+          <t>年度 / 高齢化率</t>
         </is>
       </c>
       <c r="E84" s="3" t="inlineStr">
@@ -3733,12 +3733,12 @@
     <row r="85">
       <c r="A85" s="4" t="inlineStr">
         <is>
-          <t>表6-4</t>
+          <t>表6-2</t>
         </is>
       </c>
       <c r="B85" s="4" t="inlineStr">
         <is>
-          <t>成年後見制度の利用促進に係る指標</t>
+          <t>精神障がい者及び知的障がい者の人数の推移</t>
         </is>
       </c>
       <c r="C85" s="4" t="inlineStr">
@@ -3748,61 +3748,61 @@
       </c>
       <c r="D85" s="4" t="inlineStr">
         <is>
-          <t>指標 / 何を数えるか</t>
+          <t>年度 / 精神障がい者数（※１）</t>
         </is>
       </c>
       <c r="E85" s="4" t="inlineStr">
         <is>
-          <t>―</t>
+          <t>資料：北塩原村</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" s="3" t="inlineStr">
         <is>
-          <t>表7-1</t>
+          <t>表6-3</t>
         </is>
       </c>
       <c r="B86" s="3" t="inlineStr">
         <is>
-          <t>健康21・グッドヘルスプランとの対応</t>
+          <t>成年後見制度利用支援事業の利用状況</t>
         </is>
       </c>
       <c r="C86" s="3" t="inlineStr">
         <is>
-          <t>第7章</t>
+          <t>第6章</t>
         </is>
       </c>
       <c r="D86" s="3" t="inlineStr">
         <is>
-          <t>項目 / 健康21・グッドヘルスプラン</t>
+          <t>区分 / 令和５年度</t>
         </is>
       </c>
       <c r="E86" s="3" t="inlineStr">
         <is>
-          <t>―</t>
+          <t>資料：北塩原村</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" s="4" t="inlineStr">
         <is>
-          <t>表7-2</t>
+          <t>表6-4</t>
         </is>
       </c>
       <c r="B87" s="4" t="inlineStr">
         <is>
-          <t>第五次総合振興計画における本計画の位置づけ</t>
+          <t>成年後見制度の利用促進に係る指標</t>
         </is>
       </c>
       <c r="C87" s="4" t="inlineStr">
         <is>
-          <t>第7章</t>
+          <t>第6章</t>
         </is>
       </c>
       <c r="D87" s="4" t="inlineStr">
         <is>
-          <t>総合振興計画の位置づけ / 内容</t>
+          <t>指標 / 何を数えるか</t>
         </is>
       </c>
       <c r="E87" s="4" t="inlineStr">
@@ -3814,12 +3814,12 @@
     <row r="88">
       <c r="A88" s="3" t="inlineStr">
         <is>
-          <t>表7-3</t>
+          <t>表7-1</t>
         </is>
       </c>
       <c r="B88" s="3" t="inlineStr">
         <is>
-          <t>高齢者福祉計画・介護保険事業計画と重ねて数えないための確認事項</t>
+          <t>健康21・グッドヘルスプランとの対応</t>
         </is>
       </c>
       <c r="C88" s="3" t="inlineStr">
@@ -3829,7 +3829,7 @@
       </c>
       <c r="D88" s="3" t="inlineStr">
         <is>
-          <t>事項 / 両計画での扱い</t>
+          <t>項目 / 健康21・グッドヘルスプラン</t>
         </is>
       </c>
       <c r="E88" s="3" t="inlineStr">
@@ -3841,12 +3841,12 @@
     <row r="89">
       <c r="A89" s="4" t="inlineStr">
         <is>
-          <t>表7-4</t>
+          <t>表7-2</t>
         </is>
       </c>
       <c r="B89" s="4" t="inlineStr">
         <is>
-          <t>こども・子育て計画との整合を確かめる事項</t>
+          <t>第五次総合振興計画における本計画の位置づけ</t>
         </is>
       </c>
       <c r="C89" s="4" t="inlineStr">
@@ -3856,7 +3856,7 @@
       </c>
       <c r="D89" s="4" t="inlineStr">
         <is>
-          <t>確かめる事項 / 確かめ方</t>
+          <t>総合振興計画の位置づけ / 内容</t>
         </is>
       </c>
       <c r="E89" s="4" t="inlineStr">
@@ -3868,22 +3868,22 @@
     <row r="90">
       <c r="A90" s="3" t="inlineStr">
         <is>
-          <t>表8-1</t>
+          <t>表7-3</t>
         </is>
       </c>
       <c r="B90" s="3" t="inlineStr">
         <is>
-          <t>北塩原村障がい者自立支援協議会委員名簿</t>
+          <t>高齢者福祉計画・介護保険事業計画と重ねて数えないための確認事項</t>
         </is>
       </c>
       <c r="C90" s="3" t="inlineStr">
         <is>
-          <t>第8章</t>
+          <t>第7章</t>
         </is>
       </c>
       <c r="D90" s="3" t="inlineStr">
         <is>
-          <t>区　分 / 氏　名</t>
+          <t>事項 / 両計画での扱い</t>
         </is>
       </c>
       <c r="E90" s="3" t="inlineStr">
@@ -3895,22 +3895,22 @@
     <row r="91">
       <c r="A91" s="4" t="inlineStr">
         <is>
-          <t>表8-2</t>
+          <t>表7-4</t>
         </is>
       </c>
       <c r="B91" s="4" t="inlineStr">
         <is>
-          <t>計画の策定経過</t>
+          <t>こども・子育て計画との整合を確かめる事項</t>
         </is>
       </c>
       <c r="C91" s="4" t="inlineStr">
         <is>
-          <t>第8章</t>
+          <t>第7章</t>
         </is>
       </c>
       <c r="D91" s="4" t="inlineStr">
         <is>
-          <t>年月日 / 内容</t>
+          <t>確かめる事項 / 確かめ方</t>
         </is>
       </c>
       <c r="E91" s="4" t="inlineStr">
@@ -3922,12 +3922,12 @@
     <row r="92">
       <c r="A92" s="3" t="inlineStr">
         <is>
-          <t>表8-3</t>
+          <t>表8-1</t>
         </is>
       </c>
       <c r="B92" s="3" t="inlineStr">
         <is>
-          <t>近年の障がい者施策の動向</t>
+          <t>北塩原村障がい者自立支援協議会委員名簿</t>
         </is>
       </c>
       <c r="C92" s="3" t="inlineStr">
@@ -3937,7 +3937,7 @@
       </c>
       <c r="D92" s="3" t="inlineStr">
         <is>
-          <t>年 / 主な動向</t>
+          <t>区　分 / 氏　名</t>
         </is>
       </c>
       <c r="E92" s="3" t="inlineStr">
@@ -3949,25 +3949,79 @@
     <row r="93">
       <c r="A93" s="4" t="inlineStr">
         <is>
+          <t>表8-2</t>
+        </is>
+      </c>
+      <c r="B93" s="4" t="inlineStr">
+        <is>
+          <t>計画の策定経過</t>
+        </is>
+      </c>
+      <c r="C93" s="4" t="inlineStr">
+        <is>
+          <t>第8章</t>
+        </is>
+      </c>
+      <c r="D93" s="4" t="inlineStr">
+        <is>
+          <t>年月日 / 内容</t>
+        </is>
+      </c>
+      <c r="E93" s="4" t="inlineStr">
+        <is>
+          <t>―</t>
+        </is>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" s="3" t="inlineStr">
+        <is>
+          <t>表8-3</t>
+        </is>
+      </c>
+      <c r="B94" s="3" t="inlineStr">
+        <is>
+          <t>近年の障がい者施策の動向</t>
+        </is>
+      </c>
+      <c r="C94" s="3" t="inlineStr">
+        <is>
+          <t>第8章</t>
+        </is>
+      </c>
+      <c r="D94" s="3" t="inlineStr">
+        <is>
+          <t>年 / 主な動向</t>
+        </is>
+      </c>
+      <c r="E94" s="3" t="inlineStr">
+        <is>
+          <t>―</t>
+        </is>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" s="4" t="inlineStr">
+        <is>
           <t>表8-4</t>
         </is>
       </c>
-      <c r="B93" s="4" t="inlineStr">
+      <c r="B95" s="4" t="inlineStr">
         <is>
           <t>用語解説</t>
         </is>
       </c>
-      <c r="C93" s="4" t="inlineStr">
+      <c r="C95" s="4" t="inlineStr">
         <is>
           <t>第8章</t>
         </is>
       </c>
-      <c r="D93" s="4" t="inlineStr">
+      <c r="D95" s="4" t="inlineStr">
         <is>
           <t>用語 / 説明</t>
         </is>
       </c>
-      <c r="E93" s="4" t="inlineStr">
+      <c r="E95" s="4" t="inlineStr">
         <is>
           <t>―</t>
         </is>

--- a/output/北塩原村_図表番号一覧.xlsx
+++ b/output/北塩原村_図表番号一覧.xlsx
@@ -535,7 +535,7 @@
       </c>
       <c r="B6" s="3" t="inlineStr">
         <is>
-          <t>図26点・表90点に章ごとの通し番号を振った（図１-１・表１-１の形）。注記ボックス（【村へ確認】等の1×1の枠）45点には振っていない。確定時に削るため、番号を振ると欠番が出るからである。</t>
+          <t>図26点・表91点に章ごとの通し番号を振った（図１-１・表１-１の形）。注記ボックス（【村へ確認】等の1×1の枠）45点には振っていない。確定時に削るため、番号を振ると欠番が出るからである。</t>
         </is>
       </c>
     </row>
@@ -607,7 +607,7 @@
       </c>
       <c r="B12" s="3" t="inlineStr">
         <is>
-          <t>出所は、村の実績・アンケート・外部資料から数値を引いた図表42点にのみ付けた。手順・区分・確認事項を整理しただけの表は本計画の記述そのものであり、出所を書くと出どころが二重になるためである（規約への補足1件）。</t>
+          <t>出所は、村の実績・アンケート・外部資料から数値を引いた図表43点にのみ付けた。手順・区分・確認事項を整理しただけの表は本計画の記述そのものであり、出所を書くと出どころが二重になるためである（規約への補足1件）。</t>
         </is>
       </c>
     </row>
@@ -1542,7 +1542,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E95"/>
+  <dimension ref="A1:E96"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -1555,7 +1555,7 @@
     <row r="1" ht="30" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>表 90点</t>
+          <t>表 91点</t>
         </is>
       </c>
     </row>
@@ -2523,7 +2523,7 @@
       </c>
       <c r="B40" s="3" t="inlineStr">
         <is>
-          <t>障害福祉人材の確保・定着等の目標</t>
+          <t>会津障がい保健福祉圏域の基幹相談支援センター（令和７年４月１日時点）</t>
         </is>
       </c>
       <c r="C40" s="3" t="inlineStr">
@@ -2533,12 +2533,12 @@
       </c>
       <c r="D40" s="3" t="inlineStr">
         <is>
-          <t>項目 / 数値</t>
+          <t>基幹相談支援センター / 設置の形</t>
         </is>
       </c>
       <c r="E40" s="3" t="inlineStr">
         <is>
-          <t>―</t>
+          <t>資料：厚生労働省「基幹相談支援センター一覧（令和７年４月１日時点）」</t>
         </is>
       </c>
     </row>
@@ -2550,7 +2550,7 @@
       </c>
       <c r="B41" s="4" t="inlineStr">
         <is>
-          <t>障害福祉サービス等の質を向上させる体制の構築の目標</t>
+          <t>障害福祉人材の確保・定着等の目標</t>
         </is>
       </c>
       <c r="C41" s="4" t="inlineStr">
@@ -2577,7 +2577,7 @@
       </c>
       <c r="B42" s="3" t="inlineStr">
         <is>
-          <t>発達障がい者等に対する支援の活動指標</t>
+          <t>障害福祉サービス等の質を向上させる体制の構築の目標</t>
         </is>
       </c>
       <c r="C42" s="3" t="inlineStr">
@@ -2587,7 +2587,7 @@
       </c>
       <c r="D42" s="3" t="inlineStr">
         <is>
-          <t>活動指標 / 令和９年度</t>
+          <t>項目 / 数値</t>
         </is>
       </c>
       <c r="E42" s="3" t="inlineStr">
@@ -2599,22 +2599,22 @@
     <row r="43">
       <c r="A43" s="4" t="inlineStr">
         <is>
-          <t>表5-1</t>
+          <t>表4-17</t>
         </is>
       </c>
       <c r="B43" s="4" t="inlineStr">
         <is>
-          <t>障がい福祉サービス等の体系（参考）</t>
+          <t>発達障がい者等に対する支援の活動指標</t>
         </is>
       </c>
       <c r="C43" s="4" t="inlineStr">
         <is>
-          <t>第5章</t>
+          <t>第4章</t>
         </is>
       </c>
       <c r="D43" s="4" t="inlineStr">
         <is>
-          <t>区分 / 主なサービス・事業</t>
+          <t>活動指標 / 令和９年度</t>
         </is>
       </c>
       <c r="E43" s="4" t="inlineStr">
@@ -2626,12 +2626,12 @@
     <row r="44">
       <c r="A44" s="3" t="inlineStr">
         <is>
-          <t>表5-2</t>
+          <t>表5-1</t>
         </is>
       </c>
       <c r="B44" s="3" t="inlineStr">
         <is>
-          <t>見込量を定めるまでの段階</t>
+          <t>障がい福祉サービス等の体系（参考）</t>
         </is>
       </c>
       <c r="C44" s="3" t="inlineStr">
@@ -2641,7 +2641,7 @@
       </c>
       <c r="D44" s="3" t="inlineStr">
         <is>
-          <t>段階 / 何を見るか</t>
+          <t>区分 / 主なサービス・事業</t>
         </is>
       </c>
       <c r="E44" s="3" t="inlineStr">
@@ -2653,12 +2653,12 @@
     <row r="45">
       <c r="A45" s="4" t="inlineStr">
         <is>
-          <t>表5-3</t>
+          <t>表5-2</t>
         </is>
       </c>
       <c r="B45" s="4" t="inlineStr">
         <is>
-          <t>必要な利用者数の組み立て</t>
+          <t>見込量を定めるまでの段階</t>
         </is>
       </c>
       <c r="C45" s="4" t="inlineStr">
@@ -2668,7 +2668,7 @@
       </c>
       <c r="D45" s="4" t="inlineStr">
         <is>
-          <t>加減 / 項目</t>
+          <t>段階 / 何を見るか</t>
         </is>
       </c>
       <c r="E45" s="4" t="inlineStr">
@@ -2680,12 +2680,12 @@
     <row r="46">
       <c r="A46" s="3" t="inlineStr">
         <is>
-          <t>表5-4</t>
+          <t>表5-3</t>
         </is>
       </c>
       <c r="B46" s="3" t="inlineStr">
         <is>
-          <t>訪問系サービスの実績</t>
+          <t>必要な利用者数の組み立て</t>
         </is>
       </c>
       <c r="C46" s="3" t="inlineStr">
@@ -2695,24 +2695,24 @@
       </c>
       <c r="D46" s="3" t="inlineStr">
         <is>
-          <t>サービス種別 / 単位</t>
+          <t>加減 / 項目</t>
         </is>
       </c>
       <c r="E46" s="3" t="inlineStr">
         <is>
-          <t>資料：北塩原村</t>
+          <t>―</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="4" t="inlineStr">
         <is>
-          <t>表5-5</t>
+          <t>表5-4</t>
         </is>
       </c>
       <c r="B47" s="4" t="inlineStr">
         <is>
-          <t>訪問系サービスの見込量</t>
+          <t>訪問系サービスの実績</t>
         </is>
       </c>
       <c r="C47" s="4" t="inlineStr">
@@ -2727,19 +2727,19 @@
       </c>
       <c r="E47" s="4" t="inlineStr">
         <is>
-          <t>―</t>
+          <t>資料：北塩原村</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="3" t="inlineStr">
         <is>
-          <t>表5-6</t>
+          <t>表5-5</t>
         </is>
       </c>
       <c r="B48" s="3" t="inlineStr">
         <is>
-          <t>訪問系サービスの利用がない場合に確かめる事項</t>
+          <t>訪問系サービスの見込量</t>
         </is>
       </c>
       <c r="C48" s="3" t="inlineStr">
@@ -2749,7 +2749,7 @@
       </c>
       <c r="D48" s="3" t="inlineStr">
         <is>
-          <t>確かめる側 / 確かめる事項</t>
+          <t>サービス種別 / 単位</t>
         </is>
       </c>
       <c r="E48" s="3" t="inlineStr">
@@ -2761,12 +2761,12 @@
     <row r="49">
       <c r="A49" s="4" t="inlineStr">
         <is>
-          <t>表5-7</t>
+          <t>表5-6</t>
         </is>
       </c>
       <c r="B49" s="4" t="inlineStr">
         <is>
-          <t>日中活動系サービスの実績</t>
+          <t>訪問系サービスの利用がない場合に確かめる事項</t>
         </is>
       </c>
       <c r="C49" s="4" t="inlineStr">
@@ -2776,24 +2776,24 @@
       </c>
       <c r="D49" s="4" t="inlineStr">
         <is>
-          <t>サービス種別 / 単位</t>
+          <t>確かめる側 / 確かめる事項</t>
         </is>
       </c>
       <c r="E49" s="4" t="inlineStr">
         <is>
-          <t>資料：北塩原村</t>
+          <t>―</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="3" t="inlineStr">
         <is>
-          <t>表5-8</t>
+          <t>表5-7</t>
         </is>
       </c>
       <c r="B50" s="3" t="inlineStr">
         <is>
-          <t>日中活動系サービスの見込量</t>
+          <t>日中活動系サービスの実績</t>
         </is>
       </c>
       <c r="C50" s="3" t="inlineStr">
@@ -2808,19 +2808,19 @@
       </c>
       <c r="E50" s="3" t="inlineStr">
         <is>
-          <t>―</t>
+          <t>資料：北塩原村</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="4" t="inlineStr">
         <is>
-          <t>表5-9</t>
+          <t>表5-8</t>
         </is>
       </c>
       <c r="B51" s="4" t="inlineStr">
         <is>
-          <t>強度行動障害を有する方等の生活介護の利用の見込み</t>
+          <t>日中活動系サービスの見込量</t>
         </is>
       </c>
       <c r="C51" s="4" t="inlineStr">
@@ -2830,7 +2830,7 @@
       </c>
       <c r="D51" s="4" t="inlineStr">
         <is>
-          <t>区分 / 現在の人数</t>
+          <t>サービス種別 / 単位</t>
         </is>
       </c>
       <c r="E51" s="4" t="inlineStr">
@@ -2842,12 +2842,12 @@
     <row r="52">
       <c r="A52" s="3" t="inlineStr">
         <is>
-          <t>表5-10</t>
+          <t>表5-9</t>
         </is>
       </c>
       <c r="B52" s="3" t="inlineStr">
         <is>
-          <t>居住系サービスの実績</t>
+          <t>強度行動障害を有する方等の生活介護の利用の見込み</t>
         </is>
       </c>
       <c r="C52" s="3" t="inlineStr">
@@ -2857,24 +2857,24 @@
       </c>
       <c r="D52" s="3" t="inlineStr">
         <is>
-          <t>サービス種別 / 単位</t>
+          <t>区分 / 現在の人数</t>
         </is>
       </c>
       <c r="E52" s="3" t="inlineStr">
         <is>
-          <t>資料：北塩原村</t>
+          <t>―</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="4" t="inlineStr">
         <is>
-          <t>表5-11</t>
+          <t>表5-10</t>
         </is>
       </c>
       <c r="B53" s="4" t="inlineStr">
         <is>
-          <t>居住系サービスの見込量</t>
+          <t>居住系サービスの実績</t>
         </is>
       </c>
       <c r="C53" s="4" t="inlineStr">
@@ -2889,19 +2889,19 @@
       </c>
       <c r="E53" s="4" t="inlineStr">
         <is>
-          <t>―</t>
+          <t>資料：北塩原村</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" s="3" t="inlineStr">
         <is>
-          <t>表5-12</t>
+          <t>表5-11</t>
         </is>
       </c>
       <c r="B54" s="3" t="inlineStr">
         <is>
-          <t>相談支援の実績</t>
+          <t>居住系サービスの見込量</t>
         </is>
       </c>
       <c r="C54" s="3" t="inlineStr">
@@ -2916,19 +2916,19 @@
       </c>
       <c r="E54" s="3" t="inlineStr">
         <is>
-          <t>資料：北塩原村</t>
+          <t>―</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" s="4" t="inlineStr">
         <is>
-          <t>表5-13</t>
+          <t>表5-12</t>
         </is>
       </c>
       <c r="B55" s="4" t="inlineStr">
         <is>
-          <t>相談支援の見込量</t>
+          <t>相談支援の実績</t>
         </is>
       </c>
       <c r="C55" s="4" t="inlineStr">
@@ -2943,19 +2943,19 @@
       </c>
       <c r="E55" s="4" t="inlineStr">
         <is>
-          <t>―</t>
+          <t>資料：北塩原村</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" s="3" t="inlineStr">
         <is>
-          <t>表5-14</t>
+          <t>表5-13</t>
         </is>
       </c>
       <c r="B56" s="3" t="inlineStr">
         <is>
-          <t>障がい児支援の実績</t>
+          <t>相談支援の見込量</t>
         </is>
       </c>
       <c r="C56" s="3" t="inlineStr">
@@ -2970,19 +2970,19 @@
       </c>
       <c r="E56" s="3" t="inlineStr">
         <is>
-          <t>資料：北塩原村</t>
+          <t>―</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" s="4" t="inlineStr">
         <is>
-          <t>表5-15</t>
+          <t>表5-14</t>
         </is>
       </c>
       <c r="B57" s="4" t="inlineStr">
         <is>
-          <t>障がい児支援の見込量</t>
+          <t>障がい児支援の実績</t>
         </is>
       </c>
       <c r="C57" s="4" t="inlineStr">
@@ -2997,19 +2997,19 @@
       </c>
       <c r="E57" s="4" t="inlineStr">
         <is>
-          <t>―</t>
+          <t>資料：北塩原村</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" s="3" t="inlineStr">
         <is>
-          <t>表5-16</t>
+          <t>表5-15</t>
         </is>
       </c>
       <c r="B58" s="3" t="inlineStr">
         <is>
-          <t>村内に事業所がないサービスの確保の経路</t>
+          <t>障がい児支援の見込量</t>
         </is>
       </c>
       <c r="C58" s="3" t="inlineStr">
@@ -3019,7 +3019,7 @@
       </c>
       <c r="D58" s="3" t="inlineStr">
         <is>
-          <t>サービス / 本村の設置数</t>
+          <t>サービス種別 / 単位</t>
         </is>
       </c>
       <c r="E58" s="3" t="inlineStr">
@@ -3031,12 +3031,12 @@
     <row r="59">
       <c r="A59" s="4" t="inlineStr">
         <is>
-          <t>表5-17</t>
+          <t>表5-16</t>
         </is>
       </c>
       <c r="B59" s="4" t="inlineStr">
         <is>
-          <t>地域生活支援拠点の実績について４町村で揃える定義</t>
+          <t>村内に事業所がないサービスの確保の経路</t>
         </is>
       </c>
       <c r="C59" s="4" t="inlineStr">
@@ -3046,7 +3046,7 @@
       </c>
       <c r="D59" s="4" t="inlineStr">
         <is>
-          <t>記録する事項 / ４町村で揃える定義</t>
+          <t>サービス / 本村の設置数</t>
         </is>
       </c>
       <c r="E59" s="4" t="inlineStr">
@@ -3058,12 +3058,12 @@
     <row r="60">
       <c r="A60" s="3" t="inlineStr">
         <is>
-          <t>表5-18</t>
+          <t>表5-17</t>
         </is>
       </c>
       <c r="B60" s="3" t="inlineStr">
         <is>
-          <t>一般の子育て施策と障がい福祉の切り分け</t>
+          <t>地域生活支援拠点の実績について４町村で揃える定義</t>
         </is>
       </c>
       <c r="C60" s="3" t="inlineStr">
@@ -3073,7 +3073,7 @@
       </c>
       <c r="D60" s="3" t="inlineStr">
         <is>
-          <t>場面 / まず確かめる一般の子育て施策</t>
+          <t>記録する事項 / ４町村で揃える定義</t>
         </is>
       </c>
       <c r="E60" s="3" t="inlineStr">
@@ -3085,12 +3085,12 @@
     <row r="61">
       <c r="A61" s="4" t="inlineStr">
         <is>
-          <t>表5-19</t>
+          <t>表5-18</t>
         </is>
       </c>
       <c r="B61" s="4" t="inlineStr">
         <is>
-          <t>事業所の受入余力について照会する事項</t>
+          <t>一般の子育て施策と障がい福祉の切り分け</t>
         </is>
       </c>
       <c r="C61" s="4" t="inlineStr">
@@ -3100,7 +3100,7 @@
       </c>
       <c r="D61" s="4" t="inlineStr">
         <is>
-          <t>照会する事項 / 確保できる量との関係</t>
+          <t>場面 / まず確かめる一般の子育て施策</t>
         </is>
       </c>
       <c r="E61" s="4" t="inlineStr">
@@ -3112,12 +3112,12 @@
     <row r="62">
       <c r="A62" s="3" t="inlineStr">
         <is>
-          <t>表5-20</t>
+          <t>表5-19</t>
         </is>
       </c>
       <c r="B62" s="3" t="inlineStr">
         <is>
-          <t>緊急時に働く仕組み（４つの場面）</t>
+          <t>事業所の受入余力について照会する事項</t>
         </is>
       </c>
       <c r="C62" s="3" t="inlineStr">
@@ -3127,7 +3127,7 @@
       </c>
       <c r="D62" s="3" t="inlineStr">
         <is>
-          <t>場面 / 想定される事態</t>
+          <t>照会する事項 / 確保できる量との関係</t>
         </is>
       </c>
       <c r="E62" s="3" t="inlineStr">
@@ -3139,12 +3139,12 @@
     <row r="63">
       <c r="A63" s="4" t="inlineStr">
         <is>
-          <t>表5-21</t>
+          <t>表5-20</t>
         </is>
       </c>
       <c r="B63" s="4" t="inlineStr">
         <is>
-          <t>災害時にサービスを止めないための備え</t>
+          <t>緊急時に働く仕組み（４つの場面）</t>
         </is>
       </c>
       <c r="C63" s="4" t="inlineStr">
@@ -3154,7 +3154,7 @@
       </c>
       <c r="D63" s="4" t="inlineStr">
         <is>
-          <t>備える事項 / 本村の取組み</t>
+          <t>場面 / 想定される事態</t>
         </is>
       </c>
       <c r="E63" s="4" t="inlineStr">
@@ -3166,12 +3166,12 @@
     <row r="64">
       <c r="A64" s="3" t="inlineStr">
         <is>
-          <t>表5-22</t>
+          <t>表5-21</t>
         </is>
       </c>
       <c r="B64" s="3" t="inlineStr">
         <is>
-          <t>災害時の情報の伝達について確かめること</t>
+          <t>災害時にサービスを止めないための備え</t>
         </is>
       </c>
       <c r="C64" s="3" t="inlineStr">
@@ -3181,7 +3181,7 @@
       </c>
       <c r="D64" s="3" t="inlineStr">
         <is>
-          <t>確かめること / 確かめ方</t>
+          <t>備える事項 / 本村の取組み</t>
         </is>
       </c>
       <c r="E64" s="3" t="inlineStr">
@@ -3193,12 +3193,12 @@
     <row r="65">
       <c r="A65" s="4" t="inlineStr">
         <is>
-          <t>表5-23</t>
+          <t>表5-22</t>
         </is>
       </c>
       <c r="B65" s="4" t="inlineStr">
         <is>
-          <t>虐待の予防から再発の防止までの流れ</t>
+          <t>災害時の情報の伝達について確かめること</t>
         </is>
       </c>
       <c r="C65" s="4" t="inlineStr">
@@ -3208,7 +3208,7 @@
       </c>
       <c r="D65" s="4" t="inlineStr">
         <is>
-          <t>段階 / 本村の取組み</t>
+          <t>確かめること / 確かめ方</t>
         </is>
       </c>
       <c r="E65" s="4" t="inlineStr">
@@ -3220,12 +3220,12 @@
     <row r="66">
       <c r="A66" s="3" t="inlineStr">
         <is>
-          <t>表5-24</t>
+          <t>表5-23</t>
         </is>
       </c>
       <c r="B66" s="3" t="inlineStr">
         <is>
-          <t>経営基盤に関して把握する事項</t>
+          <t>虐待の予防から再発の防止までの流れ</t>
         </is>
       </c>
       <c r="C66" s="3" t="inlineStr">
@@ -3235,7 +3235,7 @@
       </c>
       <c r="D66" s="3" t="inlineStr">
         <is>
-          <t>把握する事項 / 見込量への影響</t>
+          <t>段階 / 本村の取組み</t>
         </is>
       </c>
       <c r="E66" s="3" t="inlineStr">
@@ -3247,12 +3247,12 @@
     <row r="67">
       <c r="A67" s="4" t="inlineStr">
         <is>
-          <t>表5-25</t>
+          <t>表5-24</t>
         </is>
       </c>
       <c r="B67" s="4" t="inlineStr">
         <is>
-          <t>冬季の支援を検討する三つの段階</t>
+          <t>経営基盤に関して把握する事項</t>
         </is>
       </c>
       <c r="C67" s="4" t="inlineStr">
@@ -3262,7 +3262,7 @@
       </c>
       <c r="D67" s="4" t="inlineStr">
         <is>
-          <t>段階 / 確かめること</t>
+          <t>把握する事項 / 見込量への影響</t>
         </is>
       </c>
       <c r="E67" s="4" t="inlineStr">
@@ -3274,12 +3274,12 @@
     <row r="68">
       <c r="A68" s="3" t="inlineStr">
         <is>
-          <t>表5-26</t>
+          <t>表5-25</t>
         </is>
       </c>
       <c r="B68" s="3" t="inlineStr">
         <is>
-          <t>冬季の通行規制による中断について記録する事項</t>
+          <t>冬季の支援を検討する三つの段階</t>
         </is>
       </c>
       <c r="C68" s="3" t="inlineStr">
@@ -3289,7 +3289,7 @@
       </c>
       <c r="D68" s="3" t="inlineStr">
         <is>
-          <t>記録する事項 / 記録の仕方</t>
+          <t>段階 / 確かめること</t>
         </is>
       </c>
       <c r="E68" s="3" t="inlineStr">
@@ -3301,12 +3301,12 @@
     <row r="69">
       <c r="A69" s="4" t="inlineStr">
         <is>
-          <t>表5-27</t>
+          <t>表5-26</t>
         </is>
       </c>
       <c r="B69" s="4" t="inlineStr">
         <is>
-          <t>医療へのアクセス</t>
+          <t>冬季の通行規制による中断について記録する事項</t>
         </is>
       </c>
       <c r="C69" s="4" t="inlineStr">
@@ -3316,7 +3316,7 @@
       </c>
       <c r="D69" s="4" t="inlineStr">
         <is>
-          <t>場面 / 主な医療資源</t>
+          <t>記録する事項 / 記録の仕方</t>
         </is>
       </c>
       <c r="E69" s="4" t="inlineStr">
@@ -3328,12 +3328,12 @@
     <row r="70">
       <c r="A70" s="3" t="inlineStr">
         <is>
-          <t>表5-28</t>
+          <t>表5-27</t>
         </is>
       </c>
       <c r="B70" s="3" t="inlineStr">
         <is>
-          <t>地域生活支援事業の実績</t>
+          <t>医療へのアクセス</t>
         </is>
       </c>
       <c r="C70" s="3" t="inlineStr">
@@ -3343,24 +3343,24 @@
       </c>
       <c r="D70" s="3" t="inlineStr">
         <is>
-          <t>サービスの種類 / 令和６年度</t>
+          <t>場面 / 主な医療資源</t>
         </is>
       </c>
       <c r="E70" s="3" t="inlineStr">
         <is>
-          <t>資料：北塩原村</t>
+          <t>―</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" s="4" t="inlineStr">
         <is>
-          <t>表5-29</t>
+          <t>表5-28</t>
         </is>
       </c>
       <c r="B71" s="4" t="inlineStr">
         <is>
-          <t>地域生活支援事業の見込量</t>
+          <t>地域生活支援事業の実績</t>
         </is>
       </c>
       <c r="C71" s="4" t="inlineStr">
@@ -3370,24 +3370,24 @@
       </c>
       <c r="D71" s="4" t="inlineStr">
         <is>
-          <t>サービスの種類 / 令和９年度</t>
+          <t>サービスの種類 / 令和６年度</t>
         </is>
       </c>
       <c r="E71" s="4" t="inlineStr">
         <is>
-          <t>―</t>
+          <t>資料：北塩原村</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" s="3" t="inlineStr">
         <is>
-          <t>表5-30</t>
+          <t>表5-29</t>
         </is>
       </c>
       <c r="B72" s="3" t="inlineStr">
         <is>
-          <t>実績がない事業の扱い</t>
+          <t>地域生活支援事業の見込量</t>
         </is>
       </c>
       <c r="C72" s="3" t="inlineStr">
@@ -3397,7 +3397,7 @@
       </c>
       <c r="D72" s="3" t="inlineStr">
         <is>
-          <t>実績がない理由 / 確かめ方</t>
+          <t>サービスの種類 / 令和９年度</t>
         </is>
       </c>
       <c r="E72" s="3" t="inlineStr">
@@ -3409,12 +3409,12 @@
     <row r="73">
       <c r="A73" s="4" t="inlineStr">
         <is>
-          <t>表5-31</t>
+          <t>表5-30</t>
         </is>
       </c>
       <c r="B73" s="4" t="inlineStr">
         <is>
-          <t>地域生活支援事業の実施に必要な事項</t>
+          <t>実績がない事業の扱い</t>
         </is>
       </c>
       <c r="C73" s="4" t="inlineStr">
@@ -3424,7 +3424,7 @@
       </c>
       <c r="D73" s="4" t="inlineStr">
         <is>
-          <t>事項 / 本村の取扱い</t>
+          <t>実績がない理由 / 確かめ方</t>
         </is>
       </c>
       <c r="E73" s="4" t="inlineStr">
@@ -3436,12 +3436,12 @@
     <row r="74">
       <c r="A74" s="3" t="inlineStr">
         <is>
-          <t>表5-32</t>
+          <t>表5-31</t>
         </is>
       </c>
       <c r="B74" s="3" t="inlineStr">
         <is>
-          <t>本人に代わって伝えるための道具の使い分け</t>
+          <t>地域生活支援事業の実施に必要な事項</t>
         </is>
       </c>
       <c r="C74" s="3" t="inlineStr">
@@ -3451,7 +3451,7 @@
       </c>
       <c r="D74" s="3" t="inlineStr">
         <is>
-          <t>道具 / 伝える場面</t>
+          <t>事項 / 本村の取扱い</t>
         </is>
       </c>
       <c r="E74" s="3" t="inlineStr">
@@ -3463,12 +3463,12 @@
     <row r="75">
       <c r="A75" s="4" t="inlineStr">
         <is>
-          <t>表5-33</t>
+          <t>表5-32</t>
         </is>
       </c>
       <c r="B75" s="4" t="inlineStr">
         <is>
-          <t>年齢到達に伴うサービスの移行</t>
+          <t>本人に代わって伝えるための道具の使い分け</t>
         </is>
       </c>
       <c r="C75" s="4" t="inlineStr">
@@ -3478,7 +3478,7 @@
       </c>
       <c r="D75" s="4" t="inlineStr">
         <is>
-          <t>年齢 / 制度上の内容</t>
+          <t>道具 / 伝える場面</t>
         </is>
       </c>
       <c r="E75" s="4" t="inlineStr">
@@ -3490,12 +3490,12 @@
     <row r="76">
       <c r="A76" s="3" t="inlineStr">
         <is>
-          <t>表5-34</t>
+          <t>表5-33</t>
         </is>
       </c>
       <c r="B76" s="3" t="inlineStr">
         <is>
-          <t>学校卒業に伴う移行について確認する事項</t>
+          <t>年齢到達に伴うサービスの移行</t>
         </is>
       </c>
       <c r="C76" s="3" t="inlineStr">
@@ -3505,7 +3505,7 @@
       </c>
       <c r="D76" s="3" t="inlineStr">
         <is>
-          <t>確認する事項 / 見込量への反映</t>
+          <t>年齢 / 制度上の内容</t>
         </is>
       </c>
       <c r="E76" s="3" t="inlineStr">
@@ -3517,12 +3517,12 @@
     <row r="77">
       <c r="A77" s="4" t="inlineStr">
         <is>
-          <t>表5-35</t>
+          <t>表5-34</t>
         </is>
       </c>
       <c r="B77" s="4" t="inlineStr">
         <is>
-          <t>65歳到達時のサービスの区分</t>
+          <t>学校卒業に伴う移行について確認する事項</t>
         </is>
       </c>
       <c r="C77" s="4" t="inlineStr">
@@ -3532,7 +3532,7 @@
       </c>
       <c r="D77" s="4" t="inlineStr">
         <is>
-          <t>区分 / 該当するサービス</t>
+          <t>確認する事項 / 見込量への反映</t>
         </is>
       </c>
       <c r="E77" s="4" t="inlineStr">
@@ -3544,12 +3544,12 @@
     <row r="78">
       <c r="A78" s="3" t="inlineStr">
         <is>
-          <t>表5-36</t>
+          <t>表5-35</t>
         </is>
       </c>
       <c r="B78" s="3" t="inlineStr">
         <is>
-          <t>65歳到達時に確認する事項</t>
+          <t>65歳到達時のサービスの区分</t>
         </is>
       </c>
       <c r="C78" s="3" t="inlineStr">
@@ -3559,7 +3559,7 @@
       </c>
       <c r="D78" s="3" t="inlineStr">
         <is>
-          <t>確認する事項 / 確認の内容</t>
+          <t>区分 / 該当するサービス</t>
         </is>
       </c>
       <c r="E78" s="3" t="inlineStr">
@@ -3571,12 +3571,12 @@
     <row r="79">
       <c r="A79" s="4" t="inlineStr">
         <is>
-          <t>表5-37</t>
+          <t>表5-36</t>
         </is>
       </c>
       <c r="B79" s="4" t="inlineStr">
         <is>
-          <t>65歳到達時の引継ぎの時期と担当</t>
+          <t>65歳到達時に確認する事項</t>
         </is>
       </c>
       <c r="C79" s="4" t="inlineStr">
@@ -3586,7 +3586,7 @@
       </c>
       <c r="D79" s="4" t="inlineStr">
         <is>
-          <t>時期 / 行うこと</t>
+          <t>確認する事項 / 確認の内容</t>
         </is>
       </c>
       <c r="E79" s="4" t="inlineStr">
@@ -3598,12 +3598,12 @@
     <row r="80">
       <c r="A80" s="3" t="inlineStr">
         <is>
-          <t>表5-38</t>
+          <t>表5-37</t>
         </is>
       </c>
       <c r="B80" s="3" t="inlineStr">
         <is>
-          <t>関係機関と連携の内容</t>
+          <t>65歳到達時の引継ぎの時期と担当</t>
         </is>
       </c>
       <c r="C80" s="3" t="inlineStr">
@@ -3613,7 +3613,7 @@
       </c>
       <c r="D80" s="3" t="inlineStr">
         <is>
-          <t>分野 / 関係機関</t>
+          <t>時期 / 行うこと</t>
         </is>
       </c>
       <c r="E80" s="3" t="inlineStr">
@@ -3625,12 +3625,12 @@
     <row r="81">
       <c r="A81" s="4" t="inlineStr">
         <is>
-          <t>表5-39</t>
+          <t>表5-38</t>
         </is>
       </c>
       <c r="B81" s="4" t="inlineStr">
         <is>
-          <t>障がい福祉サービス等に係る給付費の推移</t>
+          <t>関係機関と連携の内容</t>
         </is>
       </c>
       <c r="C81" s="4" t="inlineStr">
@@ -3640,24 +3640,24 @@
       </c>
       <c r="D81" s="4" t="inlineStr">
         <is>
-          <t>年度 / 介護給付費等</t>
+          <t>分野 / 関係機関</t>
         </is>
       </c>
       <c r="E81" s="4" t="inlineStr">
         <is>
-          <t>資料：村提供の障がいサービス給付実績</t>
+          <t>―</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" s="3" t="inlineStr">
         <is>
-          <t>表5-40</t>
+          <t>表5-39</t>
         </is>
       </c>
       <c r="B82" s="3" t="inlineStr">
         <is>
-          <t>財源構成（令和７年度・法定負担割合による試算）</t>
+          <t>障がい福祉サービス等に係る給付費の推移</t>
         </is>
       </c>
       <c r="C82" s="3" t="inlineStr">
@@ -3667,7 +3667,7 @@
       </c>
       <c r="D82" s="3" t="inlineStr">
         <is>
-          <t>区分 / 金額</t>
+          <t>年度 / 介護給付費等</t>
         </is>
       </c>
       <c r="E82" s="3" t="inlineStr">
@@ -3679,12 +3679,12 @@
     <row r="83">
       <c r="A83" s="4" t="inlineStr">
         <is>
-          <t>表5-41</t>
+          <t>表5-40</t>
         </is>
       </c>
       <c r="B83" s="4" t="inlineStr">
         <is>
-          <t>サービス別の給付費と計画上の位置づけ（令和７年度）</t>
+          <t>財源構成（令和７年度・法定負担割合による試算）</t>
         </is>
       </c>
       <c r="C83" s="4" t="inlineStr">
@@ -3694,7 +3694,7 @@
       </c>
       <c r="D83" s="4" t="inlineStr">
         <is>
-          <t>サービス / 給付費（構成比）</t>
+          <t>区分 / 金額</t>
         </is>
       </c>
       <c r="E83" s="4" t="inlineStr">
@@ -3706,39 +3706,39 @@
     <row r="84">
       <c r="A84" s="3" t="inlineStr">
         <is>
-          <t>表6-1</t>
+          <t>表5-41</t>
         </is>
       </c>
       <c r="B84" s="3" t="inlineStr">
         <is>
-          <t>高齢化率の推移</t>
+          <t>サービス別の給付費と計画上の位置づけ（令和７年度）</t>
         </is>
       </c>
       <c r="C84" s="3" t="inlineStr">
         <is>
-          <t>第6章</t>
+          <t>第5章</t>
         </is>
       </c>
       <c r="D84" s="3" t="inlineStr">
         <is>
-          <t>年度 / 高齢化率</t>
+          <t>サービス / 給付費（構成比）</t>
         </is>
       </c>
       <c r="E84" s="3" t="inlineStr">
         <is>
-          <t>資料：北塩原村</t>
+          <t>資料：村提供の障がいサービス給付実績</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" s="4" t="inlineStr">
         <is>
-          <t>表6-2</t>
+          <t>表6-1</t>
         </is>
       </c>
       <c r="B85" s="4" t="inlineStr">
         <is>
-          <t>精神障がい者及び知的障がい者の人数の推移</t>
+          <t>高齢化率の推移</t>
         </is>
       </c>
       <c r="C85" s="4" t="inlineStr">
@@ -3748,7 +3748,7 @@
       </c>
       <c r="D85" s="4" t="inlineStr">
         <is>
-          <t>年度 / 精神障がい者数（※１）</t>
+          <t>年度 / 高齢化率</t>
         </is>
       </c>
       <c r="E85" s="4" t="inlineStr">
@@ -3760,12 +3760,12 @@
     <row r="86">
       <c r="A86" s="3" t="inlineStr">
         <is>
-          <t>表6-3</t>
+          <t>表6-2</t>
         </is>
       </c>
       <c r="B86" s="3" t="inlineStr">
         <is>
-          <t>成年後見制度利用支援事業の利用状況</t>
+          <t>精神障がい者及び知的障がい者の人数の推移</t>
         </is>
       </c>
       <c r="C86" s="3" t="inlineStr">
@@ -3775,7 +3775,7 @@
       </c>
       <c r="D86" s="3" t="inlineStr">
         <is>
-          <t>区分 / 令和５年度</t>
+          <t>年度 / 精神障がい者数（※１）</t>
         </is>
       </c>
       <c r="E86" s="3" t="inlineStr">
@@ -3787,12 +3787,12 @@
     <row r="87">
       <c r="A87" s="4" t="inlineStr">
         <is>
-          <t>表6-4</t>
+          <t>表6-3</t>
         </is>
       </c>
       <c r="B87" s="4" t="inlineStr">
         <is>
-          <t>成年後見制度の利用促進に係る指標</t>
+          <t>成年後見制度利用支援事業の利用状況</t>
         </is>
       </c>
       <c r="C87" s="4" t="inlineStr">
@@ -3802,34 +3802,34 @@
       </c>
       <c r="D87" s="4" t="inlineStr">
         <is>
-          <t>指標 / 何を数えるか</t>
+          <t>区分 / 令和５年度</t>
         </is>
       </c>
       <c r="E87" s="4" t="inlineStr">
         <is>
-          <t>―</t>
+          <t>資料：北塩原村</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" s="3" t="inlineStr">
         <is>
-          <t>表7-1</t>
+          <t>表6-4</t>
         </is>
       </c>
       <c r="B88" s="3" t="inlineStr">
         <is>
-          <t>健康21・グッドヘルスプランとの対応</t>
+          <t>成年後見制度の利用促進に係る指標</t>
         </is>
       </c>
       <c r="C88" s="3" t="inlineStr">
         <is>
-          <t>第7章</t>
+          <t>第6章</t>
         </is>
       </c>
       <c r="D88" s="3" t="inlineStr">
         <is>
-          <t>項目 / 健康21・グッドヘルスプラン</t>
+          <t>指標 / 何を数えるか</t>
         </is>
       </c>
       <c r="E88" s="3" t="inlineStr">
@@ -3841,12 +3841,12 @@
     <row r="89">
       <c r="A89" s="4" t="inlineStr">
         <is>
-          <t>表7-2</t>
+          <t>表7-1</t>
         </is>
       </c>
       <c r="B89" s="4" t="inlineStr">
         <is>
-          <t>第五次総合振興計画における本計画の位置づけ</t>
+          <t>健康21・グッドヘルスプランとの対応</t>
         </is>
       </c>
       <c r="C89" s="4" t="inlineStr">
@@ -3856,7 +3856,7 @@
       </c>
       <c r="D89" s="4" t="inlineStr">
         <is>
-          <t>総合振興計画の位置づけ / 内容</t>
+          <t>項目 / 健康21・グッドヘルスプラン</t>
         </is>
       </c>
       <c r="E89" s="4" t="inlineStr">
@@ -3868,12 +3868,12 @@
     <row r="90">
       <c r="A90" s="3" t="inlineStr">
         <is>
-          <t>表7-3</t>
+          <t>表7-2</t>
         </is>
       </c>
       <c r="B90" s="3" t="inlineStr">
         <is>
-          <t>高齢者福祉計画・介護保険事業計画と重ねて数えないための確認事項</t>
+          <t>第五次総合振興計画における本計画の位置づけ</t>
         </is>
       </c>
       <c r="C90" s="3" t="inlineStr">
@@ -3883,7 +3883,7 @@
       </c>
       <c r="D90" s="3" t="inlineStr">
         <is>
-          <t>事項 / 両計画での扱い</t>
+          <t>総合振興計画の位置づけ / 内容</t>
         </is>
       </c>
       <c r="E90" s="3" t="inlineStr">
@@ -3895,12 +3895,12 @@
     <row r="91">
       <c r="A91" s="4" t="inlineStr">
         <is>
-          <t>表7-4</t>
+          <t>表7-3</t>
         </is>
       </c>
       <c r="B91" s="4" t="inlineStr">
         <is>
-          <t>こども・子育て計画との整合を確かめる事項</t>
+          <t>高齢者福祉計画・介護保険事業計画と重ねて数えないための確認事項</t>
         </is>
       </c>
       <c r="C91" s="4" t="inlineStr">
@@ -3910,7 +3910,7 @@
       </c>
       <c r="D91" s="4" t="inlineStr">
         <is>
-          <t>確かめる事項 / 確かめ方</t>
+          <t>事項 / 両計画での扱い</t>
         </is>
       </c>
       <c r="E91" s="4" t="inlineStr">
@@ -3922,22 +3922,22 @@
     <row r="92">
       <c r="A92" s="3" t="inlineStr">
         <is>
-          <t>表8-1</t>
+          <t>表7-4</t>
         </is>
       </c>
       <c r="B92" s="3" t="inlineStr">
         <is>
-          <t>北塩原村障がい者自立支援協議会委員名簿</t>
+          <t>こども・子育て計画との整合を確かめる事項</t>
         </is>
       </c>
       <c r="C92" s="3" t="inlineStr">
         <is>
-          <t>第8章</t>
+          <t>第7章</t>
         </is>
       </c>
       <c r="D92" s="3" t="inlineStr">
         <is>
-          <t>区　分 / 氏　名</t>
+          <t>確かめる事項 / 確かめ方</t>
         </is>
       </c>
       <c r="E92" s="3" t="inlineStr">
@@ -3949,12 +3949,12 @@
     <row r="93">
       <c r="A93" s="4" t="inlineStr">
         <is>
-          <t>表8-2</t>
+          <t>表8-1</t>
         </is>
       </c>
       <c r="B93" s="4" t="inlineStr">
         <is>
-          <t>計画の策定経過</t>
+          <t>北塩原村障がい者自立支援協議会委員名簿</t>
         </is>
       </c>
       <c r="C93" s="4" t="inlineStr">
@@ -3964,7 +3964,7 @@
       </c>
       <c r="D93" s="4" t="inlineStr">
         <is>
-          <t>年月日 / 内容</t>
+          <t>区　分 / 氏　名</t>
         </is>
       </c>
       <c r="E93" s="4" t="inlineStr">
@@ -3976,12 +3976,12 @@
     <row r="94">
       <c r="A94" s="3" t="inlineStr">
         <is>
-          <t>表8-3</t>
+          <t>表8-2</t>
         </is>
       </c>
       <c r="B94" s="3" t="inlineStr">
         <is>
-          <t>近年の障がい者施策の動向</t>
+          <t>計画の策定経過</t>
         </is>
       </c>
       <c r="C94" s="3" t="inlineStr">
@@ -3991,7 +3991,7 @@
       </c>
       <c r="D94" s="3" t="inlineStr">
         <is>
-          <t>年 / 主な動向</t>
+          <t>年月日 / 内容</t>
         </is>
       </c>
       <c r="E94" s="3" t="inlineStr">
@@ -4003,25 +4003,52 @@
     <row r="95">
       <c r="A95" s="4" t="inlineStr">
         <is>
+          <t>表8-3</t>
+        </is>
+      </c>
+      <c r="B95" s="4" t="inlineStr">
+        <is>
+          <t>近年の障がい者施策の動向</t>
+        </is>
+      </c>
+      <c r="C95" s="4" t="inlineStr">
+        <is>
+          <t>第8章</t>
+        </is>
+      </c>
+      <c r="D95" s="4" t="inlineStr">
+        <is>
+          <t>年 / 主な動向</t>
+        </is>
+      </c>
+      <c r="E95" s="4" t="inlineStr">
+        <is>
+          <t>―</t>
+        </is>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" s="3" t="inlineStr">
+        <is>
           <t>表8-4</t>
         </is>
       </c>
-      <c r="B95" s="4" t="inlineStr">
+      <c r="B96" s="3" t="inlineStr">
         <is>
           <t>用語解説</t>
         </is>
       </c>
-      <c r="C95" s="4" t="inlineStr">
+      <c r="C96" s="3" t="inlineStr">
         <is>
           <t>第8章</t>
         </is>
       </c>
-      <c r="D95" s="4" t="inlineStr">
+      <c r="D96" s="3" t="inlineStr">
         <is>
           <t>用語 / 説明</t>
         </is>
       </c>
-      <c r="E95" s="4" t="inlineStr">
+      <c r="E96" s="3" t="inlineStr">
         <is>
           <t>―</t>
         </is>

--- a/output/北塩原村_図表番号一覧.xlsx
+++ b/output/北塩原村_図表番号一覧.xlsx
@@ -535,7 +535,7 @@
       </c>
       <c r="B6" s="3" t="inlineStr">
         <is>
-          <t>図26点・表91点に章ごとの通し番号を振った（図１-１・表１-１の形）。注記ボックス（【村へ確認】等の1×1の枠）45点には振っていない。確定時に削るため、番号を振ると欠番が出るからである。</t>
+          <t>図26点・表92点に章ごとの通し番号を振った（図１-１・表１-１の形）。注記ボックス（【村へ確認】等の1×1の枠）45点には振っていない。確定時に削るため、番号を振ると欠番が出るからである。</t>
         </is>
       </c>
     </row>
@@ -1542,7 +1542,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E96"/>
+  <dimension ref="A1:E97"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -1555,7 +1555,7 @@
     <row r="1" ht="30" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>表 91点</t>
+          <t>表 92点</t>
         </is>
       </c>
     </row>
@@ -3576,7 +3576,7 @@
       </c>
       <c r="B79" s="4" t="inlineStr">
         <is>
-          <t>65歳到達時に確認する事項</t>
+          <t>事業所の指定の形と65歳到達後の続け方</t>
         </is>
       </c>
       <c r="C79" s="4" t="inlineStr">
@@ -3586,7 +3586,7 @@
       </c>
       <c r="D79" s="4" t="inlineStr">
         <is>
-          <t>確認する事項 / 確認の内容</t>
+          <t>いま利用している事業所の指定の形 / 65歳に達した後の続け方</t>
         </is>
       </c>
       <c r="E79" s="4" t="inlineStr">
@@ -3603,7 +3603,7 @@
       </c>
       <c r="B80" s="3" t="inlineStr">
         <is>
-          <t>65歳到達時の引継ぎの時期と担当</t>
+          <t>65歳到達時に確認する事項</t>
         </is>
       </c>
       <c r="C80" s="3" t="inlineStr">
@@ -3613,7 +3613,7 @@
       </c>
       <c r="D80" s="3" t="inlineStr">
         <is>
-          <t>時期 / 行うこと</t>
+          <t>確認する事項 / 確認の内容</t>
         </is>
       </c>
       <c r="E80" s="3" t="inlineStr">
@@ -3630,7 +3630,7 @@
       </c>
       <c r="B81" s="4" t="inlineStr">
         <is>
-          <t>関係機関と連携の内容</t>
+          <t>65歳到達時の引継ぎの時期と担当</t>
         </is>
       </c>
       <c r="C81" s="4" t="inlineStr">
@@ -3640,7 +3640,7 @@
       </c>
       <c r="D81" s="4" t="inlineStr">
         <is>
-          <t>分野 / 関係機関</t>
+          <t>時期 / 行うこと</t>
         </is>
       </c>
       <c r="E81" s="4" t="inlineStr">
@@ -3657,7 +3657,7 @@
       </c>
       <c r="B82" s="3" t="inlineStr">
         <is>
-          <t>障がい福祉サービス等に係る給付費の推移</t>
+          <t>関係機関と連携の内容</t>
         </is>
       </c>
       <c r="C82" s="3" t="inlineStr">
@@ -3667,12 +3667,12 @@
       </c>
       <c r="D82" s="3" t="inlineStr">
         <is>
-          <t>年度 / 介護給付費等</t>
+          <t>分野 / 関係機関</t>
         </is>
       </c>
       <c r="E82" s="3" t="inlineStr">
         <is>
-          <t>資料：村提供の障がいサービス給付実績</t>
+          <t>―</t>
         </is>
       </c>
     </row>
@@ -3684,7 +3684,7 @@
       </c>
       <c r="B83" s="4" t="inlineStr">
         <is>
-          <t>財源構成（令和７年度・法定負担割合による試算）</t>
+          <t>障がい福祉サービス等に係る給付費の推移</t>
         </is>
       </c>
       <c r="C83" s="4" t="inlineStr">
@@ -3694,7 +3694,7 @@
       </c>
       <c r="D83" s="4" t="inlineStr">
         <is>
-          <t>区分 / 金額</t>
+          <t>年度 / 介護給付費等</t>
         </is>
       </c>
       <c r="E83" s="4" t="inlineStr">
@@ -3711,7 +3711,7 @@
       </c>
       <c r="B84" s="3" t="inlineStr">
         <is>
-          <t>サービス別の給付費と計画上の位置づけ（令和７年度）</t>
+          <t>財源構成（令和７年度・法定負担割合による試算）</t>
         </is>
       </c>
       <c r="C84" s="3" t="inlineStr">
@@ -3721,7 +3721,7 @@
       </c>
       <c r="D84" s="3" t="inlineStr">
         <is>
-          <t>サービス / 給付費（構成比）</t>
+          <t>区分 / 金額</t>
         </is>
       </c>
       <c r="E84" s="3" t="inlineStr">
@@ -3733,39 +3733,39 @@
     <row r="85">
       <c r="A85" s="4" t="inlineStr">
         <is>
-          <t>表6-1</t>
+          <t>表5-42</t>
         </is>
       </c>
       <c r="B85" s="4" t="inlineStr">
         <is>
-          <t>高齢化率の推移</t>
+          <t>サービス別の給付費と計画上の位置づけ（令和７年度）</t>
         </is>
       </c>
       <c r="C85" s="4" t="inlineStr">
         <is>
-          <t>第6章</t>
+          <t>第5章</t>
         </is>
       </c>
       <c r="D85" s="4" t="inlineStr">
         <is>
-          <t>年度 / 高齢化率</t>
+          <t>サービス / 給付費（構成比）</t>
         </is>
       </c>
       <c r="E85" s="4" t="inlineStr">
         <is>
-          <t>資料：北塩原村</t>
+          <t>資料：村提供の障がいサービス給付実績</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" s="3" t="inlineStr">
         <is>
-          <t>表6-2</t>
+          <t>表6-1</t>
         </is>
       </c>
       <c r="B86" s="3" t="inlineStr">
         <is>
-          <t>精神障がい者及び知的障がい者の人数の推移</t>
+          <t>高齢化率の推移</t>
         </is>
       </c>
       <c r="C86" s="3" t="inlineStr">
@@ -3775,7 +3775,7 @@
       </c>
       <c r="D86" s="3" t="inlineStr">
         <is>
-          <t>年度 / 精神障がい者数（※１）</t>
+          <t>年度 / 高齢化率</t>
         </is>
       </c>
       <c r="E86" s="3" t="inlineStr">
@@ -3787,12 +3787,12 @@
     <row r="87">
       <c r="A87" s="4" t="inlineStr">
         <is>
-          <t>表6-3</t>
+          <t>表6-2</t>
         </is>
       </c>
       <c r="B87" s="4" t="inlineStr">
         <is>
-          <t>成年後見制度利用支援事業の利用状況</t>
+          <t>精神障がい者及び知的障がい者の人数の推移</t>
         </is>
       </c>
       <c r="C87" s="4" t="inlineStr">
@@ -3802,7 +3802,7 @@
       </c>
       <c r="D87" s="4" t="inlineStr">
         <is>
-          <t>区分 / 令和５年度</t>
+          <t>年度 / 精神障がい者数（※１）</t>
         </is>
       </c>
       <c r="E87" s="4" t="inlineStr">
@@ -3814,12 +3814,12 @@
     <row r="88">
       <c r="A88" s="3" t="inlineStr">
         <is>
-          <t>表6-4</t>
+          <t>表6-3</t>
         </is>
       </c>
       <c r="B88" s="3" t="inlineStr">
         <is>
-          <t>成年後見制度の利用促進に係る指標</t>
+          <t>成年後見制度利用支援事業の利用状況</t>
         </is>
       </c>
       <c r="C88" s="3" t="inlineStr">
@@ -3829,34 +3829,34 @@
       </c>
       <c r="D88" s="3" t="inlineStr">
         <is>
-          <t>指標 / 何を数えるか</t>
+          <t>区分 / 令和５年度</t>
         </is>
       </c>
       <c r="E88" s="3" t="inlineStr">
         <is>
-          <t>―</t>
+          <t>資料：北塩原村</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" s="4" t="inlineStr">
         <is>
-          <t>表7-1</t>
+          <t>表6-4</t>
         </is>
       </c>
       <c r="B89" s="4" t="inlineStr">
         <is>
-          <t>健康21・グッドヘルスプランとの対応</t>
+          <t>成年後見制度の利用促進に係る指標</t>
         </is>
       </c>
       <c r="C89" s="4" t="inlineStr">
         <is>
-          <t>第7章</t>
+          <t>第6章</t>
         </is>
       </c>
       <c r="D89" s="4" t="inlineStr">
         <is>
-          <t>項目 / 健康21・グッドヘルスプラン</t>
+          <t>指標 / 何を数えるか</t>
         </is>
       </c>
       <c r="E89" s="4" t="inlineStr">
@@ -3868,12 +3868,12 @@
     <row r="90">
       <c r="A90" s="3" t="inlineStr">
         <is>
-          <t>表7-2</t>
+          <t>表7-1</t>
         </is>
       </c>
       <c r="B90" s="3" t="inlineStr">
         <is>
-          <t>第五次総合振興計画における本計画の位置づけ</t>
+          <t>健康21・グッドヘルスプランとの対応</t>
         </is>
       </c>
       <c r="C90" s="3" t="inlineStr">
@@ -3883,7 +3883,7 @@
       </c>
       <c r="D90" s="3" t="inlineStr">
         <is>
-          <t>総合振興計画の位置づけ / 内容</t>
+          <t>項目 / 健康21・グッドヘルスプラン</t>
         </is>
       </c>
       <c r="E90" s="3" t="inlineStr">
@@ -3895,12 +3895,12 @@
     <row r="91">
       <c r="A91" s="4" t="inlineStr">
         <is>
-          <t>表7-3</t>
+          <t>表7-2</t>
         </is>
       </c>
       <c r="B91" s="4" t="inlineStr">
         <is>
-          <t>高齢者福祉計画・介護保険事業計画と重ねて数えないための確認事項</t>
+          <t>第五次総合振興計画における本計画の位置づけ</t>
         </is>
       </c>
       <c r="C91" s="4" t="inlineStr">
@@ -3910,7 +3910,7 @@
       </c>
       <c r="D91" s="4" t="inlineStr">
         <is>
-          <t>事項 / 両計画での扱い</t>
+          <t>総合振興計画の位置づけ / 内容</t>
         </is>
       </c>
       <c r="E91" s="4" t="inlineStr">
@@ -3922,12 +3922,12 @@
     <row r="92">
       <c r="A92" s="3" t="inlineStr">
         <is>
-          <t>表7-4</t>
+          <t>表7-3</t>
         </is>
       </c>
       <c r="B92" s="3" t="inlineStr">
         <is>
-          <t>こども・子育て計画との整合を確かめる事項</t>
+          <t>高齢者福祉計画・介護保険事業計画と重ねて数えないための確認事項</t>
         </is>
       </c>
       <c r="C92" s="3" t="inlineStr">
@@ -3937,7 +3937,7 @@
       </c>
       <c r="D92" s="3" t="inlineStr">
         <is>
-          <t>確かめる事項 / 確かめ方</t>
+          <t>事項 / 両計画での扱い</t>
         </is>
       </c>
       <c r="E92" s="3" t="inlineStr">
@@ -3949,22 +3949,22 @@
     <row r="93">
       <c r="A93" s="4" t="inlineStr">
         <is>
-          <t>表8-1</t>
+          <t>表7-4</t>
         </is>
       </c>
       <c r="B93" s="4" t="inlineStr">
         <is>
-          <t>北塩原村障がい者自立支援協議会委員名簿</t>
+          <t>こども・子育て計画との整合を確かめる事項</t>
         </is>
       </c>
       <c r="C93" s="4" t="inlineStr">
         <is>
-          <t>第8章</t>
+          <t>第7章</t>
         </is>
       </c>
       <c r="D93" s="4" t="inlineStr">
         <is>
-          <t>区　分 / 氏　名</t>
+          <t>確かめる事項 / 確かめ方</t>
         </is>
       </c>
       <c r="E93" s="4" t="inlineStr">
@@ -3976,12 +3976,12 @@
     <row r="94">
       <c r="A94" s="3" t="inlineStr">
         <is>
-          <t>表8-2</t>
+          <t>表8-1</t>
         </is>
       </c>
       <c r="B94" s="3" t="inlineStr">
         <is>
-          <t>計画の策定経過</t>
+          <t>北塩原村障がい者自立支援協議会委員名簿</t>
         </is>
       </c>
       <c r="C94" s="3" t="inlineStr">
@@ -3991,7 +3991,7 @@
       </c>
       <c r="D94" s="3" t="inlineStr">
         <is>
-          <t>年月日 / 内容</t>
+          <t>区　分 / 氏　名</t>
         </is>
       </c>
       <c r="E94" s="3" t="inlineStr">
@@ -4003,12 +4003,12 @@
     <row r="95">
       <c r="A95" s="4" t="inlineStr">
         <is>
-          <t>表8-3</t>
+          <t>表8-2</t>
         </is>
       </c>
       <c r="B95" s="4" t="inlineStr">
         <is>
-          <t>近年の障がい者施策の動向</t>
+          <t>計画の策定経過</t>
         </is>
       </c>
       <c r="C95" s="4" t="inlineStr">
@@ -4018,7 +4018,7 @@
       </c>
       <c r="D95" s="4" t="inlineStr">
         <is>
-          <t>年 / 主な動向</t>
+          <t>年月日 / 内容</t>
         </is>
       </c>
       <c r="E95" s="4" t="inlineStr">
@@ -4030,25 +4030,52 @@
     <row r="96">
       <c r="A96" s="3" t="inlineStr">
         <is>
+          <t>表8-3</t>
+        </is>
+      </c>
+      <c r="B96" s="3" t="inlineStr">
+        <is>
+          <t>近年の障がい者施策の動向</t>
+        </is>
+      </c>
+      <c r="C96" s="3" t="inlineStr">
+        <is>
+          <t>第8章</t>
+        </is>
+      </c>
+      <c r="D96" s="3" t="inlineStr">
+        <is>
+          <t>年 / 主な動向</t>
+        </is>
+      </c>
+      <c r="E96" s="3" t="inlineStr">
+        <is>
+          <t>―</t>
+        </is>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" s="4" t="inlineStr">
+        <is>
           <t>表8-4</t>
         </is>
       </c>
-      <c r="B96" s="3" t="inlineStr">
+      <c r="B97" s="4" t="inlineStr">
         <is>
           <t>用語解説</t>
         </is>
       </c>
-      <c r="C96" s="3" t="inlineStr">
+      <c r="C97" s="4" t="inlineStr">
         <is>
           <t>第8章</t>
         </is>
       </c>
-      <c r="D96" s="3" t="inlineStr">
+      <c r="D97" s="4" t="inlineStr">
         <is>
           <t>用語 / 説明</t>
         </is>
       </c>
-      <c r="E96" s="3" t="inlineStr">
+      <c r="E97" s="4" t="inlineStr">
         <is>
           <t>―</t>
         </is>

--- a/output/北塩原村_図表番号一覧.xlsx
+++ b/output/北塩原村_図表番号一覧.xlsx
@@ -535,7 +535,7 @@
       </c>
       <c r="B6" s="3" t="inlineStr">
         <is>
-          <t>図26点・表92点に章ごとの通し番号を振った（図１-１・表１-１の形）。注記ボックス（【村へ確認】等の1×1の枠）45点には振っていない。確定時に削るため、番号を振ると欠番が出るからである。</t>
+          <t>図26点・表93点に章ごとの通し番号を振った（図１-１・表１-１の形）。注記ボックス（【村へ確認】等の1×1の枠）45点には振っていない。確定時に削るため、番号を振ると欠番が出るからである。</t>
         </is>
       </c>
     </row>
@@ -607,7 +607,7 @@
       </c>
       <c r="B12" s="3" t="inlineStr">
         <is>
-          <t>出所は、村の実績・アンケート・外部資料から数値を引いた図表43点にのみ付けた。手順・区分・確認事項を整理しただけの表は本計画の記述そのものであり、出所を書くと出どころが二重になるためである（規約への補足1件）。</t>
+          <t>出所は、村の実績・アンケート・外部資料から数値を引いた図表44点にのみ付けた。手順・区分・確認事項を整理しただけの表は本計画の記述そのものであり、出所を書くと出どころが二重になるためである（規約への補足1件）。</t>
         </is>
       </c>
     </row>
@@ -1542,7 +1542,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E97"/>
+  <dimension ref="A1:E98"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -1555,7 +1555,7 @@
     <row r="1" ht="30" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>表 92点</t>
+          <t>表 93点</t>
         </is>
       </c>
     </row>
@@ -3063,7 +3063,7 @@
       </c>
       <c r="B60" s="3" t="inlineStr">
         <is>
-          <t>地域生活支援拠点の実績について４町村で揃える定義</t>
+          <t>高次脳機能障がいと似た状態の切り分けと相談をつなぐ先</t>
         </is>
       </c>
       <c r="C60" s="3" t="inlineStr">
@@ -3073,12 +3073,12 @@
       </c>
       <c r="D60" s="3" t="inlineStr">
         <is>
-          <t>記録する事項 / ４町村で揃える定義</t>
+          <t>区分 / 施行令での扱い</t>
         </is>
       </c>
       <c r="E60" s="3" t="inlineStr">
         <is>
-          <t>―</t>
+          <t>資料：高次脳機能障害者支援法施行令（令和８年政令第60号）第１条により作成</t>
         </is>
       </c>
     </row>
@@ -3090,7 +3090,7 @@
       </c>
       <c r="B61" s="4" t="inlineStr">
         <is>
-          <t>一般の子育て施策と障がい福祉の切り分け</t>
+          <t>地域生活支援拠点の実績について４町村で揃える定義</t>
         </is>
       </c>
       <c r="C61" s="4" t="inlineStr">
@@ -3100,7 +3100,7 @@
       </c>
       <c r="D61" s="4" t="inlineStr">
         <is>
-          <t>場面 / まず確かめる一般の子育て施策</t>
+          <t>記録する事項 / ４町村で揃える定義</t>
         </is>
       </c>
       <c r="E61" s="4" t="inlineStr">
@@ -3117,7 +3117,7 @@
       </c>
       <c r="B62" s="3" t="inlineStr">
         <is>
-          <t>事業所の受入余力について照会する事項</t>
+          <t>一般の子育て施策と障がい福祉の切り分け</t>
         </is>
       </c>
       <c r="C62" s="3" t="inlineStr">
@@ -3127,7 +3127,7 @@
       </c>
       <c r="D62" s="3" t="inlineStr">
         <is>
-          <t>照会する事項 / 確保できる量との関係</t>
+          <t>場面 / まず確かめる一般の子育て施策</t>
         </is>
       </c>
       <c r="E62" s="3" t="inlineStr">
@@ -3144,7 +3144,7 @@
       </c>
       <c r="B63" s="4" t="inlineStr">
         <is>
-          <t>緊急時に働く仕組み（４つの場面）</t>
+          <t>事業所の受入余力について照会する事項</t>
         </is>
       </c>
       <c r="C63" s="4" t="inlineStr">
@@ -3154,7 +3154,7 @@
       </c>
       <c r="D63" s="4" t="inlineStr">
         <is>
-          <t>場面 / 想定される事態</t>
+          <t>照会する事項 / 確保できる量との関係</t>
         </is>
       </c>
       <c r="E63" s="4" t="inlineStr">
@@ -3171,7 +3171,7 @@
       </c>
       <c r="B64" s="3" t="inlineStr">
         <is>
-          <t>災害時にサービスを止めないための備え</t>
+          <t>緊急時に働く仕組み（４つの場面）</t>
         </is>
       </c>
       <c r="C64" s="3" t="inlineStr">
@@ -3181,7 +3181,7 @@
       </c>
       <c r="D64" s="3" t="inlineStr">
         <is>
-          <t>備える事項 / 本村の取組み</t>
+          <t>場面 / 想定される事態</t>
         </is>
       </c>
       <c r="E64" s="3" t="inlineStr">
@@ -3198,7 +3198,7 @@
       </c>
       <c r="B65" s="4" t="inlineStr">
         <is>
-          <t>災害時の情報の伝達について確かめること</t>
+          <t>災害時にサービスを止めないための備え</t>
         </is>
       </c>
       <c r="C65" s="4" t="inlineStr">
@@ -3208,7 +3208,7 @@
       </c>
       <c r="D65" s="4" t="inlineStr">
         <is>
-          <t>確かめること / 確かめ方</t>
+          <t>備える事項 / 本村の取組み</t>
         </is>
       </c>
       <c r="E65" s="4" t="inlineStr">
@@ -3225,7 +3225,7 @@
       </c>
       <c r="B66" s="3" t="inlineStr">
         <is>
-          <t>虐待の予防から再発の防止までの流れ</t>
+          <t>災害時の情報の伝達について確かめること</t>
         </is>
       </c>
       <c r="C66" s="3" t="inlineStr">
@@ -3235,7 +3235,7 @@
       </c>
       <c r="D66" s="3" t="inlineStr">
         <is>
-          <t>段階 / 本村の取組み</t>
+          <t>確かめること / 確かめ方</t>
         </is>
       </c>
       <c r="E66" s="3" t="inlineStr">
@@ -3252,7 +3252,7 @@
       </c>
       <c r="B67" s="4" t="inlineStr">
         <is>
-          <t>経営基盤に関して把握する事項</t>
+          <t>虐待の予防から再発の防止までの流れ</t>
         </is>
       </c>
       <c r="C67" s="4" t="inlineStr">
@@ -3262,7 +3262,7 @@
       </c>
       <c r="D67" s="4" t="inlineStr">
         <is>
-          <t>把握する事項 / 見込量への影響</t>
+          <t>段階 / 本村の取組み</t>
         </is>
       </c>
       <c r="E67" s="4" t="inlineStr">
@@ -3279,7 +3279,7 @@
       </c>
       <c r="B68" s="3" t="inlineStr">
         <is>
-          <t>冬季の支援を検討する三つの段階</t>
+          <t>経営基盤に関して把握する事項</t>
         </is>
       </c>
       <c r="C68" s="3" t="inlineStr">
@@ -3289,7 +3289,7 @@
       </c>
       <c r="D68" s="3" t="inlineStr">
         <is>
-          <t>段階 / 確かめること</t>
+          <t>把握する事項 / 見込量への影響</t>
         </is>
       </c>
       <c r="E68" s="3" t="inlineStr">
@@ -3306,7 +3306,7 @@
       </c>
       <c r="B69" s="4" t="inlineStr">
         <is>
-          <t>冬季の通行規制による中断について記録する事項</t>
+          <t>冬季の支援を検討する三つの段階</t>
         </is>
       </c>
       <c r="C69" s="4" t="inlineStr">
@@ -3316,7 +3316,7 @@
       </c>
       <c r="D69" s="4" t="inlineStr">
         <is>
-          <t>記録する事項 / 記録の仕方</t>
+          <t>段階 / 確かめること</t>
         </is>
       </c>
       <c r="E69" s="4" t="inlineStr">
@@ -3333,7 +3333,7 @@
       </c>
       <c r="B70" s="3" t="inlineStr">
         <is>
-          <t>医療へのアクセス</t>
+          <t>冬季の通行規制による中断について記録する事項</t>
         </is>
       </c>
       <c r="C70" s="3" t="inlineStr">
@@ -3343,7 +3343,7 @@
       </c>
       <c r="D70" s="3" t="inlineStr">
         <is>
-          <t>場面 / 主な医療資源</t>
+          <t>記録する事項 / 記録の仕方</t>
         </is>
       </c>
       <c r="E70" s="3" t="inlineStr">
@@ -3360,7 +3360,7 @@
       </c>
       <c r="B71" s="4" t="inlineStr">
         <is>
-          <t>地域生活支援事業の実績</t>
+          <t>医療へのアクセス</t>
         </is>
       </c>
       <c r="C71" s="4" t="inlineStr">
@@ -3370,12 +3370,12 @@
       </c>
       <c r="D71" s="4" t="inlineStr">
         <is>
-          <t>サービスの種類 / 令和６年度</t>
+          <t>場面 / 主な医療資源</t>
         </is>
       </c>
       <c r="E71" s="4" t="inlineStr">
         <is>
-          <t>資料：北塩原村</t>
+          <t>―</t>
         </is>
       </c>
     </row>
@@ -3387,7 +3387,7 @@
       </c>
       <c r="B72" s="3" t="inlineStr">
         <is>
-          <t>地域生活支援事業の見込量</t>
+          <t>地域生活支援事業の実績</t>
         </is>
       </c>
       <c r="C72" s="3" t="inlineStr">
@@ -3397,12 +3397,12 @@
       </c>
       <c r="D72" s="3" t="inlineStr">
         <is>
-          <t>サービスの種類 / 令和９年度</t>
+          <t>サービスの種類 / 令和６年度</t>
         </is>
       </c>
       <c r="E72" s="3" t="inlineStr">
         <is>
-          <t>―</t>
+          <t>資料：北塩原村</t>
         </is>
       </c>
     </row>
@@ -3414,7 +3414,7 @@
       </c>
       <c r="B73" s="4" t="inlineStr">
         <is>
-          <t>実績がない事業の扱い</t>
+          <t>地域生活支援事業の見込量</t>
         </is>
       </c>
       <c r="C73" s="4" t="inlineStr">
@@ -3424,7 +3424,7 @@
       </c>
       <c r="D73" s="4" t="inlineStr">
         <is>
-          <t>実績がない理由 / 確かめ方</t>
+          <t>サービスの種類 / 令和９年度</t>
         </is>
       </c>
       <c r="E73" s="4" t="inlineStr">
@@ -3441,7 +3441,7 @@
       </c>
       <c r="B74" s="3" t="inlineStr">
         <is>
-          <t>地域生活支援事業の実施に必要な事項</t>
+          <t>実績がない事業の扱い</t>
         </is>
       </c>
       <c r="C74" s="3" t="inlineStr">
@@ -3451,7 +3451,7 @@
       </c>
       <c r="D74" s="3" t="inlineStr">
         <is>
-          <t>事項 / 本村の取扱い</t>
+          <t>実績がない理由 / 確かめ方</t>
         </is>
       </c>
       <c r="E74" s="3" t="inlineStr">
@@ -3468,7 +3468,7 @@
       </c>
       <c r="B75" s="4" t="inlineStr">
         <is>
-          <t>本人に代わって伝えるための道具の使い分け</t>
+          <t>地域生活支援事業の実施に必要な事項</t>
         </is>
       </c>
       <c r="C75" s="4" t="inlineStr">
@@ -3478,7 +3478,7 @@
       </c>
       <c r="D75" s="4" t="inlineStr">
         <is>
-          <t>道具 / 伝える場面</t>
+          <t>事項 / 本村の取扱い</t>
         </is>
       </c>
       <c r="E75" s="4" t="inlineStr">
@@ -3495,7 +3495,7 @@
       </c>
       <c r="B76" s="3" t="inlineStr">
         <is>
-          <t>年齢到達に伴うサービスの移行</t>
+          <t>本人に代わって伝えるための道具の使い分け</t>
         </is>
       </c>
       <c r="C76" s="3" t="inlineStr">
@@ -3505,7 +3505,7 @@
       </c>
       <c r="D76" s="3" t="inlineStr">
         <is>
-          <t>年齢 / 制度上の内容</t>
+          <t>道具 / 伝える場面</t>
         </is>
       </c>
       <c r="E76" s="3" t="inlineStr">
@@ -3522,7 +3522,7 @@
       </c>
       <c r="B77" s="4" t="inlineStr">
         <is>
-          <t>学校卒業に伴う移行について確認する事項</t>
+          <t>年齢到達に伴うサービスの移行</t>
         </is>
       </c>
       <c r="C77" s="4" t="inlineStr">
@@ -3532,7 +3532,7 @@
       </c>
       <c r="D77" s="4" t="inlineStr">
         <is>
-          <t>確認する事項 / 見込量への反映</t>
+          <t>年齢 / 制度上の内容</t>
         </is>
       </c>
       <c r="E77" s="4" t="inlineStr">
@@ -3549,7 +3549,7 @@
       </c>
       <c r="B78" s="3" t="inlineStr">
         <is>
-          <t>65歳到達時のサービスの区分</t>
+          <t>学校卒業に伴う移行について確認する事項</t>
         </is>
       </c>
       <c r="C78" s="3" t="inlineStr">
@@ -3559,7 +3559,7 @@
       </c>
       <c r="D78" s="3" t="inlineStr">
         <is>
-          <t>区分 / 該当するサービス</t>
+          <t>確認する事項 / 見込量への反映</t>
         </is>
       </c>
       <c r="E78" s="3" t="inlineStr">
@@ -3576,7 +3576,7 @@
       </c>
       <c r="B79" s="4" t="inlineStr">
         <is>
-          <t>事業所の指定の形と65歳到達後の続け方</t>
+          <t>65歳到達時のサービスの区分</t>
         </is>
       </c>
       <c r="C79" s="4" t="inlineStr">
@@ -3586,7 +3586,7 @@
       </c>
       <c r="D79" s="4" t="inlineStr">
         <is>
-          <t>いま利用している事業所の指定の形 / 65歳に達した後の続け方</t>
+          <t>区分 / 該当するサービス</t>
         </is>
       </c>
       <c r="E79" s="4" t="inlineStr">
@@ -3603,7 +3603,7 @@
       </c>
       <c r="B80" s="3" t="inlineStr">
         <is>
-          <t>65歳到達時に確認する事項</t>
+          <t>事業所の指定の形と65歳到達後の続け方</t>
         </is>
       </c>
       <c r="C80" s="3" t="inlineStr">
@@ -3613,7 +3613,7 @@
       </c>
       <c r="D80" s="3" t="inlineStr">
         <is>
-          <t>確認する事項 / 確認の内容</t>
+          <t>いま利用している事業所の指定の形 / 65歳に達した後の続け方</t>
         </is>
       </c>
       <c r="E80" s="3" t="inlineStr">
@@ -3630,7 +3630,7 @@
       </c>
       <c r="B81" s="4" t="inlineStr">
         <is>
-          <t>65歳到達時の引継ぎの時期と担当</t>
+          <t>65歳到達時に確認する事項</t>
         </is>
       </c>
       <c r="C81" s="4" t="inlineStr">
@@ -3640,7 +3640,7 @@
       </c>
       <c r="D81" s="4" t="inlineStr">
         <is>
-          <t>時期 / 行うこと</t>
+          <t>確認する事項 / 確認の内容</t>
         </is>
       </c>
       <c r="E81" s="4" t="inlineStr">
@@ -3657,7 +3657,7 @@
       </c>
       <c r="B82" s="3" t="inlineStr">
         <is>
-          <t>関係機関と連携の内容</t>
+          <t>65歳到達時の引継ぎの時期と担当</t>
         </is>
       </c>
       <c r="C82" s="3" t="inlineStr">
@@ -3667,7 +3667,7 @@
       </c>
       <c r="D82" s="3" t="inlineStr">
         <is>
-          <t>分野 / 関係機関</t>
+          <t>時期 / 行うこと</t>
         </is>
       </c>
       <c r="E82" s="3" t="inlineStr">
@@ -3684,7 +3684,7 @@
       </c>
       <c r="B83" s="4" t="inlineStr">
         <is>
-          <t>障がい福祉サービス等に係る給付費の推移</t>
+          <t>関係機関と連携の内容</t>
         </is>
       </c>
       <c r="C83" s="4" t="inlineStr">
@@ -3694,12 +3694,12 @@
       </c>
       <c r="D83" s="4" t="inlineStr">
         <is>
-          <t>年度 / 介護給付費等</t>
+          <t>分野 / 関係機関</t>
         </is>
       </c>
       <c r="E83" s="4" t="inlineStr">
         <is>
-          <t>資料：村提供の障がいサービス給付実績</t>
+          <t>―</t>
         </is>
       </c>
     </row>
@@ -3711,7 +3711,7 @@
       </c>
       <c r="B84" s="3" t="inlineStr">
         <is>
-          <t>財源構成（令和７年度・法定負担割合による試算）</t>
+          <t>障がい福祉サービス等に係る給付費の推移</t>
         </is>
       </c>
       <c r="C84" s="3" t="inlineStr">
@@ -3721,7 +3721,7 @@
       </c>
       <c r="D84" s="3" t="inlineStr">
         <is>
-          <t>区分 / 金額</t>
+          <t>年度 / 介護給付費等</t>
         </is>
       </c>
       <c r="E84" s="3" t="inlineStr">
@@ -3738,7 +3738,7 @@
       </c>
       <c r="B85" s="4" t="inlineStr">
         <is>
-          <t>サービス別の給付費と計画上の位置づけ（令和７年度）</t>
+          <t>財源構成（令和７年度・法定負担割合による試算）</t>
         </is>
       </c>
       <c r="C85" s="4" t="inlineStr">
@@ -3748,7 +3748,7 @@
       </c>
       <c r="D85" s="4" t="inlineStr">
         <is>
-          <t>サービス / 給付費（構成比）</t>
+          <t>区分 / 金額</t>
         </is>
       </c>
       <c r="E85" s="4" t="inlineStr">
@@ -3760,39 +3760,39 @@
     <row r="86">
       <c r="A86" s="3" t="inlineStr">
         <is>
-          <t>表6-1</t>
+          <t>表5-43</t>
         </is>
       </c>
       <c r="B86" s="3" t="inlineStr">
         <is>
-          <t>高齢化率の推移</t>
+          <t>サービス別の給付費と計画上の位置づけ（令和７年度）</t>
         </is>
       </c>
       <c r="C86" s="3" t="inlineStr">
         <is>
-          <t>第6章</t>
+          <t>第5章</t>
         </is>
       </c>
       <c r="D86" s="3" t="inlineStr">
         <is>
-          <t>年度 / 高齢化率</t>
+          <t>サービス / 給付費（構成比）</t>
         </is>
       </c>
       <c r="E86" s="3" t="inlineStr">
         <is>
-          <t>資料：北塩原村</t>
+          <t>資料：村提供の障がいサービス給付実績</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" s="4" t="inlineStr">
         <is>
-          <t>表6-2</t>
+          <t>表6-1</t>
         </is>
       </c>
       <c r="B87" s="4" t="inlineStr">
         <is>
-          <t>精神障がい者及び知的障がい者の人数の推移</t>
+          <t>高齢化率の推移</t>
         </is>
       </c>
       <c r="C87" s="4" t="inlineStr">
@@ -3802,7 +3802,7 @@
       </c>
       <c r="D87" s="4" t="inlineStr">
         <is>
-          <t>年度 / 精神障がい者数（※１）</t>
+          <t>年度 / 高齢化率</t>
         </is>
       </c>
       <c r="E87" s="4" t="inlineStr">
@@ -3814,12 +3814,12 @@
     <row r="88">
       <c r="A88" s="3" t="inlineStr">
         <is>
-          <t>表6-3</t>
+          <t>表6-2</t>
         </is>
       </c>
       <c r="B88" s="3" t="inlineStr">
         <is>
-          <t>成年後見制度利用支援事業の利用状況</t>
+          <t>精神障がい者及び知的障がい者の人数の推移</t>
         </is>
       </c>
       <c r="C88" s="3" t="inlineStr">
@@ -3829,7 +3829,7 @@
       </c>
       <c r="D88" s="3" t="inlineStr">
         <is>
-          <t>区分 / 令和５年度</t>
+          <t>年度 / 精神障がい者数（※１）</t>
         </is>
       </c>
       <c r="E88" s="3" t="inlineStr">
@@ -3841,12 +3841,12 @@
     <row r="89">
       <c r="A89" s="4" t="inlineStr">
         <is>
-          <t>表6-4</t>
+          <t>表6-3</t>
         </is>
       </c>
       <c r="B89" s="4" t="inlineStr">
         <is>
-          <t>成年後見制度の利用促進に係る指標</t>
+          <t>成年後見制度利用支援事業の利用状況</t>
         </is>
       </c>
       <c r="C89" s="4" t="inlineStr">
@@ -3856,34 +3856,34 @@
       </c>
       <c r="D89" s="4" t="inlineStr">
         <is>
-          <t>指標 / 何を数えるか</t>
+          <t>区分 / 令和５年度</t>
         </is>
       </c>
       <c r="E89" s="4" t="inlineStr">
         <is>
-          <t>―</t>
+          <t>資料：北塩原村</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" s="3" t="inlineStr">
         <is>
-          <t>表7-1</t>
+          <t>表6-4</t>
         </is>
       </c>
       <c r="B90" s="3" t="inlineStr">
         <is>
-          <t>健康21・グッドヘルスプランとの対応</t>
+          <t>成年後見制度の利用促進に係る指標</t>
         </is>
       </c>
       <c r="C90" s="3" t="inlineStr">
         <is>
-          <t>第7章</t>
+          <t>第6章</t>
         </is>
       </c>
       <c r="D90" s="3" t="inlineStr">
         <is>
-          <t>項目 / 健康21・グッドヘルスプラン</t>
+          <t>指標 / 何を数えるか</t>
         </is>
       </c>
       <c r="E90" s="3" t="inlineStr">
@@ -3895,12 +3895,12 @@
     <row r="91">
       <c r="A91" s="4" t="inlineStr">
         <is>
-          <t>表7-2</t>
+          <t>表7-1</t>
         </is>
       </c>
       <c r="B91" s="4" t="inlineStr">
         <is>
-          <t>第五次総合振興計画における本計画の位置づけ</t>
+          <t>健康21・グッドヘルスプランとの対応</t>
         </is>
       </c>
       <c r="C91" s="4" t="inlineStr">
@@ -3910,7 +3910,7 @@
       </c>
       <c r="D91" s="4" t="inlineStr">
         <is>
-          <t>総合振興計画の位置づけ / 内容</t>
+          <t>項目 / 健康21・グッドヘルスプラン</t>
         </is>
       </c>
       <c r="E91" s="4" t="inlineStr">
@@ -3922,12 +3922,12 @@
     <row r="92">
       <c r="A92" s="3" t="inlineStr">
         <is>
-          <t>表7-3</t>
+          <t>表7-2</t>
         </is>
       </c>
       <c r="B92" s="3" t="inlineStr">
         <is>
-          <t>高齢者福祉計画・介護保険事業計画と重ねて数えないための確認事項</t>
+          <t>第五次総合振興計画における本計画の位置づけ</t>
         </is>
       </c>
       <c r="C92" s="3" t="inlineStr">
@@ -3937,7 +3937,7 @@
       </c>
       <c r="D92" s="3" t="inlineStr">
         <is>
-          <t>事項 / 両計画での扱い</t>
+          <t>総合振興計画の位置づけ / 内容</t>
         </is>
       </c>
       <c r="E92" s="3" t="inlineStr">
@@ -3949,12 +3949,12 @@
     <row r="93">
       <c r="A93" s="4" t="inlineStr">
         <is>
-          <t>表7-4</t>
+          <t>表7-3</t>
         </is>
       </c>
       <c r="B93" s="4" t="inlineStr">
         <is>
-          <t>こども・子育て計画との整合を確かめる事項</t>
+          <t>高齢者福祉計画・介護保険事業計画と重ねて数えないための確認事項</t>
         </is>
       </c>
       <c r="C93" s="4" t="inlineStr">
@@ -3964,7 +3964,7 @@
       </c>
       <c r="D93" s="4" t="inlineStr">
         <is>
-          <t>確かめる事項 / 確かめ方</t>
+          <t>事項 / 両計画での扱い</t>
         </is>
       </c>
       <c r="E93" s="4" t="inlineStr">
@@ -3976,22 +3976,22 @@
     <row r="94">
       <c r="A94" s="3" t="inlineStr">
         <is>
-          <t>表8-1</t>
+          <t>表7-4</t>
         </is>
       </c>
       <c r="B94" s="3" t="inlineStr">
         <is>
-          <t>北塩原村障がい者自立支援協議会委員名簿</t>
+          <t>こども・子育て計画との整合を確かめる事項</t>
         </is>
       </c>
       <c r="C94" s="3" t="inlineStr">
         <is>
-          <t>第8章</t>
+          <t>第7章</t>
         </is>
       </c>
       <c r="D94" s="3" t="inlineStr">
         <is>
-          <t>区　分 / 氏　名</t>
+          <t>確かめる事項 / 確かめ方</t>
         </is>
       </c>
       <c r="E94" s="3" t="inlineStr">
@@ -4003,12 +4003,12 @@
     <row r="95">
       <c r="A95" s="4" t="inlineStr">
         <is>
-          <t>表8-2</t>
+          <t>表8-1</t>
         </is>
       </c>
       <c r="B95" s="4" t="inlineStr">
         <is>
-          <t>計画の策定経過</t>
+          <t>北塩原村障がい者自立支援協議会委員名簿</t>
         </is>
       </c>
       <c r="C95" s="4" t="inlineStr">
@@ -4018,7 +4018,7 @@
       </c>
       <c r="D95" s="4" t="inlineStr">
         <is>
-          <t>年月日 / 内容</t>
+          <t>区　分 / 氏　名</t>
         </is>
       </c>
       <c r="E95" s="4" t="inlineStr">
@@ -4030,12 +4030,12 @@
     <row r="96">
       <c r="A96" s="3" t="inlineStr">
         <is>
-          <t>表8-3</t>
+          <t>表8-2</t>
         </is>
       </c>
       <c r="B96" s="3" t="inlineStr">
         <is>
-          <t>近年の障がい者施策の動向</t>
+          <t>計画の策定経過</t>
         </is>
       </c>
       <c r="C96" s="3" t="inlineStr">
@@ -4045,7 +4045,7 @@
       </c>
       <c r="D96" s="3" t="inlineStr">
         <is>
-          <t>年 / 主な動向</t>
+          <t>年月日 / 内容</t>
         </is>
       </c>
       <c r="E96" s="3" t="inlineStr">
@@ -4057,25 +4057,52 @@
     <row r="97">
       <c r="A97" s="4" t="inlineStr">
         <is>
+          <t>表8-3</t>
+        </is>
+      </c>
+      <c r="B97" s="4" t="inlineStr">
+        <is>
+          <t>近年の障がい者施策の動向</t>
+        </is>
+      </c>
+      <c r="C97" s="4" t="inlineStr">
+        <is>
+          <t>第8章</t>
+        </is>
+      </c>
+      <c r="D97" s="4" t="inlineStr">
+        <is>
+          <t>年 / 主な動向</t>
+        </is>
+      </c>
+      <c r="E97" s="4" t="inlineStr">
+        <is>
+          <t>―</t>
+        </is>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" s="3" t="inlineStr">
+        <is>
           <t>表8-4</t>
         </is>
       </c>
-      <c r="B97" s="4" t="inlineStr">
+      <c r="B98" s="3" t="inlineStr">
         <is>
           <t>用語解説</t>
         </is>
       </c>
-      <c r="C97" s="4" t="inlineStr">
+      <c r="C98" s="3" t="inlineStr">
         <is>
           <t>第8章</t>
         </is>
       </c>
-      <c r="D97" s="4" t="inlineStr">
+      <c r="D98" s="3" t="inlineStr">
         <is>
           <t>用語 / 説明</t>
         </is>
       </c>
-      <c r="E97" s="4" t="inlineStr">
+      <c r="E98" s="3" t="inlineStr">
         <is>
           <t>―</t>
         </is>

--- a/output/北塩原村_図表番号一覧.xlsx
+++ b/output/北塩原村_図表番号一覧.xlsx
@@ -535,7 +535,7 @@
       </c>
       <c r="B6" s="3" t="inlineStr">
         <is>
-          <t>図26点・表93点に章ごとの通し番号を振った（図１-１・表１-１の形）。注記ボックス（【村へ確認】等の1×1の枠）45点には振っていない。確定時に削るため、番号を振ると欠番が出るからである。</t>
+          <t>図26点・表94点に章ごとの通し番号を振った（図１-１・表１-１の形）。注記ボックス（【村へ確認】等の1×1の枠）45点には振っていない。確定時に削るため、番号を振ると欠番が出るからである。</t>
         </is>
       </c>
     </row>
@@ -607,7 +607,7 @@
       </c>
       <c r="B12" s="3" t="inlineStr">
         <is>
-          <t>出所は、村の実績・アンケート・外部資料から数値を引いた図表44点にのみ付けた。手順・区分・確認事項を整理しただけの表は本計画の記述そのものであり、出所を書くと出どころが二重になるためである（規約への補足1件）。</t>
+          <t>出所は、村の実績・アンケート・外部資料から数値を引いた図表45点にのみ付けた。手順・区分・確認事項を整理しただけの表は本計画の記述そのものであり、出所を書くと出どころが二重になるためである（規約への補足1件）。</t>
         </is>
       </c>
     </row>
@@ -1542,7 +1542,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E98"/>
+  <dimension ref="A1:E99"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -1555,7 +1555,7 @@
     <row r="1" ht="30" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>表 93点</t>
+          <t>表 94点</t>
         </is>
       </c>
     </row>
@@ -3684,7 +3684,7 @@
       </c>
       <c r="B83" s="4" t="inlineStr">
         <is>
-          <t>関係機関と連携の内容</t>
+          <t>介護保険の地域支援事業の区分と対象者の定め</t>
         </is>
       </c>
       <c r="C83" s="4" t="inlineStr">
@@ -3694,12 +3694,12 @@
       </c>
       <c r="D83" s="4" t="inlineStr">
         <is>
-          <t>分野 / 関係機関</t>
+          <t>地域支援事業の区分 / 主な事業</t>
         </is>
       </c>
       <c r="E83" s="4" t="inlineStr">
         <is>
-          <t>―</t>
+          <t>資料：地域支援事業の実施について（老発第0609001号。最終改正 令和８年８月20日）により作成</t>
         </is>
       </c>
     </row>
@@ -3711,7 +3711,7 @@
       </c>
       <c r="B84" s="3" t="inlineStr">
         <is>
-          <t>障がい福祉サービス等に係る給付費の推移</t>
+          <t>関係機関と連携の内容</t>
         </is>
       </c>
       <c r="C84" s="3" t="inlineStr">
@@ -3721,12 +3721,12 @@
       </c>
       <c r="D84" s="3" t="inlineStr">
         <is>
-          <t>年度 / 介護給付費等</t>
+          <t>分野 / 関係機関</t>
         </is>
       </c>
       <c r="E84" s="3" t="inlineStr">
         <is>
-          <t>資料：村提供の障がいサービス給付実績</t>
+          <t>―</t>
         </is>
       </c>
     </row>
@@ -3738,7 +3738,7 @@
       </c>
       <c r="B85" s="4" t="inlineStr">
         <is>
-          <t>財源構成（令和７年度・法定負担割合による試算）</t>
+          <t>障がい福祉サービス等に係る給付費の推移</t>
         </is>
       </c>
       <c r="C85" s="4" t="inlineStr">
@@ -3748,7 +3748,7 @@
       </c>
       <c r="D85" s="4" t="inlineStr">
         <is>
-          <t>区分 / 金額</t>
+          <t>年度 / 介護給付費等</t>
         </is>
       </c>
       <c r="E85" s="4" t="inlineStr">
@@ -3765,7 +3765,7 @@
       </c>
       <c r="B86" s="3" t="inlineStr">
         <is>
-          <t>サービス別の給付費と計画上の位置づけ（令和７年度）</t>
+          <t>財源構成（令和７年度・法定負担割合による試算）</t>
         </is>
       </c>
       <c r="C86" s="3" t="inlineStr">
@@ -3775,7 +3775,7 @@
       </c>
       <c r="D86" s="3" t="inlineStr">
         <is>
-          <t>サービス / 給付費（構成比）</t>
+          <t>区分 / 金額</t>
         </is>
       </c>
       <c r="E86" s="3" t="inlineStr">
@@ -3787,39 +3787,39 @@
     <row r="87">
       <c r="A87" s="4" t="inlineStr">
         <is>
-          <t>表6-1</t>
+          <t>表5-44</t>
         </is>
       </c>
       <c r="B87" s="4" t="inlineStr">
         <is>
-          <t>高齢化率の推移</t>
+          <t>サービス別の給付費と計画上の位置づけ（令和７年度）</t>
         </is>
       </c>
       <c r="C87" s="4" t="inlineStr">
         <is>
-          <t>第6章</t>
+          <t>第5章</t>
         </is>
       </c>
       <c r="D87" s="4" t="inlineStr">
         <is>
-          <t>年度 / 高齢化率</t>
+          <t>サービス / 給付費（構成比）</t>
         </is>
       </c>
       <c r="E87" s="4" t="inlineStr">
         <is>
-          <t>資料：北塩原村</t>
+          <t>資料：村提供の障がいサービス給付実績</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" s="3" t="inlineStr">
         <is>
-          <t>表6-2</t>
+          <t>表6-1</t>
         </is>
       </c>
       <c r="B88" s="3" t="inlineStr">
         <is>
-          <t>精神障がい者及び知的障がい者の人数の推移</t>
+          <t>高齢化率の推移</t>
         </is>
       </c>
       <c r="C88" s="3" t="inlineStr">
@@ -3829,7 +3829,7 @@
       </c>
       <c r="D88" s="3" t="inlineStr">
         <is>
-          <t>年度 / 精神障がい者数（※１）</t>
+          <t>年度 / 高齢化率</t>
         </is>
       </c>
       <c r="E88" s="3" t="inlineStr">
@@ -3841,12 +3841,12 @@
     <row r="89">
       <c r="A89" s="4" t="inlineStr">
         <is>
-          <t>表6-3</t>
+          <t>表6-2</t>
         </is>
       </c>
       <c r="B89" s="4" t="inlineStr">
         <is>
-          <t>成年後見制度利用支援事業の利用状況</t>
+          <t>精神障がい者及び知的障がい者の人数の推移</t>
         </is>
       </c>
       <c r="C89" s="4" t="inlineStr">
@@ -3856,7 +3856,7 @@
       </c>
       <c r="D89" s="4" t="inlineStr">
         <is>
-          <t>区分 / 令和５年度</t>
+          <t>年度 / 精神障がい者数（※１）</t>
         </is>
       </c>
       <c r="E89" s="4" t="inlineStr">
@@ -3868,12 +3868,12 @@
     <row r="90">
       <c r="A90" s="3" t="inlineStr">
         <is>
-          <t>表6-4</t>
+          <t>表6-3</t>
         </is>
       </c>
       <c r="B90" s="3" t="inlineStr">
         <is>
-          <t>成年後見制度の利用促進に係る指標</t>
+          <t>成年後見制度利用支援事業の利用状況</t>
         </is>
       </c>
       <c r="C90" s="3" t="inlineStr">
@@ -3883,34 +3883,34 @@
       </c>
       <c r="D90" s="3" t="inlineStr">
         <is>
-          <t>指標 / 何を数えるか</t>
+          <t>区分 / 令和５年度</t>
         </is>
       </c>
       <c r="E90" s="3" t="inlineStr">
         <is>
-          <t>―</t>
+          <t>資料：北塩原村</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" s="4" t="inlineStr">
         <is>
-          <t>表7-1</t>
+          <t>表6-4</t>
         </is>
       </c>
       <c r="B91" s="4" t="inlineStr">
         <is>
-          <t>健康21・グッドヘルスプランとの対応</t>
+          <t>成年後見制度の利用促進に係る指標</t>
         </is>
       </c>
       <c r="C91" s="4" t="inlineStr">
         <is>
-          <t>第7章</t>
+          <t>第6章</t>
         </is>
       </c>
       <c r="D91" s="4" t="inlineStr">
         <is>
-          <t>項目 / 健康21・グッドヘルスプラン</t>
+          <t>指標 / 何を数えるか</t>
         </is>
       </c>
       <c r="E91" s="4" t="inlineStr">
@@ -3922,12 +3922,12 @@
     <row r="92">
       <c r="A92" s="3" t="inlineStr">
         <is>
-          <t>表7-2</t>
+          <t>表7-1</t>
         </is>
       </c>
       <c r="B92" s="3" t="inlineStr">
         <is>
-          <t>第五次総合振興計画における本計画の位置づけ</t>
+          <t>健康21・グッドヘルスプランとの対応</t>
         </is>
       </c>
       <c r="C92" s="3" t="inlineStr">
@@ -3937,7 +3937,7 @@
       </c>
       <c r="D92" s="3" t="inlineStr">
         <is>
-          <t>総合振興計画の位置づけ / 内容</t>
+          <t>項目 / 健康21・グッドヘルスプラン</t>
         </is>
       </c>
       <c r="E92" s="3" t="inlineStr">
@@ -3949,12 +3949,12 @@
     <row r="93">
       <c r="A93" s="4" t="inlineStr">
         <is>
-          <t>表7-3</t>
+          <t>表7-2</t>
         </is>
       </c>
       <c r="B93" s="4" t="inlineStr">
         <is>
-          <t>高齢者福祉計画・介護保険事業計画と重ねて数えないための確認事項</t>
+          <t>第五次総合振興計画における本計画の位置づけ</t>
         </is>
       </c>
       <c r="C93" s="4" t="inlineStr">
@@ -3964,7 +3964,7 @@
       </c>
       <c r="D93" s="4" t="inlineStr">
         <is>
-          <t>事項 / 両計画での扱い</t>
+          <t>総合振興計画の位置づけ / 内容</t>
         </is>
       </c>
       <c r="E93" s="4" t="inlineStr">
@@ -3976,12 +3976,12 @@
     <row r="94">
       <c r="A94" s="3" t="inlineStr">
         <is>
-          <t>表7-4</t>
+          <t>表7-3</t>
         </is>
       </c>
       <c r="B94" s="3" t="inlineStr">
         <is>
-          <t>こども・子育て計画との整合を確かめる事項</t>
+          <t>高齢者福祉計画・介護保険事業計画と重ねて数えないための確認事項</t>
         </is>
       </c>
       <c r="C94" s="3" t="inlineStr">
@@ -3991,7 +3991,7 @@
       </c>
       <c r="D94" s="3" t="inlineStr">
         <is>
-          <t>確かめる事項 / 確かめ方</t>
+          <t>事項 / 両計画での扱い</t>
         </is>
       </c>
       <c r="E94" s="3" t="inlineStr">
@@ -4003,22 +4003,22 @@
     <row r="95">
       <c r="A95" s="4" t="inlineStr">
         <is>
-          <t>表8-1</t>
+          <t>表7-4</t>
         </is>
       </c>
       <c r="B95" s="4" t="inlineStr">
         <is>
-          <t>北塩原村障がい者自立支援協議会委員名簿</t>
+          <t>こども・子育て計画との整合を確かめる事項</t>
         </is>
       </c>
       <c r="C95" s="4" t="inlineStr">
         <is>
-          <t>第8章</t>
+          <t>第7章</t>
         </is>
       </c>
       <c r="D95" s="4" t="inlineStr">
         <is>
-          <t>区　分 / 氏　名</t>
+          <t>確かめる事項 / 確かめ方</t>
         </is>
       </c>
       <c r="E95" s="4" t="inlineStr">
@@ -4030,12 +4030,12 @@
     <row r="96">
       <c r="A96" s="3" t="inlineStr">
         <is>
-          <t>表8-2</t>
+          <t>表8-1</t>
         </is>
       </c>
       <c r="B96" s="3" t="inlineStr">
         <is>
-          <t>計画の策定経過</t>
+          <t>北塩原村障がい者自立支援協議会委員名簿</t>
         </is>
       </c>
       <c r="C96" s="3" t="inlineStr">
@@ -4045,7 +4045,7 @@
       </c>
       <c r="D96" s="3" t="inlineStr">
         <is>
-          <t>年月日 / 内容</t>
+          <t>区　分 / 氏　名</t>
         </is>
       </c>
       <c r="E96" s="3" t="inlineStr">
@@ -4057,12 +4057,12 @@
     <row r="97">
       <c r="A97" s="4" t="inlineStr">
         <is>
-          <t>表8-3</t>
+          <t>表8-2</t>
         </is>
       </c>
       <c r="B97" s="4" t="inlineStr">
         <is>
-          <t>近年の障がい者施策の動向</t>
+          <t>計画の策定経過</t>
         </is>
       </c>
       <c r="C97" s="4" t="inlineStr">
@@ -4072,7 +4072,7 @@
       </c>
       <c r="D97" s="4" t="inlineStr">
         <is>
-          <t>年 / 主な動向</t>
+          <t>年月日 / 内容</t>
         </is>
       </c>
       <c r="E97" s="4" t="inlineStr">
@@ -4084,25 +4084,52 @@
     <row r="98">
       <c r="A98" s="3" t="inlineStr">
         <is>
+          <t>表8-3</t>
+        </is>
+      </c>
+      <c r="B98" s="3" t="inlineStr">
+        <is>
+          <t>近年の障がい者施策の動向</t>
+        </is>
+      </c>
+      <c r="C98" s="3" t="inlineStr">
+        <is>
+          <t>第8章</t>
+        </is>
+      </c>
+      <c r="D98" s="3" t="inlineStr">
+        <is>
+          <t>年 / 主な動向</t>
+        </is>
+      </c>
+      <c r="E98" s="3" t="inlineStr">
+        <is>
+          <t>―</t>
+        </is>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" s="4" t="inlineStr">
+        <is>
           <t>表8-4</t>
         </is>
       </c>
-      <c r="B98" s="3" t="inlineStr">
+      <c r="B99" s="4" t="inlineStr">
         <is>
           <t>用語解説</t>
         </is>
       </c>
-      <c r="C98" s="3" t="inlineStr">
+      <c r="C99" s="4" t="inlineStr">
         <is>
           <t>第8章</t>
         </is>
       </c>
-      <c r="D98" s="3" t="inlineStr">
+      <c r="D99" s="4" t="inlineStr">
         <is>
           <t>用語 / 説明</t>
         </is>
       </c>
-      <c r="E98" s="3" t="inlineStr">
+      <c r="E99" s="4" t="inlineStr">
         <is>
           <t>―</t>
         </is>

--- a/output/北塩原村_図表番号一覧.xlsx
+++ b/output/北塩原村_図表番号一覧.xlsx
@@ -535,7 +535,7 @@
       </c>
       <c r="B6" s="3" t="inlineStr">
         <is>
-          <t>図26点・表94点に章ごとの通し番号を振った（図１-１・表１-１の形）。注記ボックス（【村へ確認】等の1×1の枠）45点には振っていない。確定時に削るため、番号を振ると欠番が出るからである。</t>
+          <t>図26点・表95点に章ごとの通し番号を振った（図１-１・表１-１の形）。注記ボックス（【村へ確認】等の1×1の枠）45点には振っていない。確定時に削るため、番号を振ると欠番が出るからである。</t>
         </is>
       </c>
     </row>
@@ -1542,7 +1542,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E99"/>
+  <dimension ref="A1:E100"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -1555,7 +1555,7 @@
     <row r="1" ht="30" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>表 94点</t>
+          <t>表 95点</t>
         </is>
       </c>
     </row>
@@ -2166,39 +2166,39 @@
     <row r="27">
       <c r="A27" s="4" t="inlineStr">
         <is>
-          <t>表4-1</t>
+          <t>表3-3</t>
         </is>
       </c>
       <c r="B27" s="4" t="inlineStr">
         <is>
-          <t>第７期計画の成果目標の達成状況</t>
+          <t>本計画で新たに加える施策</t>
         </is>
       </c>
       <c r="C27" s="4" t="inlineStr">
         <is>
-          <t>第4章</t>
+          <t>第3章</t>
         </is>
       </c>
       <c r="D27" s="4" t="inlineStr">
         <is>
-          <t>成果目標 / 項目</t>
+          <t>新たに加える施策 / 主な内容</t>
         </is>
       </c>
       <c r="E27" s="4" t="inlineStr">
         <is>
-          <t>資料：北塩原村</t>
+          <t>―</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="3" t="inlineStr">
         <is>
-          <t>表4-2</t>
+          <t>表4-1</t>
         </is>
       </c>
       <c r="B28" s="3" t="inlineStr">
         <is>
-          <t>施設入所者の地域生活への移行の目標</t>
+          <t>第７期計画の成果目標の達成状況</t>
         </is>
       </c>
       <c r="C28" s="3" t="inlineStr">
@@ -2208,24 +2208,24 @@
       </c>
       <c r="D28" s="3" t="inlineStr">
         <is>
-          <t>項目 / 数値</t>
+          <t>成果目標 / 項目</t>
         </is>
       </c>
       <c r="E28" s="3" t="inlineStr">
         <is>
-          <t>―</t>
+          <t>資料：北塩原村</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="4" t="inlineStr">
         <is>
-          <t>表4-3</t>
+          <t>表4-2</t>
         </is>
       </c>
       <c r="B29" s="4" t="inlineStr">
         <is>
-          <t>地域移行の可能性を確かめる事項</t>
+          <t>施設入所者の地域生活への移行の目標</t>
         </is>
       </c>
       <c r="C29" s="4" t="inlineStr">
@@ -2235,7 +2235,7 @@
       </c>
       <c r="D29" s="4" t="inlineStr">
         <is>
-          <t>確認する事項 / 確認の方法</t>
+          <t>項目 / 数値</t>
         </is>
       </c>
       <c r="E29" s="4" t="inlineStr">
@@ -2247,12 +2247,12 @@
     <row r="30">
       <c r="A30" s="3" t="inlineStr">
         <is>
-          <t>表4-4</t>
+          <t>表4-3</t>
         </is>
       </c>
       <c r="B30" s="3" t="inlineStr">
         <is>
-          <t>精神障害にも対応した地域包括ケアシステムの構築の目標</t>
+          <t>地域移行の可能性を確かめる事項</t>
         </is>
       </c>
       <c r="C30" s="3" t="inlineStr">
@@ -2262,7 +2262,7 @@
       </c>
       <c r="D30" s="3" t="inlineStr">
         <is>
-          <t>項目 / 数値</t>
+          <t>確認する事項 / 確認の方法</t>
         </is>
       </c>
       <c r="E30" s="3" t="inlineStr">
@@ -2274,12 +2274,12 @@
     <row r="31">
       <c r="A31" s="4" t="inlineStr">
         <is>
-          <t>表4-5</t>
+          <t>表4-4</t>
         </is>
       </c>
       <c r="B31" s="4" t="inlineStr">
         <is>
-          <t>精神障がい者のサービス利用の見込み（活動指標）</t>
+          <t>精神障害にも対応した地域包括ケアシステムの構築の目標</t>
         </is>
       </c>
       <c r="C31" s="4" t="inlineStr">
@@ -2289,7 +2289,7 @@
       </c>
       <c r="D31" s="4" t="inlineStr">
         <is>
-          <t>サービス種別 / 単位</t>
+          <t>項目 / 数値</t>
         </is>
       </c>
       <c r="E31" s="4" t="inlineStr">
@@ -2301,12 +2301,12 @@
     <row r="32">
       <c r="A32" s="3" t="inlineStr">
         <is>
-          <t>表4-6</t>
+          <t>表4-5</t>
         </is>
       </c>
       <c r="B32" s="3" t="inlineStr">
         <is>
-          <t>精神病床からの退院に関する県の算定との関係</t>
+          <t>精神障がい者のサービス利用の見込み（活動指標）</t>
         </is>
       </c>
       <c r="C32" s="3" t="inlineStr">
@@ -2316,7 +2316,7 @@
       </c>
       <c r="D32" s="3" t="inlineStr">
         <is>
-          <t>項目 / 値</t>
+          <t>サービス種別 / 単位</t>
         </is>
       </c>
       <c r="E32" s="3" t="inlineStr">
@@ -2328,12 +2328,12 @@
     <row r="33">
       <c r="A33" s="4" t="inlineStr">
         <is>
-          <t>表4-7</t>
+          <t>表4-6</t>
         </is>
       </c>
       <c r="B33" s="4" t="inlineStr">
         <is>
-          <t>福祉施設から一般就労への移行等の目標</t>
+          <t>精神病床からの退院に関する県の算定との関係</t>
         </is>
       </c>
       <c r="C33" s="4" t="inlineStr">
@@ -2343,7 +2343,7 @@
       </c>
       <c r="D33" s="4" t="inlineStr">
         <is>
-          <t>項目 / 数値</t>
+          <t>項目 / 値</t>
         </is>
       </c>
       <c r="E33" s="4" t="inlineStr">
@@ -2355,12 +2355,12 @@
     <row r="34">
       <c r="A34" s="3" t="inlineStr">
         <is>
-          <t>表4-8</t>
+          <t>表4-7</t>
         </is>
       </c>
       <c r="B34" s="3" t="inlineStr">
         <is>
-          <t>就労移行支援等から一般就労への移行者数の目標</t>
+          <t>福祉施設から一般就労への移行等の目標</t>
         </is>
       </c>
       <c r="C34" s="3" t="inlineStr">
@@ -2370,7 +2370,7 @@
       </c>
       <c r="D34" s="3" t="inlineStr">
         <is>
-          <t>事業種別 / 令和６年度実績</t>
+          <t>項目 / 数値</t>
         </is>
       </c>
       <c r="E34" s="3" t="inlineStr">
@@ -2382,52 +2382,52 @@
     <row r="35">
       <c r="A35" s="4" t="inlineStr">
         <is>
+          <t>表4-8</t>
+        </is>
+      </c>
+      <c r="B35" s="4" t="inlineStr">
+        <is>
+          <t>就労移行支援等から一般就労への移行者数の目標</t>
+        </is>
+      </c>
+      <c r="C35" s="4" t="inlineStr">
+        <is>
+          <t>第4章</t>
+        </is>
+      </c>
+      <c r="D35" s="4" t="inlineStr">
+        <is>
+          <t>事業種別 / 令和６年度実績</t>
+        </is>
+      </c>
+      <c r="E35" s="4" t="inlineStr">
+        <is>
+          <t>―</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="3" t="inlineStr">
+        <is>
           <t>表4-9</t>
         </is>
       </c>
-      <c r="B35" s="4" t="inlineStr">
+      <c r="B36" s="3" t="inlineStr">
         <is>
           <t>障がい児支援の提供体制の整備等の目標</t>
         </is>
       </c>
-      <c r="C35" s="4" t="inlineStr">
+      <c r="C36" s="3" t="inlineStr">
         <is>
           <t>第4章</t>
         </is>
       </c>
-      <c r="D35" s="4" t="inlineStr">
+      <c r="D36" s="3" t="inlineStr">
         <is>
           <t>項目 / 現状
 （令和８年度見込み）</t>
         </is>
       </c>
-      <c r="E35" s="4" t="inlineStr">
-        <is>
-          <t>―</t>
-        </is>
-      </c>
-    </row>
-    <row r="36">
-      <c r="A36" s="3" t="inlineStr">
-        <is>
-          <t>表4-10</t>
-        </is>
-      </c>
-      <c r="B36" s="3" t="inlineStr">
-        <is>
-          <t>早期発見から支援につながる経路の記録</t>
-        </is>
-      </c>
-      <c r="C36" s="3" t="inlineStr">
-        <is>
-          <t>第4章</t>
-        </is>
-      </c>
-      <c r="D36" s="3" t="inlineStr">
-        <is>
-          <t>記録する事項 / ねらい</t>
-        </is>
-      </c>
       <c r="E36" s="3" t="inlineStr">
         <is>
           <t>―</t>
@@ -2437,12 +2437,12 @@
     <row r="37">
       <c r="A37" s="4" t="inlineStr">
         <is>
-          <t>表4-11</t>
+          <t>表4-10</t>
         </is>
       </c>
       <c r="B37" s="4" t="inlineStr">
         <is>
-          <t>地域生活支援の充実の目標</t>
+          <t>早期発見から支援につながる経路の記録</t>
         </is>
       </c>
       <c r="C37" s="4" t="inlineStr">
@@ -2452,7 +2452,7 @@
       </c>
       <c r="D37" s="4" t="inlineStr">
         <is>
-          <t>項目 / 数値</t>
+          <t>記録する事項 / ねらい</t>
         </is>
       </c>
       <c r="E37" s="4" t="inlineStr">
@@ -2464,12 +2464,12 @@
     <row r="38">
       <c r="A38" s="3" t="inlineStr">
         <is>
-          <t>表4-12</t>
+          <t>表4-11</t>
         </is>
       </c>
       <c r="B38" s="3" t="inlineStr">
         <is>
-          <t>地域生活支援拠点等の５つの機能と記録する実績</t>
+          <t>地域生活支援の充実の目標</t>
         </is>
       </c>
       <c r="C38" s="3" t="inlineStr">
@@ -2479,7 +2479,7 @@
       </c>
       <c r="D38" s="3" t="inlineStr">
         <is>
-          <t>機能 / 本村での確保の方法</t>
+          <t>項目 / 数値</t>
         </is>
       </c>
       <c r="E38" s="3" t="inlineStr">
@@ -2491,12 +2491,12 @@
     <row r="39">
       <c r="A39" s="4" t="inlineStr">
         <is>
-          <t>表4-13</t>
+          <t>表4-12</t>
         </is>
       </c>
       <c r="B39" s="4" t="inlineStr">
         <is>
-          <t>相談支援体制の充実・強化等の目標</t>
+          <t>地域生活支援拠点等の５つの機能と記録する実績</t>
         </is>
       </c>
       <c r="C39" s="4" t="inlineStr">
@@ -2506,7 +2506,7 @@
       </c>
       <c r="D39" s="4" t="inlineStr">
         <is>
-          <t>項目 / 数値</t>
+          <t>機能 / 本村での確保の方法</t>
         </is>
       </c>
       <c r="E39" s="4" t="inlineStr">
@@ -2518,12 +2518,12 @@
     <row r="40">
       <c r="A40" s="3" t="inlineStr">
         <is>
-          <t>表4-14</t>
+          <t>表4-13</t>
         </is>
       </c>
       <c r="B40" s="3" t="inlineStr">
         <is>
-          <t>会津障がい保健福祉圏域の基幹相談支援センター（令和７年４月１日時点）</t>
+          <t>相談支援体制の充実・強化等の目標</t>
         </is>
       </c>
       <c r="C40" s="3" t="inlineStr">
@@ -2533,24 +2533,24 @@
       </c>
       <c r="D40" s="3" t="inlineStr">
         <is>
-          <t>基幹相談支援センター / 設置の形</t>
+          <t>項目 / 数値</t>
         </is>
       </c>
       <c r="E40" s="3" t="inlineStr">
         <is>
-          <t>資料：厚生労働省「基幹相談支援センター一覧（令和７年４月１日時点）」</t>
+          <t>―</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="4" t="inlineStr">
         <is>
-          <t>表4-15</t>
+          <t>表4-14</t>
         </is>
       </c>
       <c r="B41" s="4" t="inlineStr">
         <is>
-          <t>障害福祉人材の確保・定着等の目標</t>
+          <t>会津障がい保健福祉圏域の基幹相談支援センター（令和７年４月１日時点）</t>
         </is>
       </c>
       <c r="C41" s="4" t="inlineStr">
@@ -2560,24 +2560,24 @@
       </c>
       <c r="D41" s="4" t="inlineStr">
         <is>
-          <t>項目 / 数値</t>
+          <t>基幹相談支援センター / 設置の形</t>
         </is>
       </c>
       <c r="E41" s="4" t="inlineStr">
         <is>
-          <t>―</t>
+          <t>資料：厚生労働省「基幹相談支援センター一覧（令和７年４月１日時点）」</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="3" t="inlineStr">
         <is>
-          <t>表4-16</t>
+          <t>表4-15</t>
         </is>
       </c>
       <c r="B42" s="3" t="inlineStr">
         <is>
-          <t>障害福祉サービス等の質を向上させる体制の構築の目標</t>
+          <t>障害福祉人材の確保・定着等の目標</t>
         </is>
       </c>
       <c r="C42" s="3" t="inlineStr">
@@ -2599,12 +2599,12 @@
     <row r="43">
       <c r="A43" s="4" t="inlineStr">
         <is>
-          <t>表4-17</t>
+          <t>表4-16</t>
         </is>
       </c>
       <c r="B43" s="4" t="inlineStr">
         <is>
-          <t>発達障がい者等に対する支援の活動指標</t>
+          <t>障害福祉サービス等の質を向上させる体制の構築の目標</t>
         </is>
       </c>
       <c r="C43" s="4" t="inlineStr">
@@ -2614,7 +2614,7 @@
       </c>
       <c r="D43" s="4" t="inlineStr">
         <is>
-          <t>活動指標 / 令和９年度</t>
+          <t>項目 / 数値</t>
         </is>
       </c>
       <c r="E43" s="4" t="inlineStr">
@@ -2626,22 +2626,22 @@
     <row r="44">
       <c r="A44" s="3" t="inlineStr">
         <is>
-          <t>表5-1</t>
+          <t>表4-17</t>
         </is>
       </c>
       <c r="B44" s="3" t="inlineStr">
         <is>
-          <t>障がい福祉サービス等の体系（参考）</t>
+          <t>発達障がい者等に対する支援の活動指標</t>
         </is>
       </c>
       <c r="C44" s="3" t="inlineStr">
         <is>
-          <t>第5章</t>
+          <t>第4章</t>
         </is>
       </c>
       <c r="D44" s="3" t="inlineStr">
         <is>
-          <t>区分 / 主なサービス・事業</t>
+          <t>活動指標 / 令和９年度</t>
         </is>
       </c>
       <c r="E44" s="3" t="inlineStr">
@@ -2653,12 +2653,12 @@
     <row r="45">
       <c r="A45" s="4" t="inlineStr">
         <is>
-          <t>表5-2</t>
+          <t>表5-1</t>
         </is>
       </c>
       <c r="B45" s="4" t="inlineStr">
         <is>
-          <t>見込量を定めるまでの段階</t>
+          <t>障がい福祉サービス等の体系（参考）</t>
         </is>
       </c>
       <c r="C45" s="4" t="inlineStr">
@@ -2668,7 +2668,7 @@
       </c>
       <c r="D45" s="4" t="inlineStr">
         <is>
-          <t>段階 / 何を見るか</t>
+          <t>区分 / 主なサービス・事業</t>
         </is>
       </c>
       <c r="E45" s="4" t="inlineStr">
@@ -2680,12 +2680,12 @@
     <row r="46">
       <c r="A46" s="3" t="inlineStr">
         <is>
-          <t>表5-3</t>
+          <t>表5-2</t>
         </is>
       </c>
       <c r="B46" s="3" t="inlineStr">
         <is>
-          <t>必要な利用者数の組み立て</t>
+          <t>見込量を定めるまでの段階</t>
         </is>
       </c>
       <c r="C46" s="3" t="inlineStr">
@@ -2695,7 +2695,7 @@
       </c>
       <c r="D46" s="3" t="inlineStr">
         <is>
-          <t>加減 / 項目</t>
+          <t>段階 / 何を見るか</t>
         </is>
       </c>
       <c r="E46" s="3" t="inlineStr">
@@ -2707,12 +2707,12 @@
     <row r="47">
       <c r="A47" s="4" t="inlineStr">
         <is>
-          <t>表5-4</t>
+          <t>表5-3</t>
         </is>
       </c>
       <c r="B47" s="4" t="inlineStr">
         <is>
-          <t>訪問系サービスの実績</t>
+          <t>必要な利用者数の組み立て</t>
         </is>
       </c>
       <c r="C47" s="4" t="inlineStr">
@@ -2722,24 +2722,24 @@
       </c>
       <c r="D47" s="4" t="inlineStr">
         <is>
-          <t>サービス種別 / 単位</t>
+          <t>加減 / 項目</t>
         </is>
       </c>
       <c r="E47" s="4" t="inlineStr">
         <is>
-          <t>資料：北塩原村</t>
+          <t>―</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="3" t="inlineStr">
         <is>
-          <t>表5-5</t>
+          <t>表5-4</t>
         </is>
       </c>
       <c r="B48" s="3" t="inlineStr">
         <is>
-          <t>訪問系サービスの見込量</t>
+          <t>訪問系サービスの実績</t>
         </is>
       </c>
       <c r="C48" s="3" t="inlineStr">
@@ -2754,19 +2754,19 @@
       </c>
       <c r="E48" s="3" t="inlineStr">
         <is>
-          <t>―</t>
+          <t>資料：北塩原村</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="4" t="inlineStr">
         <is>
-          <t>表5-6</t>
+          <t>表5-5</t>
         </is>
       </c>
       <c r="B49" s="4" t="inlineStr">
         <is>
-          <t>訪問系サービスの利用がない場合に確かめる事項</t>
+          <t>訪問系サービスの見込量</t>
         </is>
       </c>
       <c r="C49" s="4" t="inlineStr">
@@ -2776,7 +2776,7 @@
       </c>
       <c r="D49" s="4" t="inlineStr">
         <is>
-          <t>確かめる側 / 確かめる事項</t>
+          <t>サービス種別 / 単位</t>
         </is>
       </c>
       <c r="E49" s="4" t="inlineStr">
@@ -2788,12 +2788,12 @@
     <row r="50">
       <c r="A50" s="3" t="inlineStr">
         <is>
-          <t>表5-7</t>
+          <t>表5-6</t>
         </is>
       </c>
       <c r="B50" s="3" t="inlineStr">
         <is>
-          <t>日中活動系サービスの実績</t>
+          <t>訪問系サービスの利用がない場合に確かめる事項</t>
         </is>
       </c>
       <c r="C50" s="3" t="inlineStr">
@@ -2803,24 +2803,24 @@
       </c>
       <c r="D50" s="3" t="inlineStr">
         <is>
-          <t>サービス種別 / 単位</t>
+          <t>確かめる側 / 確かめる事項</t>
         </is>
       </c>
       <c r="E50" s="3" t="inlineStr">
         <is>
-          <t>資料：北塩原村</t>
+          <t>―</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="4" t="inlineStr">
         <is>
-          <t>表5-8</t>
+          <t>表5-7</t>
         </is>
       </c>
       <c r="B51" s="4" t="inlineStr">
         <is>
-          <t>日中活動系サービスの見込量</t>
+          <t>日中活動系サービスの実績</t>
         </is>
       </c>
       <c r="C51" s="4" t="inlineStr">
@@ -2835,19 +2835,19 @@
       </c>
       <c r="E51" s="4" t="inlineStr">
         <is>
-          <t>―</t>
+          <t>資料：北塩原村</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="3" t="inlineStr">
         <is>
-          <t>表5-9</t>
+          <t>表5-8</t>
         </is>
       </c>
       <c r="B52" s="3" t="inlineStr">
         <is>
-          <t>強度行動障害を有する方等の生活介護の利用の見込み</t>
+          <t>日中活動系サービスの見込量</t>
         </is>
       </c>
       <c r="C52" s="3" t="inlineStr">
@@ -2857,7 +2857,7 @@
       </c>
       <c r="D52" s="3" t="inlineStr">
         <is>
-          <t>区分 / 現在の人数</t>
+          <t>サービス種別 / 単位</t>
         </is>
       </c>
       <c r="E52" s="3" t="inlineStr">
@@ -2869,12 +2869,12 @@
     <row r="53">
       <c r="A53" s="4" t="inlineStr">
         <is>
-          <t>表5-10</t>
+          <t>表5-9</t>
         </is>
       </c>
       <c r="B53" s="4" t="inlineStr">
         <is>
-          <t>居住系サービスの実績</t>
+          <t>強度行動障害を有する方等の生活介護の利用の見込み</t>
         </is>
       </c>
       <c r="C53" s="4" t="inlineStr">
@@ -2884,24 +2884,24 @@
       </c>
       <c r="D53" s="4" t="inlineStr">
         <is>
-          <t>サービス種別 / 単位</t>
+          <t>区分 / 現在の人数</t>
         </is>
       </c>
       <c r="E53" s="4" t="inlineStr">
         <is>
-          <t>資料：北塩原村</t>
+          <t>―</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" s="3" t="inlineStr">
         <is>
-          <t>表5-11</t>
+          <t>表5-10</t>
         </is>
       </c>
       <c r="B54" s="3" t="inlineStr">
         <is>
-          <t>居住系サービスの見込量</t>
+          <t>居住系サービスの実績</t>
         </is>
       </c>
       <c r="C54" s="3" t="inlineStr">
@@ -2916,19 +2916,19 @@
       </c>
       <c r="E54" s="3" t="inlineStr">
         <is>
-          <t>―</t>
+          <t>資料：北塩原村</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" s="4" t="inlineStr">
         <is>
-          <t>表5-12</t>
+          <t>表5-11</t>
         </is>
       </c>
       <c r="B55" s="4" t="inlineStr">
         <is>
-          <t>相談支援の実績</t>
+          <t>居住系サービスの見込量</t>
         </is>
       </c>
       <c r="C55" s="4" t="inlineStr">
@@ -2943,19 +2943,19 @@
       </c>
       <c r="E55" s="4" t="inlineStr">
         <is>
-          <t>資料：北塩原村</t>
+          <t>―</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" s="3" t="inlineStr">
         <is>
-          <t>表5-13</t>
+          <t>表5-12</t>
         </is>
       </c>
       <c r="B56" s="3" t="inlineStr">
         <is>
-          <t>相談支援の見込量</t>
+          <t>相談支援の実績</t>
         </is>
       </c>
       <c r="C56" s="3" t="inlineStr">
@@ -2970,19 +2970,19 @@
       </c>
       <c r="E56" s="3" t="inlineStr">
         <is>
-          <t>―</t>
+          <t>資料：北塩原村</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" s="4" t="inlineStr">
         <is>
-          <t>表5-14</t>
+          <t>表5-13</t>
         </is>
       </c>
       <c r="B57" s="4" t="inlineStr">
         <is>
-          <t>障がい児支援の実績</t>
+          <t>相談支援の見込量</t>
         </is>
       </c>
       <c r="C57" s="4" t="inlineStr">
@@ -2997,19 +2997,19 @@
       </c>
       <c r="E57" s="4" t="inlineStr">
         <is>
-          <t>資料：北塩原村</t>
+          <t>―</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" s="3" t="inlineStr">
         <is>
-          <t>表5-15</t>
+          <t>表5-14</t>
         </is>
       </c>
       <c r="B58" s="3" t="inlineStr">
         <is>
-          <t>障がい児支援の見込量</t>
+          <t>障がい児支援の実績</t>
         </is>
       </c>
       <c r="C58" s="3" t="inlineStr">
@@ -3024,19 +3024,19 @@
       </c>
       <c r="E58" s="3" t="inlineStr">
         <is>
-          <t>―</t>
+          <t>資料：北塩原村</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" s="4" t="inlineStr">
         <is>
-          <t>表5-16</t>
+          <t>表5-15</t>
         </is>
       </c>
       <c r="B59" s="4" t="inlineStr">
         <is>
-          <t>村内に事業所がないサービスの確保の経路</t>
+          <t>障がい児支援の見込量</t>
         </is>
       </c>
       <c r="C59" s="4" t="inlineStr">
@@ -3046,7 +3046,7 @@
       </c>
       <c r="D59" s="4" t="inlineStr">
         <is>
-          <t>サービス / 本村の設置数</t>
+          <t>サービス種別 / 単位</t>
         </is>
       </c>
       <c r="E59" s="4" t="inlineStr">
@@ -3058,12 +3058,12 @@
     <row r="60">
       <c r="A60" s="3" t="inlineStr">
         <is>
-          <t>表5-17</t>
+          <t>表5-16</t>
         </is>
       </c>
       <c r="B60" s="3" t="inlineStr">
         <is>
-          <t>高次脳機能障がいと似た状態の切り分けと相談をつなぐ先</t>
+          <t>村内に事業所がないサービスの確保の経路</t>
         </is>
       </c>
       <c r="C60" s="3" t="inlineStr">
@@ -3073,24 +3073,24 @@
       </c>
       <c r="D60" s="3" t="inlineStr">
         <is>
-          <t>区分 / 施行令での扱い</t>
+          <t>サービス / 本村の設置数</t>
         </is>
       </c>
       <c r="E60" s="3" t="inlineStr">
         <is>
-          <t>資料：高次脳機能障害者支援法施行令（令和８年政令第60号）第１条により作成</t>
+          <t>―</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" s="4" t="inlineStr">
         <is>
-          <t>表5-18</t>
+          <t>表5-17</t>
         </is>
       </c>
       <c r="B61" s="4" t="inlineStr">
         <is>
-          <t>地域生活支援拠点の実績について４町村で揃える定義</t>
+          <t>高次脳機能障がいと似た状態の切り分けと相談をつなぐ先</t>
         </is>
       </c>
       <c r="C61" s="4" t="inlineStr">
@@ -3100,24 +3100,24 @@
       </c>
       <c r="D61" s="4" t="inlineStr">
         <is>
-          <t>記録する事項 / ４町村で揃える定義</t>
+          <t>区分 / 施行令での扱い</t>
         </is>
       </c>
       <c r="E61" s="4" t="inlineStr">
         <is>
-          <t>―</t>
+          <t>資料：高次脳機能障害者支援法施行令（令和８年政令第60号）第１条により作成</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" s="3" t="inlineStr">
         <is>
-          <t>表5-19</t>
+          <t>表5-18</t>
         </is>
       </c>
       <c r="B62" s="3" t="inlineStr">
         <is>
-          <t>一般の子育て施策と障がい福祉の切り分け</t>
+          <t>地域生活支援拠点の実績について４町村で揃える定義</t>
         </is>
       </c>
       <c r="C62" s="3" t="inlineStr">
@@ -3127,7 +3127,7 @@
       </c>
       <c r="D62" s="3" t="inlineStr">
         <is>
-          <t>場面 / まず確かめる一般の子育て施策</t>
+          <t>記録する事項 / ４町村で揃える定義</t>
         </is>
       </c>
       <c r="E62" s="3" t="inlineStr">
@@ -3139,12 +3139,12 @@
     <row r="63">
       <c r="A63" s="4" t="inlineStr">
         <is>
-          <t>表5-20</t>
+          <t>表5-19</t>
         </is>
       </c>
       <c r="B63" s="4" t="inlineStr">
         <is>
-          <t>事業所の受入余力について照会する事項</t>
+          <t>一般の子育て施策と障がい福祉の切り分け</t>
         </is>
       </c>
       <c r="C63" s="4" t="inlineStr">
@@ -3154,7 +3154,7 @@
       </c>
       <c r="D63" s="4" t="inlineStr">
         <is>
-          <t>照会する事項 / 確保できる量との関係</t>
+          <t>場面 / まず確かめる一般の子育て施策</t>
         </is>
       </c>
       <c r="E63" s="4" t="inlineStr">
@@ -3166,12 +3166,12 @@
     <row r="64">
       <c r="A64" s="3" t="inlineStr">
         <is>
-          <t>表5-21</t>
+          <t>表5-20</t>
         </is>
       </c>
       <c r="B64" s="3" t="inlineStr">
         <is>
-          <t>緊急時に働く仕組み（４つの場面）</t>
+          <t>事業所の受入余力について照会する事項</t>
         </is>
       </c>
       <c r="C64" s="3" t="inlineStr">
@@ -3181,7 +3181,7 @@
       </c>
       <c r="D64" s="3" t="inlineStr">
         <is>
-          <t>場面 / 想定される事態</t>
+          <t>照会する事項 / 確保できる量との関係</t>
         </is>
       </c>
       <c r="E64" s="3" t="inlineStr">
@@ -3193,12 +3193,12 @@
     <row r="65">
       <c r="A65" s="4" t="inlineStr">
         <is>
-          <t>表5-22</t>
+          <t>表5-21</t>
         </is>
       </c>
       <c r="B65" s="4" t="inlineStr">
         <is>
-          <t>災害時にサービスを止めないための備え</t>
+          <t>緊急時に働く仕組み（４つの場面）</t>
         </is>
       </c>
       <c r="C65" s="4" t="inlineStr">
@@ -3208,7 +3208,7 @@
       </c>
       <c r="D65" s="4" t="inlineStr">
         <is>
-          <t>備える事項 / 本村の取組み</t>
+          <t>場面 / 想定される事態</t>
         </is>
       </c>
       <c r="E65" s="4" t="inlineStr">
@@ -3220,12 +3220,12 @@
     <row r="66">
       <c r="A66" s="3" t="inlineStr">
         <is>
-          <t>表5-23</t>
+          <t>表5-22</t>
         </is>
       </c>
       <c r="B66" s="3" t="inlineStr">
         <is>
-          <t>災害時の情報の伝達について確かめること</t>
+          <t>災害時にサービスを止めないための備え</t>
         </is>
       </c>
       <c r="C66" s="3" t="inlineStr">
@@ -3235,7 +3235,7 @@
       </c>
       <c r="D66" s="3" t="inlineStr">
         <is>
-          <t>確かめること / 確かめ方</t>
+          <t>備える事項 / 本村の取組み</t>
         </is>
       </c>
       <c r="E66" s="3" t="inlineStr">
@@ -3247,12 +3247,12 @@
     <row r="67">
       <c r="A67" s="4" t="inlineStr">
         <is>
-          <t>表5-24</t>
+          <t>表5-23</t>
         </is>
       </c>
       <c r="B67" s="4" t="inlineStr">
         <is>
-          <t>虐待の予防から再発の防止までの流れ</t>
+          <t>災害時の情報の伝達について確かめること</t>
         </is>
       </c>
       <c r="C67" s="4" t="inlineStr">
@@ -3262,7 +3262,7 @@
       </c>
       <c r="D67" s="4" t="inlineStr">
         <is>
-          <t>段階 / 本村の取組み</t>
+          <t>確かめること / 確かめ方</t>
         </is>
       </c>
       <c r="E67" s="4" t="inlineStr">
@@ -3274,12 +3274,12 @@
     <row r="68">
       <c r="A68" s="3" t="inlineStr">
         <is>
-          <t>表5-25</t>
+          <t>表5-24</t>
         </is>
       </c>
       <c r="B68" s="3" t="inlineStr">
         <is>
-          <t>経営基盤に関して把握する事項</t>
+          <t>虐待の予防から再発の防止までの流れ</t>
         </is>
       </c>
       <c r="C68" s="3" t="inlineStr">
@@ -3289,7 +3289,7 @@
       </c>
       <c r="D68" s="3" t="inlineStr">
         <is>
-          <t>把握する事項 / 見込量への影響</t>
+          <t>段階 / 本村の取組み</t>
         </is>
       </c>
       <c r="E68" s="3" t="inlineStr">
@@ -3301,12 +3301,12 @@
     <row r="69">
       <c r="A69" s="4" t="inlineStr">
         <is>
-          <t>表5-26</t>
+          <t>表5-25</t>
         </is>
       </c>
       <c r="B69" s="4" t="inlineStr">
         <is>
-          <t>冬季の支援を検討する三つの段階</t>
+          <t>経営基盤に関して把握する事項</t>
         </is>
       </c>
       <c r="C69" s="4" t="inlineStr">
@@ -3316,7 +3316,7 @@
       </c>
       <c r="D69" s="4" t="inlineStr">
         <is>
-          <t>段階 / 確かめること</t>
+          <t>把握する事項 / 見込量への影響</t>
         </is>
       </c>
       <c r="E69" s="4" t="inlineStr">
@@ -3328,12 +3328,12 @@
     <row r="70">
       <c r="A70" s="3" t="inlineStr">
         <is>
-          <t>表5-27</t>
+          <t>表5-26</t>
         </is>
       </c>
       <c r="B70" s="3" t="inlineStr">
         <is>
-          <t>冬季の通行規制による中断について記録する事項</t>
+          <t>冬季の支援を検討する三つの段階</t>
         </is>
       </c>
       <c r="C70" s="3" t="inlineStr">
@@ -3343,7 +3343,7 @@
       </c>
       <c r="D70" s="3" t="inlineStr">
         <is>
-          <t>記録する事項 / 記録の仕方</t>
+          <t>段階 / 確かめること</t>
         </is>
       </c>
       <c r="E70" s="3" t="inlineStr">
@@ -3355,12 +3355,12 @@
     <row r="71">
       <c r="A71" s="4" t="inlineStr">
         <is>
-          <t>表5-28</t>
+          <t>表5-27</t>
         </is>
       </c>
       <c r="B71" s="4" t="inlineStr">
         <is>
-          <t>医療へのアクセス</t>
+          <t>冬季の通行規制による中断について記録する事項</t>
         </is>
       </c>
       <c r="C71" s="4" t="inlineStr">
@@ -3370,7 +3370,7 @@
       </c>
       <c r="D71" s="4" t="inlineStr">
         <is>
-          <t>場面 / 主な医療資源</t>
+          <t>記録する事項 / 記録の仕方</t>
         </is>
       </c>
       <c r="E71" s="4" t="inlineStr">
@@ -3382,12 +3382,12 @@
     <row r="72">
       <c r="A72" s="3" t="inlineStr">
         <is>
-          <t>表5-29</t>
+          <t>表5-28</t>
         </is>
       </c>
       <c r="B72" s="3" t="inlineStr">
         <is>
-          <t>地域生活支援事業の実績</t>
+          <t>医療へのアクセス</t>
         </is>
       </c>
       <c r="C72" s="3" t="inlineStr">
@@ -3397,24 +3397,24 @@
       </c>
       <c r="D72" s="3" t="inlineStr">
         <is>
-          <t>サービスの種類 / 令和６年度</t>
+          <t>場面 / 主な医療資源</t>
         </is>
       </c>
       <c r="E72" s="3" t="inlineStr">
         <is>
-          <t>資料：北塩原村</t>
+          <t>―</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" s="4" t="inlineStr">
         <is>
-          <t>表5-30</t>
+          <t>表5-29</t>
         </is>
       </c>
       <c r="B73" s="4" t="inlineStr">
         <is>
-          <t>地域生活支援事業の見込量</t>
+          <t>地域生活支援事業の実績</t>
         </is>
       </c>
       <c r="C73" s="4" t="inlineStr">
@@ -3424,24 +3424,24 @@
       </c>
       <c r="D73" s="4" t="inlineStr">
         <is>
-          <t>サービスの種類 / 令和９年度</t>
+          <t>サービスの種類 / 令和６年度</t>
         </is>
       </c>
       <c r="E73" s="4" t="inlineStr">
         <is>
-          <t>―</t>
+          <t>資料：北塩原村</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" s="3" t="inlineStr">
         <is>
-          <t>表5-31</t>
+          <t>表5-30</t>
         </is>
       </c>
       <c r="B74" s="3" t="inlineStr">
         <is>
-          <t>実績がない事業の扱い</t>
+          <t>地域生活支援事業の見込量</t>
         </is>
       </c>
       <c r="C74" s="3" t="inlineStr">
@@ -3451,7 +3451,7 @@
       </c>
       <c r="D74" s="3" t="inlineStr">
         <is>
-          <t>実績がない理由 / 確かめ方</t>
+          <t>サービスの種類 / 令和９年度</t>
         </is>
       </c>
       <c r="E74" s="3" t="inlineStr">
@@ -3463,12 +3463,12 @@
     <row r="75">
       <c r="A75" s="4" t="inlineStr">
         <is>
-          <t>表5-32</t>
+          <t>表5-31</t>
         </is>
       </c>
       <c r="B75" s="4" t="inlineStr">
         <is>
-          <t>地域生活支援事業の実施に必要な事項</t>
+          <t>実績がない事業の扱い</t>
         </is>
       </c>
       <c r="C75" s="4" t="inlineStr">
@@ -3478,7 +3478,7 @@
       </c>
       <c r="D75" s="4" t="inlineStr">
         <is>
-          <t>事項 / 本村の取扱い</t>
+          <t>実績がない理由 / 確かめ方</t>
         </is>
       </c>
       <c r="E75" s="4" t="inlineStr">
@@ -3490,12 +3490,12 @@
     <row r="76">
       <c r="A76" s="3" t="inlineStr">
         <is>
-          <t>表5-33</t>
+          <t>表5-32</t>
         </is>
       </c>
       <c r="B76" s="3" t="inlineStr">
         <is>
-          <t>本人に代わって伝えるための道具の使い分け</t>
+          <t>地域生活支援事業の実施に必要な事項</t>
         </is>
       </c>
       <c r="C76" s="3" t="inlineStr">
@@ -3505,7 +3505,7 @@
       </c>
       <c r="D76" s="3" t="inlineStr">
         <is>
-          <t>道具 / 伝える場面</t>
+          <t>事項 / 本村の取扱い</t>
         </is>
       </c>
       <c r="E76" s="3" t="inlineStr">
@@ -3517,12 +3517,12 @@
     <row r="77">
       <c r="A77" s="4" t="inlineStr">
         <is>
-          <t>表5-34</t>
+          <t>表5-33</t>
         </is>
       </c>
       <c r="B77" s="4" t="inlineStr">
         <is>
-          <t>年齢到達に伴うサービスの移行</t>
+          <t>本人に代わって伝えるための道具の使い分け</t>
         </is>
       </c>
       <c r="C77" s="4" t="inlineStr">
@@ -3532,7 +3532,7 @@
       </c>
       <c r="D77" s="4" t="inlineStr">
         <is>
-          <t>年齢 / 制度上の内容</t>
+          <t>道具 / 伝える場面</t>
         </is>
       </c>
       <c r="E77" s="4" t="inlineStr">
@@ -3544,12 +3544,12 @@
     <row r="78">
       <c r="A78" s="3" t="inlineStr">
         <is>
-          <t>表5-35</t>
+          <t>表5-34</t>
         </is>
       </c>
       <c r="B78" s="3" t="inlineStr">
         <is>
-          <t>学校卒業に伴う移行について確認する事項</t>
+          <t>年齢到達に伴うサービスの移行</t>
         </is>
       </c>
       <c r="C78" s="3" t="inlineStr">
@@ -3559,7 +3559,7 @@
       </c>
       <c r="D78" s="3" t="inlineStr">
         <is>
-          <t>確認する事項 / 見込量への反映</t>
+          <t>年齢 / 制度上の内容</t>
         </is>
       </c>
       <c r="E78" s="3" t="inlineStr">
@@ -3571,12 +3571,12 @@
     <row r="79">
       <c r="A79" s="4" t="inlineStr">
         <is>
-          <t>表5-36</t>
+          <t>表5-35</t>
         </is>
       </c>
       <c r="B79" s="4" t="inlineStr">
         <is>
-          <t>65歳到達時のサービスの区分</t>
+          <t>学校卒業に伴う移行について確認する事項</t>
         </is>
       </c>
       <c r="C79" s="4" t="inlineStr">
@@ -3586,7 +3586,7 @@
       </c>
       <c r="D79" s="4" t="inlineStr">
         <is>
-          <t>区分 / 該当するサービス</t>
+          <t>確認する事項 / 見込量への反映</t>
         </is>
       </c>
       <c r="E79" s="4" t="inlineStr">
@@ -3598,12 +3598,12 @@
     <row r="80">
       <c r="A80" s="3" t="inlineStr">
         <is>
-          <t>表5-37</t>
+          <t>表5-36</t>
         </is>
       </c>
       <c r="B80" s="3" t="inlineStr">
         <is>
-          <t>事業所の指定の形と65歳到達後の続け方</t>
+          <t>65歳到達時のサービスの区分</t>
         </is>
       </c>
       <c r="C80" s="3" t="inlineStr">
@@ -3613,7 +3613,7 @@
       </c>
       <c r="D80" s="3" t="inlineStr">
         <is>
-          <t>いま利用している事業所の指定の形 / 65歳に達した後の続け方</t>
+          <t>区分 / 該当するサービス</t>
         </is>
       </c>
       <c r="E80" s="3" t="inlineStr">
@@ -3625,12 +3625,12 @@
     <row r="81">
       <c r="A81" s="4" t="inlineStr">
         <is>
-          <t>表5-38</t>
+          <t>表5-37</t>
         </is>
       </c>
       <c r="B81" s="4" t="inlineStr">
         <is>
-          <t>65歳到達時に確認する事項</t>
+          <t>事業所の指定の形と65歳到達後の続け方</t>
         </is>
       </c>
       <c r="C81" s="4" t="inlineStr">
@@ -3640,7 +3640,7 @@
       </c>
       <c r="D81" s="4" t="inlineStr">
         <is>
-          <t>確認する事項 / 確認の内容</t>
+          <t>いま利用している事業所の指定の形 / 65歳に達した後の続け方</t>
         </is>
       </c>
       <c r="E81" s="4" t="inlineStr">
@@ -3652,12 +3652,12 @@
     <row r="82">
       <c r="A82" s="3" t="inlineStr">
         <is>
-          <t>表5-39</t>
+          <t>表5-38</t>
         </is>
       </c>
       <c r="B82" s="3" t="inlineStr">
         <is>
-          <t>65歳到達時の引継ぎの時期と担当</t>
+          <t>65歳到達時に確認する事項</t>
         </is>
       </c>
       <c r="C82" s="3" t="inlineStr">
@@ -3667,7 +3667,7 @@
       </c>
       <c r="D82" s="3" t="inlineStr">
         <is>
-          <t>時期 / 行うこと</t>
+          <t>確認する事項 / 確認の内容</t>
         </is>
       </c>
       <c r="E82" s="3" t="inlineStr">
@@ -3679,12 +3679,12 @@
     <row r="83">
       <c r="A83" s="4" t="inlineStr">
         <is>
-          <t>表5-40</t>
+          <t>表5-39</t>
         </is>
       </c>
       <c r="B83" s="4" t="inlineStr">
         <is>
-          <t>介護保険の地域支援事業の区分と対象者の定め</t>
+          <t>65歳到達時の引継ぎの時期と担当</t>
         </is>
       </c>
       <c r="C83" s="4" t="inlineStr">
@@ -3694,24 +3694,24 @@
       </c>
       <c r="D83" s="4" t="inlineStr">
         <is>
-          <t>地域支援事業の区分 / 主な事業</t>
+          <t>時期 / 行うこと</t>
         </is>
       </c>
       <c r="E83" s="4" t="inlineStr">
         <is>
-          <t>資料：地域支援事業の実施について（老発第0609001号。最終改正 令和８年８月20日）により作成</t>
+          <t>―</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" s="3" t="inlineStr">
         <is>
-          <t>表5-41</t>
+          <t>表5-40</t>
         </is>
       </c>
       <c r="B84" s="3" t="inlineStr">
         <is>
-          <t>関係機関と連携の内容</t>
+          <t>介護保険の地域支援事業の区分と対象者の定め</t>
         </is>
       </c>
       <c r="C84" s="3" t="inlineStr">
@@ -3721,24 +3721,24 @@
       </c>
       <c r="D84" s="3" t="inlineStr">
         <is>
-          <t>分野 / 関係機関</t>
+          <t>地域支援事業の区分 / 主な事業</t>
         </is>
       </c>
       <c r="E84" s="3" t="inlineStr">
         <is>
-          <t>―</t>
+          <t>資料：地域支援事業の実施について（老発第0609001号。最終改正 令和８年８月20日）により作成</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" s="4" t="inlineStr">
         <is>
-          <t>表5-42</t>
+          <t>表5-41</t>
         </is>
       </c>
       <c r="B85" s="4" t="inlineStr">
         <is>
-          <t>障がい福祉サービス等に係る給付費の推移</t>
+          <t>関係機関と連携の内容</t>
         </is>
       </c>
       <c r="C85" s="4" t="inlineStr">
@@ -3748,24 +3748,24 @@
       </c>
       <c r="D85" s="4" t="inlineStr">
         <is>
-          <t>年度 / 介護給付費等</t>
+          <t>分野 / 関係機関</t>
         </is>
       </c>
       <c r="E85" s="4" t="inlineStr">
         <is>
-          <t>資料：村提供の障がいサービス給付実績</t>
+          <t>―</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" s="3" t="inlineStr">
         <is>
-          <t>表5-43</t>
+          <t>表5-42</t>
         </is>
       </c>
       <c r="B86" s="3" t="inlineStr">
         <is>
-          <t>財源構成（令和７年度・法定負担割合による試算）</t>
+          <t>障がい福祉サービス等に係る給付費の推移</t>
         </is>
       </c>
       <c r="C86" s="3" t="inlineStr">
@@ -3775,7 +3775,7 @@
       </c>
       <c r="D86" s="3" t="inlineStr">
         <is>
-          <t>区分 / 金額</t>
+          <t>年度 / 介護給付費等</t>
         </is>
       </c>
       <c r="E86" s="3" t="inlineStr">
@@ -3787,12 +3787,12 @@
     <row r="87">
       <c r="A87" s="4" t="inlineStr">
         <is>
-          <t>表5-44</t>
+          <t>表5-43</t>
         </is>
       </c>
       <c r="B87" s="4" t="inlineStr">
         <is>
-          <t>サービス別の給付費と計画上の位置づけ（令和７年度）</t>
+          <t>財源構成（令和７年度・法定負担割合による試算）</t>
         </is>
       </c>
       <c r="C87" s="4" t="inlineStr">
@@ -3802,7 +3802,7 @@
       </c>
       <c r="D87" s="4" t="inlineStr">
         <is>
-          <t>サービス / 給付費（構成比）</t>
+          <t>区分 / 金額</t>
         </is>
       </c>
       <c r="E87" s="4" t="inlineStr">
@@ -3814,39 +3814,39 @@
     <row r="88">
       <c r="A88" s="3" t="inlineStr">
         <is>
-          <t>表6-1</t>
+          <t>表5-44</t>
         </is>
       </c>
       <c r="B88" s="3" t="inlineStr">
         <is>
-          <t>高齢化率の推移</t>
+          <t>サービス別の給付費と計画上の位置づけ（令和７年度）</t>
         </is>
       </c>
       <c r="C88" s="3" t="inlineStr">
         <is>
-          <t>第6章</t>
+          <t>第5章</t>
         </is>
       </c>
       <c r="D88" s="3" t="inlineStr">
         <is>
-          <t>年度 / 高齢化率</t>
+          <t>サービス / 給付費（構成比）</t>
         </is>
       </c>
       <c r="E88" s="3" t="inlineStr">
         <is>
-          <t>資料：北塩原村</t>
+          <t>資料：村提供の障がいサービス給付実績</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" s="4" t="inlineStr">
         <is>
-          <t>表6-2</t>
+          <t>表6-1</t>
         </is>
       </c>
       <c r="B89" s="4" t="inlineStr">
         <is>
-          <t>精神障がい者及び知的障がい者の人数の推移</t>
+          <t>高齢化率の推移</t>
         </is>
       </c>
       <c r="C89" s="4" t="inlineStr">
@@ -3856,7 +3856,7 @@
       </c>
       <c r="D89" s="4" t="inlineStr">
         <is>
-          <t>年度 / 精神障がい者数（※１）</t>
+          <t>年度 / 高齢化率</t>
         </is>
       </c>
       <c r="E89" s="4" t="inlineStr">
@@ -3868,12 +3868,12 @@
     <row r="90">
       <c r="A90" s="3" t="inlineStr">
         <is>
-          <t>表6-3</t>
+          <t>表6-2</t>
         </is>
       </c>
       <c r="B90" s="3" t="inlineStr">
         <is>
-          <t>成年後見制度利用支援事業の利用状況</t>
+          <t>精神障がい者及び知的障がい者の人数の推移</t>
         </is>
       </c>
       <c r="C90" s="3" t="inlineStr">
@@ -3883,7 +3883,7 @@
       </c>
       <c r="D90" s="3" t="inlineStr">
         <is>
-          <t>区分 / 令和５年度</t>
+          <t>年度 / 精神障がい者数（※１）</t>
         </is>
       </c>
       <c r="E90" s="3" t="inlineStr">
@@ -3895,12 +3895,12 @@
     <row r="91">
       <c r="A91" s="4" t="inlineStr">
         <is>
-          <t>表6-4</t>
+          <t>表6-3</t>
         </is>
       </c>
       <c r="B91" s="4" t="inlineStr">
         <is>
-          <t>成年後見制度の利用促進に係る指標</t>
+          <t>成年後見制度利用支援事業の利用状況</t>
         </is>
       </c>
       <c r="C91" s="4" t="inlineStr">
@@ -3910,34 +3910,34 @@
       </c>
       <c r="D91" s="4" t="inlineStr">
         <is>
-          <t>指標 / 何を数えるか</t>
+          <t>区分 / 令和５年度</t>
         </is>
       </c>
       <c r="E91" s="4" t="inlineStr">
         <is>
-          <t>―</t>
+          <t>資料：北塩原村</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" s="3" t="inlineStr">
         <is>
-          <t>表7-1</t>
+          <t>表6-4</t>
         </is>
       </c>
       <c r="B92" s="3" t="inlineStr">
         <is>
-          <t>健康21・グッドヘルスプランとの対応</t>
+          <t>成年後見制度の利用促進に係る指標</t>
         </is>
       </c>
       <c r="C92" s="3" t="inlineStr">
         <is>
-          <t>第7章</t>
+          <t>第6章</t>
         </is>
       </c>
       <c r="D92" s="3" t="inlineStr">
         <is>
-          <t>項目 / 健康21・グッドヘルスプラン</t>
+          <t>指標 / 何を数えるか</t>
         </is>
       </c>
       <c r="E92" s="3" t="inlineStr">
@@ -3949,12 +3949,12 @@
     <row r="93">
       <c r="A93" s="4" t="inlineStr">
         <is>
-          <t>表7-2</t>
+          <t>表7-1</t>
         </is>
       </c>
       <c r="B93" s="4" t="inlineStr">
         <is>
-          <t>第五次総合振興計画における本計画の位置づけ</t>
+          <t>健康21・グッドヘルスプランとの対応</t>
         </is>
       </c>
       <c r="C93" s="4" t="inlineStr">
@@ -3964,7 +3964,7 @@
       </c>
       <c r="D93" s="4" t="inlineStr">
         <is>
-          <t>総合振興計画の位置づけ / 内容</t>
+          <t>項目 / 健康21・グッドヘルスプラン</t>
         </is>
       </c>
       <c r="E93" s="4" t="inlineStr">
@@ -3976,12 +3976,12 @@
     <row r="94">
       <c r="A94" s="3" t="inlineStr">
         <is>
-          <t>表7-3</t>
+          <t>表7-2</t>
         </is>
       </c>
       <c r="B94" s="3" t="inlineStr">
         <is>
-          <t>高齢者福祉計画・介護保険事業計画と重ねて数えないための確認事項</t>
+          <t>第五次総合振興計画における本計画の位置づけ</t>
         </is>
       </c>
       <c r="C94" s="3" t="inlineStr">
@@ -3991,7 +3991,7 @@
       </c>
       <c r="D94" s="3" t="inlineStr">
         <is>
-          <t>事項 / 両計画での扱い</t>
+          <t>総合振興計画の位置づけ / 内容</t>
         </is>
       </c>
       <c r="E94" s="3" t="inlineStr">
@@ -4003,12 +4003,12 @@
     <row r="95">
       <c r="A95" s="4" t="inlineStr">
         <is>
-          <t>表7-4</t>
+          <t>表7-3</t>
         </is>
       </c>
       <c r="B95" s="4" t="inlineStr">
         <is>
-          <t>こども・子育て計画との整合を確かめる事項</t>
+          <t>高齢者福祉計画・介護保険事業計画と重ねて数えないための確認事項</t>
         </is>
       </c>
       <c r="C95" s="4" t="inlineStr">
@@ -4018,7 +4018,7 @@
       </c>
       <c r="D95" s="4" t="inlineStr">
         <is>
-          <t>確かめる事項 / 確かめ方</t>
+          <t>事項 / 両計画での扱い</t>
         </is>
       </c>
       <c r="E95" s="4" t="inlineStr">
@@ -4030,22 +4030,22 @@
     <row r="96">
       <c r="A96" s="3" t="inlineStr">
         <is>
-          <t>表8-1</t>
+          <t>表7-4</t>
         </is>
       </c>
       <c r="B96" s="3" t="inlineStr">
         <is>
-          <t>北塩原村障がい者自立支援協議会委員名簿</t>
+          <t>こども・子育て計画との整合を確かめる事項</t>
         </is>
       </c>
       <c r="C96" s="3" t="inlineStr">
         <is>
-          <t>第8章</t>
+          <t>第7章</t>
         </is>
       </c>
       <c r="D96" s="3" t="inlineStr">
         <is>
-          <t>区　分 / 氏　名</t>
+          <t>確かめる事項 / 確かめ方</t>
         </is>
       </c>
       <c r="E96" s="3" t="inlineStr">
@@ -4057,12 +4057,12 @@
     <row r="97">
       <c r="A97" s="4" t="inlineStr">
         <is>
-          <t>表8-2</t>
+          <t>表8-1</t>
         </is>
       </c>
       <c r="B97" s="4" t="inlineStr">
         <is>
-          <t>計画の策定経過</t>
+          <t>北塩原村障がい者自立支援協議会委員名簿</t>
         </is>
       </c>
       <c r="C97" s="4" t="inlineStr">
@@ -4072,7 +4072,7 @@
       </c>
       <c r="D97" s="4" t="inlineStr">
         <is>
-          <t>年月日 / 内容</t>
+          <t>区　分 / 氏　名</t>
         </is>
       </c>
       <c r="E97" s="4" t="inlineStr">
@@ -4084,12 +4084,12 @@
     <row r="98">
       <c r="A98" s="3" t="inlineStr">
         <is>
-          <t>表8-3</t>
+          <t>表8-2</t>
         </is>
       </c>
       <c r="B98" s="3" t="inlineStr">
         <is>
-          <t>近年の障がい者施策の動向</t>
+          <t>計画の策定経過</t>
         </is>
       </c>
       <c r="C98" s="3" t="inlineStr">
@@ -4099,7 +4099,7 @@
       </c>
       <c r="D98" s="3" t="inlineStr">
         <is>
-          <t>年 / 主な動向</t>
+          <t>年月日 / 内容</t>
         </is>
       </c>
       <c r="E98" s="3" t="inlineStr">
@@ -4111,25 +4111,52 @@
     <row r="99">
       <c r="A99" s="4" t="inlineStr">
         <is>
+          <t>表8-3</t>
+        </is>
+      </c>
+      <c r="B99" s="4" t="inlineStr">
+        <is>
+          <t>近年の障がい者施策の動向</t>
+        </is>
+      </c>
+      <c r="C99" s="4" t="inlineStr">
+        <is>
+          <t>第8章</t>
+        </is>
+      </c>
+      <c r="D99" s="4" t="inlineStr">
+        <is>
+          <t>年 / 主な動向</t>
+        </is>
+      </c>
+      <c r="E99" s="4" t="inlineStr">
+        <is>
+          <t>―</t>
+        </is>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" s="3" t="inlineStr">
+        <is>
           <t>表8-4</t>
         </is>
       </c>
-      <c r="B99" s="4" t="inlineStr">
+      <c r="B100" s="3" t="inlineStr">
         <is>
           <t>用語解説</t>
         </is>
       </c>
-      <c r="C99" s="4" t="inlineStr">
+      <c r="C100" s="3" t="inlineStr">
         <is>
           <t>第8章</t>
         </is>
       </c>
-      <c r="D99" s="4" t="inlineStr">
+      <c r="D100" s="3" t="inlineStr">
         <is>
           <t>用語 / 説明</t>
         </is>
       </c>
-      <c r="E99" s="4" t="inlineStr">
+      <c r="E100" s="3" t="inlineStr">
         <is>
           <t>―</t>
         </is>

--- a/output/北塩原村_図表番号一覧.xlsx
+++ b/output/北塩原村_図表番号一覧.xlsx
@@ -2874,7 +2874,7 @@
       </c>
       <c r="B53" s="4" t="inlineStr">
         <is>
-          <t>強度行動障害を有する方等の生活介護の利用の見込み</t>
+          <t>強度行動障害を有する方等の重度障がい者の内数の見込み</t>
         </is>
       </c>
       <c r="C53" s="4" t="inlineStr">

--- a/output/北塩原村_図表番号一覧.xlsx
+++ b/output/北塩原村_図表番号一覧.xlsx
@@ -535,7 +535,7 @@
       </c>
       <c r="B6" s="3" t="inlineStr">
         <is>
-          <t>図26点・表95点に章ごとの通し番号を振った（図１-１・表１-１の形）。注記ボックス（【村へ確認】等の1×1の枠）45点には振っていない。確定時に削るため、番号を振ると欠番が出るからである。</t>
+          <t>図26点・表96点に章ごとの通し番号を振った（図１-１・表１-１の形）。注記ボックス（【村へ確認】等の1×1の枠）45点には振っていない。確定時に削るため、番号を振ると欠番が出るからである。</t>
         </is>
       </c>
     </row>
@@ -1542,7 +1542,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E100"/>
+  <dimension ref="A1:E101"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -1555,7 +1555,7 @@
     <row r="1" ht="30" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>表 95点</t>
+          <t>表 96点</t>
         </is>
       </c>
     </row>
@@ -4057,22 +4057,22 @@
     <row r="97">
       <c r="A97" s="4" t="inlineStr">
         <is>
-          <t>表8-1</t>
+          <t>表7-5</t>
         </is>
       </c>
       <c r="B97" s="4" t="inlineStr">
         <is>
-          <t>北塩原村障がい者自立支援協議会委員名簿</t>
+          <t>第８次福島県医療計画との連携</t>
         </is>
       </c>
       <c r="C97" s="4" t="inlineStr">
         <is>
-          <t>第8章</t>
+          <t>第7章</t>
         </is>
       </c>
       <c r="D97" s="4" t="inlineStr">
         <is>
-          <t>区　分 / 氏　名</t>
+          <t>医療計画の分野 / 県の主な内容</t>
         </is>
       </c>
       <c r="E97" s="4" t="inlineStr">
@@ -4084,12 +4084,12 @@
     <row r="98">
       <c r="A98" s="3" t="inlineStr">
         <is>
-          <t>表8-2</t>
+          <t>表8-1</t>
         </is>
       </c>
       <c r="B98" s="3" t="inlineStr">
         <is>
-          <t>計画の策定経過</t>
+          <t>北塩原村障がい者自立支援協議会委員名簿</t>
         </is>
       </c>
       <c r="C98" s="3" t="inlineStr">
@@ -4099,7 +4099,7 @@
       </c>
       <c r="D98" s="3" t="inlineStr">
         <is>
-          <t>年月日 / 内容</t>
+          <t>区　分 / 氏　名</t>
         </is>
       </c>
       <c r="E98" s="3" t="inlineStr">
@@ -4111,12 +4111,12 @@
     <row r="99">
       <c r="A99" s="4" t="inlineStr">
         <is>
-          <t>表8-3</t>
+          <t>表8-2</t>
         </is>
       </c>
       <c r="B99" s="4" t="inlineStr">
         <is>
-          <t>近年の障がい者施策の動向</t>
+          <t>計画の策定経過</t>
         </is>
       </c>
       <c r="C99" s="4" t="inlineStr">
@@ -4126,7 +4126,7 @@
       </c>
       <c r="D99" s="4" t="inlineStr">
         <is>
-          <t>年 / 主な動向</t>
+          <t>年月日 / 内容</t>
         </is>
       </c>
       <c r="E99" s="4" t="inlineStr">
@@ -4138,25 +4138,52 @@
     <row r="100">
       <c r="A100" s="3" t="inlineStr">
         <is>
+          <t>表8-3</t>
+        </is>
+      </c>
+      <c r="B100" s="3" t="inlineStr">
+        <is>
+          <t>近年の障がい者施策の動向</t>
+        </is>
+      </c>
+      <c r="C100" s="3" t="inlineStr">
+        <is>
+          <t>第8章</t>
+        </is>
+      </c>
+      <c r="D100" s="3" t="inlineStr">
+        <is>
+          <t>年 / 主な動向</t>
+        </is>
+      </c>
+      <c r="E100" s="3" t="inlineStr">
+        <is>
+          <t>―</t>
+        </is>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" s="4" t="inlineStr">
+        <is>
           <t>表8-4</t>
         </is>
       </c>
-      <c r="B100" s="3" t="inlineStr">
+      <c r="B101" s="4" t="inlineStr">
         <is>
           <t>用語解説</t>
         </is>
       </c>
-      <c r="C100" s="3" t="inlineStr">
+      <c r="C101" s="4" t="inlineStr">
         <is>
           <t>第8章</t>
         </is>
       </c>
-      <c r="D100" s="3" t="inlineStr">
+      <c r="D101" s="4" t="inlineStr">
         <is>
           <t>用語 / 説明</t>
         </is>
       </c>
-      <c r="E100" s="3" t="inlineStr">
+      <c r="E101" s="4" t="inlineStr">
         <is>
           <t>―</t>
         </is>
